--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>AI추천_new</t>
+          <t>AI추천</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U15" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U19" t="n">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U20" t="n">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U23" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U24" t="n">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U25" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U26" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U28" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U30" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U31" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U32" t="n">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U33" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U34" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U35" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U36" t="n">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U37" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U38" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U39" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U40" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U41" t="n">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U42" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U43" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U44" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U45" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U46" t="n">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U47" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U48" t="n">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U49" t="n">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U50" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U51" t="n">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U52" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U53" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U54" t="n">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U55" t="n">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U56" t="n">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U57" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U58" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U59" t="n">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U60" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U61" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U62" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U63" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U64" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U65" t="n">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U66" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U67" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U68" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U69" t="n">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U70" t="n">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U71" t="n">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U72" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U73" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U74" t="n">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U75" t="n">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U76" t="n">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U77" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U78" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U79" t="n">
@@ -7642,7 +7642,7 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>분석불가</t>
+          <t>분석중</t>
         </is>
       </c>
       <c r="U80" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U81" t="n">
@@ -7814,7 +7814,7 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
-          <t>분석불가</t>
+          <t>분석중</t>
         </is>
       </c>
       <c r="U82" t="n">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>데이터확인</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U83" t="n">

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U63"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,36 +526,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Belediye Derincespor</t>
+          <t>Steel City</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.88</v>
+        <v>5.45</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>10.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,22 +586,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>36</v>
       </c>
       <c r="R2" t="n">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,42 +609,42 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AFC Fylde</t>
+          <t>Barracas Central Res.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Rosario Central Res.</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="F3" t="n">
-        <v>5.15</v>
+        <v>3.42</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -665,75 +665,75 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="R3" t="n">
-        <v>66.2</v>
+        <v>76.2</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>66.2</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Artvin Hopaspor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Zonguldak Kömürspor</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.68</v>
+        <v>3.22</v>
       </c>
       <c r="F4" t="n">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -754,46 +754,46 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="R4" t="n">
-        <v>65.7</v>
+        <v>72.2</v>
       </c>
       <c r="S4" t="n">
-        <v>18.6</v>
+        <v>22.2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>65.7</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -803,26 +803,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Civil Service Strollers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Cumbernauld Colts</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6.9</v>
+        <v>3.98</v>
       </c>
       <c r="F5" t="n">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -853,22 +853,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="S5" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -876,52 +876,52 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Al-Rayyan SC</t>
+          <t>Atletico Tucuman</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -942,22 +942,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>65.8</v>
       </c>
       <c r="S6" t="n">
-        <v>13.3</v>
+        <v>15.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -965,42 +965,42 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>60</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eskişehirspor</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tire 2021 FK</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="F7" t="n">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="R7" t="n">
-        <v>59.1</v>
+        <v>64.8</v>
       </c>
       <c r="S7" t="n">
-        <v>22.7</v>
+        <v>18.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1054,42 +1054,42 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>59.1</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Real Bedford</t>
+          <t>Karacabey Belediyespor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Harborough Town</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.55</v>
+        <v>1.17</v>
       </c>
       <c r="F8" t="n">
-        <v>3.62</v>
+        <v>5.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1110,46 +1110,46 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="R8" t="n">
-        <v>58.5</v>
+        <v>64.8</v>
       </c>
       <c r="S8" t="n">
-        <v>11.3</v>
+        <v>18.1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>58.5</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1159,26 +1159,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weston-super-Mare</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="F9" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1209,22 +1209,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="R9" t="n">
-        <v>57.1</v>
+        <v>60.7</v>
       </c>
       <c r="S9" t="n">
-        <v>28.6</v>
+        <v>16.1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1232,42 +1232,42 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>57.1</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hanwell Town</t>
+          <t>Kufstein</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evesham United</t>
+          <t>Schwaz</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.22</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1288,75 +1288,75 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="R10" t="n">
-        <v>56.2</v>
+        <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>27.1</v>
+        <v>16.1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>56.2</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adana 1954 FK</t>
+          <t>Brechin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Buca FK</t>
+          <t>Formartine United</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="F11" t="n">
-        <v>9.6</v>
+        <v>3.84</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1387,22 +1387,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>55.6</v>
+        <v>60.6</v>
       </c>
       <c r="S11" t="n">
-        <v>22.2</v>
+        <v>6.1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1410,42 +1410,42 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>55.6</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.24</v>
+        <v>2.16</v>
       </c>
       <c r="F12" t="n">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>3.08</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1466,85 +1466,85 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="R12" t="n">
-        <v>54.3</v>
+        <v>60.2</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>54.3</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Naft</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cucuta</t>
+          <t>Al-Qasim</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.99</v>
+        <v>14.75</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1565,22 +1565,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Q13" t="n">
-        <v>206</v>
+        <v>45</v>
       </c>
       <c r="R13" t="n">
-        <v>52.9</v>
+        <v>60</v>
       </c>
       <c r="S13" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1588,42 +1588,42 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>52.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yate Town</t>
+          <t>CSKA Sofia II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Poole Town</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="F14" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="G14" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1654,22 +1654,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R14" t="n">
-        <v>52.7</v>
+        <v>57.4</v>
       </c>
       <c r="S14" t="n">
-        <v>16.4</v>
+        <v>11.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1677,52 +1677,52 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>52.7</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Blackburn Rovers U21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Reading U21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>4.75</v>
+        <v>2.23</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1733,46 +1733,46 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="R15" t="n">
-        <v>50.9</v>
+        <v>54.3</v>
       </c>
       <c r="S15" t="n">
-        <v>17.2</v>
+        <v>12.8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>50.9</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1782,36 +1782,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gainsborough Trinity</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bamber Bridge</t>
+          <t>Chelmsford City</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1822,85 +1822,85 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="R16" t="n">
-        <v>50.4</v>
+        <v>54.3</v>
       </c>
       <c r="S16" t="n">
-        <v>21.9</v>
+        <v>12.8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>50.4</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Elgin City</t>
+          <t>Flota Świnoujście</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Forfar Athletic</t>
+          <t>Noteć Czarnków</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q17" t="n">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="R17" t="n">
-        <v>46.6</v>
+        <v>52.7</v>
       </c>
       <c r="S17" t="n">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1944,42 +1944,42 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>46.6</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy</t>
+          <t>Ghivizzano Borgo Mozzano</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Sansepolcro</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="F18" t="n">
-        <v>2.88</v>
+        <v>3.66</v>
       </c>
       <c r="G18" t="n">
-        <v>4.25</v>
+        <v>6.45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2010,22 +2010,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="R18" t="n">
-        <v>46.6</v>
+        <v>52.2</v>
       </c>
       <c r="S18" t="n">
-        <v>24.1</v>
+        <v>26.1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2033,42 +2033,42 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>46.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Grimsby</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.84</v>
+        <v>5.65</v>
       </c>
       <c r="F19" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>1.49</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2089,71 +2089,71 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="R19" t="n">
-        <v>46.6</v>
+        <v>51.8</v>
       </c>
       <c r="S19" t="n">
-        <v>24.1</v>
+        <v>16.1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>46.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleethorpes Town</t>
+          <t>Al Minaa Basra</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Guiseley AFC</t>
+          <t>Duhok</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="F20" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="G20" t="n">
-        <v>3.34</v>
+        <v>2.57</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2193,17 +2193,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>46.6</v>
+        <v>51.7</v>
       </c>
       <c r="S20" t="n">
-        <v>24.1</v>
+        <v>34.5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2211,52 +2211,52 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>46.6</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>AD Carmelita</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Futbol Consultants Moravia</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="F21" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="G21" t="n">
-        <v>4.75</v>
+        <v>2.64</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2277,22 +2277,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="R21" t="n">
-        <v>46.4</v>
+        <v>51.3</v>
       </c>
       <c r="S21" t="n">
-        <v>21.4</v>
+        <v>24</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2300,47 +2300,47 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>46.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Enfield Town</t>
+          <t>Atletico el Vigia FC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dover</t>
+          <t>Fundación Lara Deportiva</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.32</v>
+        <v>4.45</v>
       </c>
       <c r="F22" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.52</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2375,52 +2375,52 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="R22" t="n">
-        <v>45.8</v>
+        <v>51.1</v>
       </c>
       <c r="S22" t="n">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>45.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Leamington</t>
+          <t>Atlético Choloma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>King's Lynn Town</t>
+          <t>Génesis</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.8</v>
+        <v>2.06</v>
       </c>
       <c r="F23" t="n">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="G23" t="n">
-        <v>1.62</v>
+        <v>3.16</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2460,70 +2460,70 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="R23" t="n">
-        <v>45.5</v>
+        <v>50.8</v>
       </c>
       <c r="S23" t="n">
-        <v>27.3</v>
+        <v>17.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>45.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Silivrispor</t>
+          <t>Lentigione</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Küçükçekmece Sinopspor</t>
+          <t>Pistoiese</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="F24" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="G24" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2544,22 +2544,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="R24" t="n">
-        <v>45</v>
+        <v>50.8</v>
       </c>
       <c r="S24" t="n">
-        <v>26</v>
+        <v>19.7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2567,38 +2567,38 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>45</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alvechurch</t>
+          <t>Kırıkkale Büyük Anadolu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>St Ives Town</t>
+          <t>Niğde Belediyesispor</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="G25" t="n">
-        <v>3.62</v>
+        <v>2.51</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2638,17 +2638,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="R25" t="n">
-        <v>44.5</v>
+        <v>50.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.2</v>
+        <v>17.8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2656,52 +2656,52 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>44.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kilis Belediyespor</t>
+          <t>Warta Sieradz</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Karaköprü Belediyespor</t>
+          <t>Olimpia Elbląg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.92</v>
+        <v>1.68</v>
       </c>
       <c r="F26" t="n">
-        <v>3.22</v>
+        <v>3.78</v>
       </c>
       <c r="G26" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2712,85 +2712,85 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="R26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S26" t="n">
-        <v>30.7</v>
+        <v>21.7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lobos Upnfm</t>
+          <t>Greenville Triumph</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>NY Cosmos</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.86</v>
+        <v>1.47</v>
       </c>
       <c r="F27" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2801,75 +2801,75 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="R27" t="n">
-        <v>43.9</v>
+        <v>49.5</v>
       </c>
       <c r="S27" t="n">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>43.9</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UMM Salal</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Al Bidda SC</t>
+          <t>Bogota FC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="G28" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="R28" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="S28" t="n">
-        <v>28.6</v>
+        <v>20.7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2939,26 +2939,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="G29" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2989,22 +2989,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R29" t="n">
-        <v>40.8</v>
+        <v>48</v>
       </c>
       <c r="S29" t="n">
-        <v>28.6</v>
+        <v>16</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3012,42 +3012,42 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>40.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oldham</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Água Santa</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="F30" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3078,22 +3078,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="R30" t="n">
-        <v>40</v>
+        <v>47.9</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3101,42 +3101,42 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>40</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3157,85 +3157,85 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="R31" t="n">
-        <v>39.3</v>
+        <v>44.9</v>
       </c>
       <c r="S31" t="n">
-        <v>21.4</v>
+        <v>20.4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>39.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>XV de Piracicaba</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Votuporanguense</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.44</v>
+        <v>1.9</v>
       </c>
       <c r="F32" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>3.82</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -3246,85 +3246,85 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="R32" t="n">
-        <v>36.6</v>
+        <v>44</v>
       </c>
       <c r="S32" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>36.6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Darlington 1883</t>
+          <t>Çorluspor 1947</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Kidderminster Harriers</t>
+          <t>Bursa Yıldırımspor</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="F33" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="G33" t="n">
-        <v>2.31</v>
+        <v>4.7</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -3335,46 +3335,46 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="R33" t="n">
-        <v>36.6</v>
+        <v>44</v>
       </c>
       <c r="S33" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>36.6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3384,26 +3384,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tiverton Town</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Gloucester City</t>
+          <t>Yeovil Town</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="F34" t="n">
-        <v>5.75</v>
+        <v>3.44</v>
       </c>
       <c r="G34" t="n">
-        <v>1.17</v>
+        <v>3.78</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1:5</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -3424,85 +3424,85 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>250</v>
       </c>
       <c r="R34" t="n">
-        <v>36.4</v>
+        <v>44</v>
       </c>
       <c r="S34" t="n">
-        <v>36.4</v>
+        <v>31.2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>36.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Kasetsart FC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="F35" t="n">
         <v>3.34</v>
       </c>
       <c r="G35" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3523,22 +3523,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="R35" t="n">
-        <v>33.9</v>
+        <v>43.4</v>
       </c>
       <c r="S35" t="n">
-        <v>32.1</v>
+        <v>30.3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3546,42 +3546,42 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>33.9</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sholing</t>
+          <t>Pikine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Walton &amp; Hersham</t>
+          <t>Teungueth</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="F36" t="n">
-        <v>3.72</v>
+        <v>2.4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3612,22 +3612,22 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="R36" t="n">
-        <v>33.8</v>
+        <v>42.9</v>
       </c>
       <c r="S36" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3635,52 +3635,52 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>33.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kırklarelispor</t>
+          <t>AJEL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ankara Demirspor</t>
+          <t>AS Camberene</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="F37" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="G37" t="n">
-        <v>2.68</v>
+        <v>7.8</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -3701,22 +3701,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="R37" t="n">
-        <v>33.3</v>
+        <v>42.3</v>
       </c>
       <c r="S37" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3724,13 +3724,13 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>33.3</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3740,26 +3740,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Baglan Dragons</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cwmbran Celtic</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="F38" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="G38" t="n">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3790,22 +3790,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="Q38" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="R38" t="n">
-        <v>32</v>
+        <v>42.3</v>
       </c>
       <c r="S38" t="n">
-        <v>32</v>
+        <v>22.3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3813,52 +3813,52 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>32</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bath City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Hemel Hempstead Town</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.08</v>
+        <v>1.83</v>
       </c>
       <c r="F39" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="G39" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -3869,75 +3869,75 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="R39" t="n">
-        <v>31.7</v>
+        <v>42.3</v>
       </c>
       <c r="S39" t="n">
-        <v>11.7</v>
+        <v>22.3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>31.7</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hereford</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Spennymoor Town</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.93</v>
+        <v>2.67</v>
       </c>
       <c r="F40" t="n">
-        <v>3.68</v>
+        <v>2.56</v>
       </c>
       <c r="G40" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3968,65 +3968,65 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>31.6</v>
+        <v>40</v>
       </c>
       <c r="S40" t="n">
-        <v>28.1</v>
+        <v>40</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>31.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston United</t>
+          <t>Itapipoca</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Uniclinic Atletico Clube</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="F41" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="G41" t="n">
-        <v>3.52</v>
+        <v>7.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4057,22 +4057,22 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="R41" t="n">
-        <v>30.8</v>
+        <v>36.7</v>
       </c>
       <c r="S41" t="n">
-        <v>15.4</v>
+        <v>34.8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4080,38 +4080,38 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>30.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aldershot Town</t>
+          <t>Real Kashmir</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Namdhari</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.04</v>
+        <v>2.01</v>
       </c>
       <c r="F42" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="G42" t="n">
-        <v>1.97</v>
+        <v>3.24</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4151,70 +4151,70 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="R42" t="n">
-        <v>30.5</v>
+        <v>36.7</v>
       </c>
       <c r="S42" t="n">
-        <v>28</v>
+        <v>34.8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>30.5</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ammanford AFC</t>
+          <t>Argentinos Juniors Res.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cambrian &amp; Clydach</t>
+          <t>Instituto Res.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4.45</v>
+        <v>1.88</v>
       </c>
       <c r="F43" t="n">
-        <v>3.8</v>
+        <v>3.06</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6</v>
+        <v>3.94</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -4225,85 +4225,85 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>221</v>
       </c>
       <c r="R43" t="n">
-        <v>28.6</v>
+        <v>36.7</v>
       </c>
       <c r="S43" t="n">
-        <v>28.6</v>
+        <v>34.8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>28.6</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stratford Town</t>
+          <t>Sevlievo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Sportist Svoge</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="F44" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="G44" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -4324,22 +4324,22 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="R44" t="n">
-        <v>27</v>
+        <v>36.7</v>
       </c>
       <c r="S44" t="n">
-        <v>26.2</v>
+        <v>34.8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4347,52 +4347,52 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>27</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Peterborough United U21</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Watford U21</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G45" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -4403,85 +4403,85 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="R45" t="n">
-        <v>25</v>
+        <v>36.1</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>30.1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>25</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>24 Erzincanspor</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kepez Belediyespor</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.45</v>
+        <v>5.75</v>
       </c>
       <c r="F46" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="G46" t="n">
-        <v>5.4</v>
+        <v>1.53</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -4492,75 +4492,75 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="R46" t="n">
-        <v>24.6</v>
+        <v>35.7</v>
       </c>
       <c r="S46" t="n">
-        <v>24.6</v>
+        <v>57.1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>24.6</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Manchester United W</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bucaramanga</t>
+          <t>Bayern Munich W</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="F47" t="n">
-        <v>2.82</v>
+        <v>3.52</v>
       </c>
       <c r="G47" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -4581,75 +4581,75 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="R47" t="n">
-        <v>24.6</v>
+        <v>35.6</v>
       </c>
       <c r="S47" t="n">
-        <v>24.6</v>
+        <v>35.6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>24.6</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>León W</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Atlas W</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.43</v>
+        <v>2.61</v>
       </c>
       <c r="F48" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="G48" t="n">
-        <v>5.35</v>
+        <v>2.39</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -4670,446 +4670,446 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="R48" t="n">
-        <v>23.1</v>
+        <v>33.3</v>
       </c>
       <c r="S48" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>23.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Huracan</t>
+          <t>SKRA Częstochowa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Miedź Legnica II</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="F49" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G49" t="n">
         <v>3.02</v>
       </c>
-      <c r="G49" t="n">
-        <v>5.4</v>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>67</v>
+      </c>
+      <c r="R49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="S49" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Altınordu</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Kastamonuspor 1966</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>오버</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>67</v>
+      </c>
+      <c r="R50" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sporting JAX</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>10</v>
+      </c>
+      <c r="R51" t="n">
+        <v>30</v>
+      </c>
+      <c r="S51" t="n">
+        <v>30</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>PRE
 VIEW</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>108</v>
-      </c>
-      <c r="R49" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="S49" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="T49" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>35</v>
+      </c>
+      <c r="R52" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="U49" t="n">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>United of Manchester</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Stockton Town</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>48</v>
-      </c>
-      <c r="R50" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S50" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U50" t="n">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Chesham United</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>AFC Hornchurch</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>101</v>
-      </c>
-      <c r="R51" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S51" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U51" t="n">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Pitbulls Santa Barbara FC</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Escorpiones Belén</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="F52" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>101</v>
-      </c>
-      <c r="R52" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S52" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
       <c r="U52" t="n">
-        <v>20.8</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Atletico Torque</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.53</v>
+        <v>1.4</v>
       </c>
       <c r="F53" t="n">
-        <v>2.91</v>
+        <v>4.15</v>
       </c>
       <c r="G53" t="n">
-        <v>2.69</v>
+        <v>6.35</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>3 : 2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -5130,22 +5130,22 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="R53" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="S53" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5153,38 +5153,38 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alfreton Town</t>
+          <t>Gucha Stars</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="F54" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="G54" t="n">
-        <v>1.59</v>
+        <v>2.38</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -5224,17 +5224,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="R54" t="n">
-        <v>19.8</v>
+        <v>27.5</v>
       </c>
       <c r="S54" t="n">
-        <v>19.8</v>
+        <v>27.5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5242,42 +5242,42 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>19.8</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>União Leiria U23</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Farense U23</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.36</v>
+        <v>1.78</v>
       </c>
       <c r="F55" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="G55" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -5298,75 +5298,75 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
       <c r="Q55" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="R55" t="n">
-        <v>19.6</v>
+        <v>24.5</v>
       </c>
       <c r="S55" t="n">
-        <v>17.6</v>
+        <v>25.5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>19.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Antigua GFC</t>
+          <t>Sporting San Jose</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Marquense</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="F56" t="n">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
-        <v>5.95</v>
+        <v>3.32</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -5397,22 +5397,22 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="R56" t="n">
-        <v>17.7</v>
+        <v>24.5</v>
       </c>
       <c r="S56" t="n">
-        <v>17.7</v>
+        <v>25.5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5420,52 +5420,52 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>17.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cardiff Draconians</t>
+          <t>Gimnasia La Plata Res.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ynyshir Albions</t>
+          <t>Racing Club Res.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="F57" t="n">
-        <v>3.78</v>
+        <v>3.02</v>
       </c>
       <c r="G57" t="n">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -5486,22 +5486,22 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="R57" t="n">
-        <v>17.7</v>
+        <v>23.7</v>
       </c>
       <c r="S57" t="n">
-        <v>21.5</v>
+        <v>23.7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5509,42 +5509,42 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>17.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Newroz</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Gharraf</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="G58" t="n">
-        <v>3.88</v>
+        <v>3.52</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="R58" t="n">
-        <v>14.7</v>
+        <v>23</v>
       </c>
       <c r="S58" t="n">
-        <v>14.7</v>
+        <v>24.3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5598,42 +5598,42 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>14.7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kettering Town</t>
+          <t>Ouakam</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Banbury United</t>
+          <t>HLM</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.76</v>
+        <v>2.22</v>
       </c>
       <c r="F59" t="n">
-        <v>3.66</v>
+        <v>2.41</v>
       </c>
       <c r="G59" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="R59" t="n">
-        <v>13.6</v>
+        <v>22.9</v>
       </c>
       <c r="S59" t="n">
-        <v>28</v>
+        <v>22.4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5687,42 +5687,42 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>13.6</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Club Atletico Barinas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dorking Wanderers</t>
+          <t>Urena SC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="F60" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="G60" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -5753,22 +5753,22 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="Q60" t="n">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="R60" t="n">
-        <v>9.5</v>
+        <v>22.9</v>
       </c>
       <c r="S60" t="n">
-        <v>9.5</v>
+        <v>22.4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5776,55 +5776,55 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>9.5</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UMECIT</t>
+          <t>Newell's Old Boys Res.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Belgrano Córdoba Res.</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="F61" t="n">
-        <v>4.05</v>
+        <v>2.85</v>
       </c>
       <c r="G61" t="n">
-        <v>6.2</v>
+        <v>3.28</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>미결</t>
@@ -5842,65 +5842,75 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>68</v>
+      </c>
+      <c r="R61" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Léttir</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Stokkseyri</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="F62" t="n">
-        <v>4.45</v>
+        <v>3.76</v>
       </c>
       <c r="G62" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1 : 5</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5921,22 +5931,22 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5944,42 +5954,42 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 24 March 2026</t>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg W</t>
+          <t>Sreenidi Deccan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lyon W</t>
+          <t>Dempo</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.95</v>
+        <v>1.62</v>
       </c>
       <c r="F63" t="n">
-        <v>5.1</v>
+        <v>3.74</v>
       </c>
       <c r="G63" t="n">
-        <v>1.34</v>
+        <v>4.45</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5989,7 +5999,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1 : 4</t>
+          <t>3 : 2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -6000,39 +6010,824 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>14</v>
+      </c>
+      <c r="R63" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S63" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tamworth</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>102</v>
+      </c>
+      <c r="R64" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S64" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Aldosivi Res.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sarmiento Res.</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>49</v>
+      </c>
+      <c r="R65" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S65" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>107</v>
+      </c>
+      <c r="R66" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="S66" t="n">
+        <v>29</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Spartak Pleven</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Belasitsa</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>107</v>
+      </c>
+      <c r="R67" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="S67" t="n">
+        <v>29</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yaracuyanos FC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Zamora FC B</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>165</v>
+      </c>
+      <c r="R68" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pazarspor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tokat Bld Plevnespor</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>80</v>
+      </c>
+      <c r="R69" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ankaragücü</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ankaraspor</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Muaither SC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Al-Markhiya</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Real Madrid W</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Barcelona W</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F72" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0 : 4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
+      <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="n">
+      <c r="S72" t="n">
         <v>0</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>원정승</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="U72" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U72"/>
+  <dimension ref="A1:U93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,46 +526,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Iceland U21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Steel City</t>
+          <t>Estonia U21</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F2" t="n">
-        <v>5.45</v>
+        <v>6.05</v>
       </c>
       <c r="G2" t="n">
-        <v>10.75</v>
+        <v>13</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>4 : 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,22 +586,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="S2" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,42 +609,42 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Barracas Central Res.</t>
+          <t>Republic of Ireland U21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rosario Central Res.</t>
+          <t>Moldova U21</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="n">
-        <v>3.42</v>
+        <v>5.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>11.75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -665,40 +665,40 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="R3" t="n">
-        <v>76.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>76.2</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -709,31 +709,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Artvin Hopaspor</t>
+          <t>Barracas Central Res.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zonguldak Kömürspor</t>
+          <t>Rosario Central Res.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0 : 3</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -764,22 +764,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>72.2</v>
+        <v>76.2</v>
       </c>
       <c r="S4" t="n">
-        <v>22.2</v>
+        <v>19</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -787,52 +787,52 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>72.2</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Civil Service Strollers</t>
+          <t>Escorpiones Belén</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cumbernauld Colts</t>
+          <t>CS Uruguay</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.98</v>
+        <v>1.38</v>
       </c>
       <c r="F5" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -843,71 +843,71 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="R5" t="n">
-        <v>66.7</v>
+        <v>73.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>66.7</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atletico Tucuman</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3</v>
+        <v>5.65</v>
       </c>
       <c r="G6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -947,17 +947,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="R6" t="n">
-        <v>65.8</v>
+        <v>73.5</v>
       </c>
       <c r="S6" t="n">
-        <v>15.8</v>
+        <v>5.9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -965,42 +965,42 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>65.8</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
-        <v>64.8</v>
+        <v>73.5</v>
       </c>
       <c r="S7" t="n">
-        <v>18.1</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>64.8</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="8">
@@ -1065,31 +1065,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Karacabey Belediyespor</t>
+          <t>Civil Service Strollers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Karaman Belediyespor</t>
+          <t>Cumbernauld Colts</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.17</v>
+        <v>3.98</v>
       </c>
       <c r="F8" t="n">
-        <v>5.4</v>
+        <v>3.54</v>
       </c>
       <c r="G8" t="n">
-        <v>13.5</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1110,40 +1110,40 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>64.8</v>
+        <v>66.7</v>
       </c>
       <c r="S8" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>64.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.97</v>
+        <v>1.38</v>
       </c>
       <c r="F9" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1199,75 +1199,75 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R9" t="n">
-        <v>60.7</v>
+        <v>66</v>
       </c>
       <c r="S9" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>60.7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kufstein</t>
+          <t>Al Quwa Al Jawiya</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Schwaz</t>
+          <t>Al Karkh</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.7</v>
+        <v>1.46</v>
       </c>
       <c r="F10" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1288,40 +1288,40 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>66</v>
       </c>
       <c r="S10" t="n">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>60.7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1332,31 +1332,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brechin</t>
+          <t>Atletico Tucuman</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Formartine United</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="F11" t="n">
-        <v>3.84</v>
+        <v>5.3</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1387,22 +1387,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>60.6</v>
+        <v>65.8</v>
       </c>
       <c r="S11" t="n">
-        <v>6.1</v>
+        <v>15.8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1410,47 +1410,47 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>60.6</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cariari Pococi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Pitbulls Santa Barbara FC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="R12" t="n">
-        <v>60.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>16.1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>60.2</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1510,31 +1510,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Naft</t>
+          <t>Kufstein</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Qasim</t>
+          <t>Schwaz</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="G13" t="n">
-        <v>14.75</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1555,40 +1555,40 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>60.7</v>
       </c>
       <c r="S13" t="n">
-        <v>22.2</v>
+        <v>16.1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>60</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="14">
@@ -1599,31 +1599,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CSKA Sofia II</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="F14" t="n">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1663,13 +1663,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R14" t="n">
-        <v>57.4</v>
+        <v>60.7</v>
       </c>
       <c r="S14" t="n">
-        <v>11.1</v>
+        <v>16.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>57.4</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="15">
@@ -1688,41 +1688,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Blackburn Rovers U21</t>
+          <t>Brechin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Reading U21</t>
+          <t>Formartine United</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="G15" t="n">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1733,85 +1733,85 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="R15" t="n">
-        <v>54.3</v>
+        <v>60.6</v>
       </c>
       <c r="S15" t="n">
-        <v>12.8</v>
+        <v>6.1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>54.3</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Italy U21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chelmsford City</t>
+          <t>North Macedonia U21</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="F16" t="n">
-        <v>3.52</v>
+        <v>10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>28</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>5:0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1822,85 +1822,85 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="S16" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>54.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Flota Świnoujście</t>
+          <t>Luxembourg U21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Noteć Czarnków</t>
+          <t>France U21</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>16.5</v>
       </c>
       <c r="F17" t="n">
-        <v>3.52</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1911,75 +1911,75 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>52.7</v>
+        <v>58.6</v>
       </c>
       <c r="S17" t="n">
-        <v>23.2</v>
+        <v>17.2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>52.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ghivizzano Borgo Mozzano</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sansepolcro</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.46</v>
+        <v>3.52</v>
       </c>
       <c r="F18" t="n">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="G18" t="n">
-        <v>6.45</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2000,80 +2000,80 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="R18" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
       <c r="S18" t="n">
-        <v>26.1</v>
+        <v>12.7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>52.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Hércules</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Águila</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.65</v>
+        <v>6.4</v>
       </c>
       <c r="F19" t="n">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2099,22 +2099,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>51.8</v>
+        <v>55.3</v>
       </c>
       <c r="S19" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>51.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="20">
@@ -2133,41 +2133,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Al Minaa Basra</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Duhok</t>
+          <t>Chelmsford City</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="F20" t="n">
-        <v>3.04</v>
+        <v>3.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.57</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2178,40 +2178,40 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="R20" t="n">
-        <v>51.7</v>
+        <v>53.7</v>
       </c>
       <c r="S20" t="n">
-        <v>34.5</v>
+        <v>12.6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>51.7</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="21">
@@ -2222,31 +2222,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AD Carmelita</t>
+          <t>Blackburn Rovers U21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Futbol Consultants Moravia</t>
+          <t>Reading U21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="F21" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2267,80 +2267,80 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="R21" t="n">
-        <v>51.3</v>
+        <v>53.7</v>
       </c>
       <c r="S21" t="n">
-        <v>24</v>
+        <v>12.6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>51.3</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atletico el Vigia FC</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fundación Lara Deportiva</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.45</v>
+        <v>5.6</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="G22" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="Q22" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R22" t="n">
-        <v>51.1</v>
+        <v>53.7</v>
       </c>
       <c r="S22" t="n">
-        <v>24.4</v>
+        <v>12.6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>51.1</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="23">
@@ -2400,27 +2400,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlético Choloma</t>
+          <t>Al Minaa Basra</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Génesis</t>
+          <t>Duhok</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="F23" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="G23" t="n">
-        <v>3.16</v>
+        <v>2.57</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2460,17 +2460,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="S23" t="n">
-        <v>17.8</v>
+        <v>34.5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="24">
@@ -2489,31 +2489,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lentigione</t>
+          <t>Atletico el Vigia FC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pistoiese</t>
+          <t>Fundación Lara Deportiva</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.61</v>
+        <v>4.45</v>
       </c>
       <c r="F24" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.61</v>
+        <v>1.66</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2544,22 +2544,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="R24" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="S24" t="n">
-        <v>19.7</v>
+        <v>24.4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2567,47 +2567,47 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kırıkkale Büyük Anadolu</t>
+          <t>Masar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Niğde Belediyesispor</t>
+          <t>Baladiyyat Al Mehalla</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="F25" t="n">
-        <v>3.18</v>
+        <v>2.58</v>
       </c>
       <c r="G25" t="n">
-        <v>2.51</v>
+        <v>4.15</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="R25" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="S25" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -2667,41 +2667,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warta Sieradz</t>
+          <t>AD Carmelita</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Olimpia Elbląg</t>
+          <t>Futbol Consultants Moravia</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="F26" t="n">
-        <v>3.78</v>
+        <v>3.32</v>
       </c>
       <c r="G26" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2722,22 +2722,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="R26" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S26" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -2756,41 +2756,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenville Triumph</t>
+          <t>Kırıkkale Büyük Anadolu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NY Cosmos</t>
+          <t>Niğde Belediyesispor</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="G27" t="n">
-        <v>5.5</v>
+        <v>2.51</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2811,22 +2811,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q27" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="R27" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="S27" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2834,55 +2834,60 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bogota FC</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="F28" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>5.75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2900,22 +2905,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="R28" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="S28" t="n">
-        <v>20.7</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2923,42 +2928,42 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.38</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>3.32</v>
+        <v>4.15</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2968,7 +2973,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2989,22 +2994,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
         <v>50</v>
       </c>
-      <c r="R29" t="n">
-        <v>48</v>
-      </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3012,7 +3017,7 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -3023,27 +3028,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Warta Sieradz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Água Santa</t>
+          <t>Olimpia Elbląg</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="F30" t="n">
-        <v>2.96</v>
+        <v>3.78</v>
       </c>
       <c r="G30" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3057,7 +3062,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3083,17 +3088,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>234</v>
+        <v>139</v>
       </c>
       <c r="R30" t="n">
-        <v>47.9</v>
+        <v>49.6</v>
       </c>
       <c r="S30" t="n">
-        <v>24.4</v>
+        <v>21.6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3101,52 +3106,52 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>47.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Boca Juniors Res.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Estudiantes La Plata Res</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3167,22 +3172,22 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="R31" t="n">
-        <v>44.9</v>
+        <v>49.6</v>
       </c>
       <c r="S31" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3190,38 +3195,38 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>44.9</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XV de Piracicaba</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Votuporanguense</t>
+          <t>Gazelle</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="F32" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="G32" t="n">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3235,7 +3240,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -3261,17 +3266,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="R32" t="n">
-        <v>44</v>
+        <v>48.5</v>
       </c>
       <c r="S32" t="n">
-        <v>31.2</v>
+        <v>24.3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3279,7 +3284,7 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>44</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="33">
@@ -3290,27 +3295,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Çorluspor 1947</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bursa Yıldırımspor</t>
+          <t>Água Santa</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.64</v>
+        <v>2.29</v>
       </c>
       <c r="F33" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="G33" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3324,7 +3329,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -3350,17 +3355,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="R33" t="n">
-        <v>44</v>
+        <v>48.5</v>
       </c>
       <c r="S33" t="n">
-        <v>31.2</v>
+        <v>24.3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3368,7 +3373,7 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>44</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="34">
@@ -3379,31 +3384,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Yeovil Town</t>
+          <t>Bogota FC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="F34" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="G34" t="n">
-        <v>3.78</v>
+        <v>7.4</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3413,7 +3418,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -3434,22 +3439,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="R34" t="n">
-        <v>44</v>
+        <v>48.3</v>
       </c>
       <c r="S34" t="n">
-        <v>31.2</v>
+        <v>20.7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3457,7 +3462,7 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>44</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="35">
@@ -3468,41 +3473,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kasetsart FC</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="F35" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="G35" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3523,22 +3528,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="R35" t="n">
-        <v>43.4</v>
+        <v>48</v>
       </c>
       <c r="S35" t="n">
-        <v>30.3</v>
+        <v>16</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3546,42 +3551,42 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>43.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pikine</t>
+          <t>Godoy Cruz Res.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Teungueth</t>
+          <t>San Lorenzo Res.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="F36" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="G36" t="n">
-        <v>2.88</v>
+        <v>2.21</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3591,7 +3596,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3612,22 +3617,22 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="R36" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="S36" t="n">
-        <v>28.6</v>
+        <v>15.6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3635,7 +3640,7 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="37">
@@ -3646,41 +3651,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AJEL</t>
+          <t>Çorluspor 1947</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AS Camberene</t>
+          <t>Bursa Yıldırımspor</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="F37" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="G37" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -3701,22 +3706,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="R37" t="n">
-        <v>42.3</v>
+        <v>44</v>
       </c>
       <c r="S37" t="n">
-        <v>22.3</v>
+        <v>32</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3724,7 +3729,7 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>42.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3740,36 +3745,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Yeovil Town</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="F38" t="n">
-        <v>3.74</v>
+        <v>3.44</v>
       </c>
       <c r="G38" t="n">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3790,22 +3795,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="R38" t="n">
-        <v>42.3</v>
+        <v>44</v>
       </c>
       <c r="S38" t="n">
-        <v>22.3</v>
+        <v>32</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3813,52 +3818,52 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>42.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rajasthan United</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Diamond Harbour</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="F39" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="G39" t="n">
-        <v>4.35</v>
+        <v>2.92</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -3879,30 +3884,30 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="R39" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
       <c r="S39" t="n">
-        <v>22.3</v>
+        <v>37.1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="40">
@@ -3913,41 +3918,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AJEL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AS Camberene</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.67</v>
+        <v>1.47</v>
       </c>
       <c r="F40" t="n">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3968,30 +3973,30 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="R40" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>22.3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="41">
@@ -4007,26 +4012,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Itapipoca</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Uniclinic Atletico Clube</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="F41" t="n">
-        <v>3.64</v>
+        <v>2.99</v>
       </c>
       <c r="G41" t="n">
-        <v>7.8</v>
+        <v>4.35</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4057,7 +4062,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4066,13 +4071,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>221</v>
+        <v>130</v>
       </c>
       <c r="R41" t="n">
-        <v>36.7</v>
+        <v>42.3</v>
       </c>
       <c r="S41" t="n">
-        <v>34.8</v>
+        <v>22.3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4080,7 +4085,7 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>36.7</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="42">
@@ -4091,31 +4096,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Real Kashmir</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Namdhari</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="F42" t="n">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="G42" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4146,7 +4151,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4155,13 +4160,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>221</v>
+        <v>130</v>
       </c>
       <c r="R42" t="n">
-        <v>36.7</v>
+        <v>42.3</v>
       </c>
       <c r="S42" t="n">
-        <v>34.8</v>
+        <v>22.3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4169,7 +4174,7 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>36.7</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="43">
@@ -4180,36 +4185,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentinos Juniors Res.</t>
+          <t>Pikine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Instituto Res.</t>
+          <t>Teungueth</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.88</v>
+        <v>2.88</v>
       </c>
       <c r="F43" t="n">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="G43" t="n">
-        <v>3.94</v>
+        <v>2.88</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4225,17 +4230,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4244,61 +4249,61 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>221</v>
+        <v>51</v>
       </c>
       <c r="R43" t="n">
-        <v>36.7</v>
+        <v>41.2</v>
       </c>
       <c r="S43" t="n">
-        <v>34.8</v>
+        <v>27.5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>36.7</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sevlievo</t>
+          <t>Porto Velho</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sportist Svoge</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.71</v>
+        <v>2.89</v>
       </c>
       <c r="F44" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="G44" t="n">
-        <v>4.6</v>
+        <v>2.17</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4314,17 +4319,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4333,61 +4338,61 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>221</v>
+        <v>51</v>
       </c>
       <c r="R44" t="n">
-        <v>36.7</v>
+        <v>41.2</v>
       </c>
       <c r="S44" t="n">
-        <v>34.8</v>
+        <v>27.5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>36.7</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Juventud</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.8</v>
+        <v>3.56</v>
       </c>
       <c r="F45" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="G45" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4422,13 +4427,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="R45" t="n">
-        <v>36.1</v>
+        <v>41.2</v>
       </c>
       <c r="S45" t="n">
-        <v>30.1</v>
+        <v>27.5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4436,52 +4441,52 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>36.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="F46" t="n">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="G46" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1:4</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -4502,30 +4507,30 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="R46" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
       <c r="S46" t="n">
-        <v>57.1</v>
+        <v>21.1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="47">
@@ -4536,36 +4541,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manchester United W</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bayern Munich W</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="F47" t="n">
-        <v>3.52</v>
+        <v>2.56</v>
       </c>
       <c r="G47" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4581,17 +4586,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4600,13 +4605,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>35.6</v>
+        <v>40</v>
       </c>
       <c r="S47" t="n">
-        <v>35.6</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4614,52 +4619,52 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>35.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Maleyet Kafr El Zayiat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.61</v>
+        <v>3.36</v>
       </c>
       <c r="F48" t="n">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="G48" t="n">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -4680,22 +4685,22 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="R48" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="S48" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4703,7 +4708,7 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="49">
@@ -4714,27 +4719,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SKRA Częstochowa</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Miedź Legnica II</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="F49" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4748,7 +4753,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -4759,12 +4764,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4774,70 +4779,70 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R49" t="n">
-        <v>32.8</v>
+        <v>37.3</v>
       </c>
       <c r="S49" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>37.3</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U49" t="n">
-        <v>32.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Altınordu</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kastamonuspor 1966</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="F50" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="G50" t="n">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -4858,22 +4863,22 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="R50" t="n">
-        <v>31.3</v>
+        <v>36.6</v>
       </c>
       <c r="S50" t="n">
-        <v>25.4</v>
+        <v>34.4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4881,42 +4886,42 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>31.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Aswan Sc</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Tanta SC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="F51" t="n">
-        <v>3.38</v>
+        <v>2.58</v>
       </c>
       <c r="G51" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4926,7 +4931,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4937,40 +4942,40 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="R51" t="n">
-        <v>30</v>
+        <v>36.6</v>
       </c>
       <c r="S51" t="n">
-        <v>30</v>
+        <v>34.4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>30</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="52">
@@ -4981,748 +4986,748 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Argentinos Juniors Res.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Instituto Res.</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="F52" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="G52" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>224</v>
+      </c>
+      <c r="R52" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="S52" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>El Dakhleya</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>El Entag EL Harby</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>224</v>
+      </c>
+      <c r="R53" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="S53" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Manchester United W</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bayern Munich W</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>59</v>
+      </c>
+      <c r="R54" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="S54" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>35.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Truro City</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Solihull Moors</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>24</v>
+      </c>
+      <c r="R55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SKRA Częstochowa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Miedź Legnica II</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>67</v>
+      </c>
+      <c r="R56" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="S56" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Masr</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>El Mokawloon</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>0:1</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>언더</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0 : 0</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>78</v>
+      </c>
+      <c r="R57" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gokulam</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Shillong Lajong</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>58</v>
+      </c>
+      <c r="R58" t="n">
+        <v>31</v>
+      </c>
+      <c r="S58" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bosnia &amp; Herzegovina</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>PRE
 VIEW</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>35</v>
-      </c>
-      <c r="R52" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="S52" t="n">
-        <v>20</v>
-      </c>
-      <c r="T52" t="inlineStr">
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>58</v>
+      </c>
+      <c r="R59" t="n">
+        <v>31</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="U52" t="n">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Batman Petrolspor</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Şanlıurfaspor</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="G53" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>3 : 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>7</v>
-      </c>
-      <c r="R53" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Gucha Stars</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>40</v>
-      </c>
-      <c r="R54" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Club Guarani</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2 de Mayo</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>98</v>
-      </c>
-      <c r="R55" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Sporting San Jose</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Puntarenas FC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>98</v>
-      </c>
-      <c r="R56" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U56" t="n">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Gimnasia La Plata Res.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Racing Club Res.</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>131</v>
-      </c>
-      <c r="R57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="S57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Newroz</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Gharraf</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>1 : 0</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>74</v>
-      </c>
-      <c r="R58" t="n">
-        <v>23</v>
-      </c>
-      <c r="S58" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U58" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ouakam</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>HLM</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="G59" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>170</v>
-      </c>
-      <c r="R59" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="S59" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
       <c r="U59" t="n">
-        <v>22.9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Club Atletico Barinas</t>
+          <t>La Viena FC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Urena SC</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="n">
-        <v>3.24</v>
+        <v>2.36</v>
       </c>
       <c r="G60" t="n">
-        <v>2.57</v>
+        <v>3.48</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5732,7 +5737,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -5753,22 +5758,22 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="R60" t="n">
-        <v>22.9</v>
+        <v>27.8</v>
       </c>
       <c r="S60" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5776,7 +5781,7 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>22.9</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="61">
@@ -5787,41 +5792,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newell's Old Boys Res.</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Belgrano Córdoba Res.</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="F61" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="G61" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -5842,22 +5847,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="R61" t="n">
-        <v>22.1</v>
+        <v>26.8</v>
       </c>
       <c r="S61" t="n">
-        <v>22.1</v>
+        <v>26.1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5865,38 +5870,38 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>22.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="F62" t="n">
-        <v>3.76</v>
+        <v>2.86</v>
       </c>
       <c r="G62" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5910,7 +5915,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5936,17 +5941,17 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="R62" t="n">
-        <v>22.1</v>
+        <v>25</v>
       </c>
       <c r="S62" t="n">
-        <v>22.1</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5954,42 +5959,42 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>22.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sreenidi Deccan</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dempo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="F63" t="n">
-        <v>3.74</v>
+        <v>3.02</v>
       </c>
       <c r="G63" t="n">
-        <v>4.45</v>
+        <v>2.98</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5999,7 +6004,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -6020,22 +6025,22 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="R63" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="S63" t="n">
-        <v>14.3</v>
+        <v>24.4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6043,52 +6048,52 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Municipal Grecia</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>AD Cofutpa</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.25</v>
+        <v>1.69</v>
       </c>
       <c r="F64" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="G64" t="n">
-        <v>1.91</v>
+        <v>3.98</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -6099,40 +6104,40 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R64" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
       <c r="S64" t="n">
-        <v>21.6</v>
+        <v>25.3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>20.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="65">
@@ -6143,31 +6148,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aldosivi Res.</t>
+          <t>Club Guarani</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sarmiento Res.</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="F65" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="G65" t="n">
-        <v>2.94</v>
+        <v>3.9</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6177,7 +6182,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -6198,22 +6203,22 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
       <c r="Q65" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="R65" t="n">
-        <v>20.4</v>
+        <v>24.2</v>
       </c>
       <c r="S65" t="n">
-        <v>34.7</v>
+        <v>25.3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6221,7 +6226,7 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>20.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="66">
@@ -6232,31 +6237,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Gimnasia La Plata Res.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Wanderers</t>
+          <t>Racing Club Res.</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="F66" t="n">
-        <v>2.76</v>
+        <v>3.02</v>
       </c>
       <c r="G66" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6287,7 +6292,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6296,13 +6301,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="R66" t="n">
-        <v>19.6</v>
+        <v>23.5</v>
       </c>
       <c r="S66" t="n">
-        <v>29</v>
+        <v>23.5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6310,7 +6315,7 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>19.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="67">
@@ -6321,31 +6326,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spartak Pleven</t>
+          <t>Club Atletico Barinas</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Belasitsa</t>
+          <t>Urena SC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.76</v>
+        <v>2.41</v>
       </c>
       <c r="F67" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="G67" t="n">
-        <v>4.3</v>
+        <v>2.57</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6376,7 +6381,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6385,13 +6390,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="R67" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
       <c r="S67" t="n">
-        <v>29</v>
+        <v>22.1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6399,7 +6404,7 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="68">
@@ -6410,31 +6415,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yaracuyanos FC</t>
+          <t>Ouakam</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Zamora FC B</t>
+          <t>HLM</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.46</v>
+        <v>2.22</v>
       </c>
       <c r="F68" t="n">
-        <v>3.8</v>
+        <v>2.41</v>
       </c>
       <c r="G68" t="n">
-        <v>6.05</v>
+        <v>4.05</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6444,7 +6449,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -6465,22 +6470,22 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Q68" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="R68" t="n">
-        <v>17.6</v>
+        <v>22.7</v>
       </c>
       <c r="S68" t="n">
-        <v>17.6</v>
+        <v>22.1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6488,52 +6493,52 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>17.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pazarspor</t>
+          <t>Sousa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tokat Bld Plevnespor</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="F69" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -6554,22 +6559,22 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="R69" t="n">
-        <v>17.5</v>
+        <v>22.7</v>
       </c>
       <c r="S69" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6577,42 +6582,42 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>17.5</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 25 March 2026</t>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>America de Cali</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="F70" t="n">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="G70" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6620,12 +6625,12 @@
           <t>언더</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>미결</t>
@@ -6643,20 +6648,30 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>172</v>
+      </c>
+      <c r="R70" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S70" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="71">
@@ -6667,41 +6682,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Muaither SC</t>
+          <t>Newell's Old Boys Res.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Al-Markhiya</t>
+          <t>Belgrano Córdoba Res.</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -6712,34 +6727,40 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>68</v>
+      </c>
+      <c r="R71" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="72">
@@ -6750,31 +6771,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>11.25</v>
+        <v>3.25</v>
       </c>
       <c r="F72" t="n">
-        <v>6.7</v>
+        <v>3.58</v>
       </c>
       <c r="G72" t="n">
-        <v>1.15</v>
+        <v>1.91</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6784,7 +6805,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0 : 4</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -6805,29 +6826,1896 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>102</v>
+      </c>
+      <c r="R72" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S72" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Santa Cruz FC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AD Sarchí</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>50</v>
+      </c>
+      <c r="R73" t="n">
+        <v>20</v>
+      </c>
+      <c r="S73" t="n">
+        <v>34</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>20</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Aldosivi Res.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sarmiento Res.</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>50</v>
+      </c>
+      <c r="R75" t="n">
+        <v>20</v>
+      </c>
+      <c r="S75" t="n">
+        <v>34</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wanderers</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>108</v>
+      </c>
+      <c r="R76" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S76" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ind. Juniors</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Cumbayá</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Yaracuyanos FC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Zamora FC B</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>166</v>
+      </c>
+      <c r="R78" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S78" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Proxy</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Asyut Petrol</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>69</v>
+      </c>
+      <c r="R79" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>81</v>
+      </c>
+      <c r="R80" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S80" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>18</v>
+      </c>
+      <c r="R81" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S81" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ferro 2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Central Córdoba SdE Res.</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>69</v>
+      </c>
+      <c r="R82" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Famalicão U23</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sporting CP U23</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>120</v>
+      </c>
+      <c r="R83" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S83" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>120</v>
+      </c>
+      <c r="R84" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S84" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Chapecoense-sc</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>38</v>
+      </c>
+      <c r="R85" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Galvez</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>17</v>
+      </c>
+      <c r="R86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="S86" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Unisport Bafang</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Cotonsport</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>26</v>
+      </c>
+      <c r="R87" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S87" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Seychelles</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lesotho</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
           <t>04</t>
         </is>
       </c>
-      <c r="Q72" t="n">
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
         <v>1</v>
       </c>
-      <c r="R72" t="n">
+      <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="n">
+      <c r="S88" t="n">
         <v>0</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>원정승</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 25 March 2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Muaither SC</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Al-Markhiya</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>San Marino U21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Finland U21</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0 : 5</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tigres UANL W</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>América W</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>3 : 1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>3</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Rep. Of Ireland</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 26 March 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>FYR Macedonia</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>4 : 1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>5</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>80</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,46 +526,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Palmeiras W</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Flamengo W</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>6.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,22 +586,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>77.5</v>
+        <v>72</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>77.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,26 +625,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Portugal U21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Scotland U21</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>6.45</v>
       </c>
       <c r="G3" t="n">
-        <v>4.85</v>
+        <v>15.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>4 : 0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -675,22 +675,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -698,52 +698,52 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ironi Modi'in</t>
+          <t>Switzerland U20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Romania U20</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.48</v>
+        <v>1.95</v>
       </c>
       <c r="F4" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>3.28</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>4 : 0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -754,85 +754,85 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>55.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>55.9</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Slovenia U21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Spanish Town Police</t>
+          <t>Norway U21</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.26</v>
+        <v>4.05</v>
       </c>
       <c r="F5" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -843,85 +843,85 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>52.7</v>
+        <v>70</v>
       </c>
       <c r="S5" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>52.7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.67</v>
+        <v>3.88</v>
       </c>
       <c r="F6" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>1.82</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -932,75 +932,75 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="R6" t="n">
-        <v>48.3</v>
+        <v>69</v>
       </c>
       <c r="S6" t="n">
-        <v>22.5</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>48.3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AS Camberene</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wally Daan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.24</v>
+        <v>1.52</v>
       </c>
       <c r="F7" t="n">
-        <v>2.57</v>
+        <v>4.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2.41</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>2 : 2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1021,85 +1021,85 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
-        <v>46.9</v>
+        <v>68.2</v>
       </c>
       <c r="S7" t="n">
-        <v>18.4</v>
+        <v>9.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>46.9</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tijuana W</t>
+          <t>Georgia U21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Guadalajara W</t>
+          <t>Malta U21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.48</v>
+        <v>1.12</v>
       </c>
       <c r="F8" t="n">
-        <v>3.52</v>
+        <v>7.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>19</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>5:0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1110,75 +1110,75 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="R8" t="n">
-        <v>45.7</v>
+        <v>68</v>
       </c>
       <c r="S8" t="n">
-        <v>21.7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>45.7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Melbourne Victory II</t>
+          <t>Greece U21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Langwarrin</t>
+          <t>Germany U21</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="n">
-        <v>3.96</v>
+        <v>4.35</v>
       </c>
       <c r="G9" t="n">
-        <v>3.18</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1199,75 +1199,75 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="S9" t="n">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Centro Español</t>
+          <t>AFC Fylde</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="F10" t="n">
-        <v>2.83</v>
+        <v>5.95</v>
       </c>
       <c r="G10" t="n">
-        <v>2.65</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1298,65 +1298,65 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="R10" t="n">
-        <v>43.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>35.1</v>
+        <v>19.5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>43.2</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>South Melbourne</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Dandenong City</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="F11" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1387,65 +1387,65 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="R11" t="n">
-        <v>43.2</v>
+        <v>63.5</v>
       </c>
       <c r="S11" t="n">
-        <v>35.1</v>
+        <v>16.7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>43.2</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hamburger SV W</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen W</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.05</v>
+        <v>1.13</v>
       </c>
       <c r="F12" t="n">
-        <v>4.05</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>16</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1466,75 +1466,75 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>42.4</v>
+        <v>62.5</v>
       </c>
       <c r="S12" t="n">
-        <v>29.3</v>
+        <v>15.6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>42.4</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Spain U21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>Kosovo U21</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="F13" t="n">
-        <v>4.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>6.55</v>
+        <v>18.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1565,22 +1565,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1588,42 +1588,42 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>England U21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Moldova U21</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="F14" t="n">
-        <v>2.94</v>
+        <v>13.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.34</v>
+        <v>51</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1644,85 +1644,85 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="R14" t="n">
-        <v>37.3</v>
+        <v>62.5</v>
       </c>
       <c r="S14" t="n">
-        <v>25.4</v>
+        <v>18.8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>37.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Bulgaria U21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ska-khabarovsk</t>
+          <t>Azerbaijan U21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>4 : 0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>36.6</v>
+        <v>62.5</v>
       </c>
       <c r="S15" t="n">
-        <v>33.2</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1766,52 +1766,52 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>36.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Club Sp. San Lorenzo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="F16" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1832,22 +1832,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="R16" t="n">
-        <v>30.8</v>
+        <v>59.7</v>
       </c>
       <c r="S16" t="n">
-        <v>23.1</v>
+        <v>14.5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1855,38 +1855,38 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>30.8</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Futbol Consultants Moravia</t>
+          <t>Platense Res.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Escorpiones Belén</t>
+          <t>Independiente Res.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="F17" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="R17" t="n">
-        <v>29.2</v>
+        <v>59.7</v>
       </c>
       <c r="S17" t="n">
-        <v>20.8</v>
+        <v>14.5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1944,42 +1944,42 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>29.2</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacuipense</t>
+          <t>Al-Qasim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>America-RN</t>
+          <t>Diyala</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.96</v>
+        <v>11.5</v>
       </c>
       <c r="F18" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.29</v>
+        <v>1.27</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2010,22 +2010,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="R18" t="n">
-        <v>28.6</v>
+        <v>59.7</v>
       </c>
       <c r="S18" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2033,52 +2033,52 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>28.6</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunderland U21</t>
+          <t>Kazakhstan U21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reading U21</t>
+          <t>Republic of Ireland U21</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.65</v>
+        <v>4.65</v>
       </c>
       <c r="F19" t="n">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2089,85 +2089,85 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="R19" t="n">
-        <v>25</v>
+        <v>59.2</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>6.1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Independiente Medellin</t>
+          <t>Inter San Carlos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>Municipal Grecia</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="F20" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.58</v>
+        <v>6.15</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2188,22 +2188,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="R20" t="n">
-        <v>24.6</v>
+        <v>58.5</v>
       </c>
       <c r="S20" t="n">
-        <v>24.6</v>
+        <v>18.9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2211,52 +2211,52 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>24.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Defensores De Belgrano</t>
+          <t>Slovenia U19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Atletico DE Rafaela</t>
+          <t>Finland U19</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="F21" t="n">
-        <v>2.59</v>
+        <v>3.36</v>
       </c>
       <c r="G21" t="n">
-        <v>4.33</v>
+        <v>2.41</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2267,85 +2267,85 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="R21" t="n">
-        <v>22.4</v>
+        <v>58.1</v>
       </c>
       <c r="S21" t="n">
-        <v>34.5</v>
+        <v>16.1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>22.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Gharraf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Al Najaf</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="F22" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="G22" t="n">
-        <v>5.15</v>
+        <v>4.25</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>20.7</v>
+        <v>58</v>
       </c>
       <c r="S22" t="n">
-        <v>17.2</v>
+        <v>24</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2389,52 +2389,52 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>20.7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="F23" t="n">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>4.05</v>
+        <v>7.9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2455,22 +2455,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="R23" t="n">
-        <v>20</v>
+        <v>57.9</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>22.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2478,42 +2478,42 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gorée</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sonacos</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="F24" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8</v>
+        <v>1.94</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2534,75 +2534,75 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q24" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="R24" t="n">
-        <v>17.6</v>
+        <v>57.9</v>
       </c>
       <c r="S24" t="n">
-        <v>21.2</v>
+        <v>10.5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U24" t="n">
-        <v>17.6</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="G25" t="n">
-        <v>3.82</v>
+        <v>4.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2633,22 +2633,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="R25" t="n">
-        <v>16.9</v>
+        <v>53.8</v>
       </c>
       <c r="S25" t="n">
-        <v>16.9</v>
+        <v>17.9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2656,38 +2656,38 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>16.9</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deportivo Muñiz</t>
+          <t>Croatia U21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Canuelas</t>
+          <t>Turkey U21</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.86</v>
+        <v>1.88</v>
       </c>
       <c r="F26" t="n">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="G26" t="n">
-        <v>2.51</v>
+        <v>3.74</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2727,73 +2727,73 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="R26" t="n">
-        <v>16.7</v>
+        <v>52.8</v>
       </c>
       <c r="S26" t="n">
-        <v>44.4</v>
+        <v>23.6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>16.7</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>León W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Toluca W</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="F27" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2811,65 +2811,75 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>27</v>
+      </c>
+      <c r="R27" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="S27" t="n">
+        <v>11.1</v>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 30 March 2026</t>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Independiente Riva. Res.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>U. Catolica</t>
+          <t>Defensa y Justicia Res.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.62</v>
+        <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2890,29 +2900,6257 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>27</v>
+      </c>
+      <c r="R28" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Universidad O&amp;M</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Salcedo</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>59</v>
+      </c>
+      <c r="R29" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>59</v>
+      </c>
+      <c r="R30" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="S30" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Maidenhead</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bath City</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>166</v>
+      </c>
+      <c r="R31" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="S31" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Eswatini</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Eritrea</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>166</v>
+      </c>
+      <c r="R32" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bosnia &amp; Herzegovina</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>10</v>
+      </c>
+      <c r="R33" t="n">
+        <v>50</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Denmark U21</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wales U21</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" t="n">
+        <v>50</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Montenegro U21</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Poland U21</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>22</v>
+      </c>
+      <c r="R35" t="n">
+        <v>50</v>
+      </c>
+      <c r="S35" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Yeovil Town</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>150</v>
+      </c>
+      <c r="R36" t="n">
+        <v>48</v>
+      </c>
+      <c r="S36" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>249</v>
+      </c>
+      <c r="R37" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Somalia</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>249</v>
+      </c>
+      <c r="R38" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Newroz</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Naft Maysan</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>249</v>
+      </c>
+      <c r="R39" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>91</v>
+      </c>
+      <c r="R40" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>22</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Burundi</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>91</v>
+      </c>
+      <c r="R41" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>22</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>51</v>
+      </c>
+      <c r="R42" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>India U23</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Tajikistan U23</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>52</v>
+      </c>
+      <c r="R43" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hanwell Town</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sholing</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>46</v>
+      </c>
+      <c r="R44" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2 de Mayo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Nacional Asuncion</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0 : 2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>78</v>
+      </c>
+      <c r="R45" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="S45" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Alfreton Town</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Chorley</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0 : 2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>78</v>
+      </c>
+      <c r="R46" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="S46" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0 : 2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>47</v>
+      </c>
+      <c r="R47" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="S47" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Gokulam</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Aizawl</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0 : 2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>38</v>
+      </c>
+      <c r="R48" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="S48" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hungary U19</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Slovakia U19</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>74</v>
+      </c>
+      <c r="R49" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="S49" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>74</v>
+      </c>
+      <c r="R50" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra Res.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys Res.</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R51" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Turkmenistan</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2 : 3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q52" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="S52" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tiverton Town</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Evesham United</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>60</v>
+      </c>
+      <c r="R53" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="S53" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>38.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>240</v>
+      </c>
+      <c r="R54" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="S54" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Denmark U19</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Czech Republic U19</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>51</v>
+      </c>
+      <c r="R55" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>64</v>
+      </c>
+      <c r="R56" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="S56" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Austria U21</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Belarus U21</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>6</v>
+      </c>
+      <c r="R57" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Armenia U21</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>North Macedonia U21</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>87</v>
+      </c>
+      <c r="R58" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S58" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sweden U21</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Italy U21</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0 : 3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>21</v>
+      </c>
+      <c r="R59" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S59" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0 : 3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S60" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Spennymoor Town</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>87</v>
+      </c>
+      <c r="R61" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S61" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>87</v>
+      </c>
+      <c r="R62" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>64</v>
+      </c>
+      <c r="R63" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Belgrano Córdoba Res.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lanús Res.</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>26</v>
+      </c>
+      <c r="R64" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="S64" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3 : 0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q65" t="n">
+        <v>20</v>
+      </c>
+      <c r="R65" t="n">
+        <v>30</v>
+      </c>
+      <c r="S65" t="n">
+        <v>30</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Internacional Palmira</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>64</v>
+      </c>
+      <c r="R66" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Latvia U21</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Northern Ireland U21</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>64</v>
+      </c>
+      <c r="R67" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hereford</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Macclesfield</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>90</v>
+      </c>
+      <c r="R68" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="S68" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Enfield Town</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Chesham United</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>90</v>
+      </c>
+      <c r="R69" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="S69" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2 : 3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>15</v>
+      </c>
+      <c r="R70" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="S70" t="n">
+        <v>20</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Israel U21</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Bosnia-Herzegovina U21</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>38</v>
+      </c>
+      <c r="R71" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="S71" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>151</v>
+      </c>
+      <c r="R72" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G73" t="n">
+        <v>22</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>12</v>
+      </c>
+      <c r="R73" t="n">
+        <v>25</v>
+      </c>
+      <c r="S73" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Weston-super-Mare</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead Town</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1 : 2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>52</v>
+      </c>
+      <c r="R74" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bhutan</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Brunei</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>14</v>
+      </c>
+      <c r="R75" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S75" t="n">
+        <v>50</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>무승부/역배</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ferroviaria W</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Cruzeiro W</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>118</v>
+      </c>
+      <c r="R76" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tigres FC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>118</v>
+      </c>
+      <c r="R77" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Águia de Marabá</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>40</v>
+      </c>
+      <c r="R78" t="n">
+        <v>20</v>
+      </c>
+      <c r="S78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>54</v>
+      </c>
+      <c r="R79" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="S79" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>86</v>
+      </c>
+      <c r="R80" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hartlepool</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>23</v>
+      </c>
+      <c r="R81" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S81" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruna</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>179</v>
+      </c>
+      <c r="R82" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S82" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hungary U21</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ukraine U21</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>19</v>
+      </c>
+      <c r="R83" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>72</v>
+      </c>
+      <c r="R84" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Comoros</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>31</v>
+      </c>
+      <c r="R85" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="S85" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Laos</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>58</v>
+      </c>
+      <c r="R86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0 : 4</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Austria U19</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Germany U19</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
         <v>3</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S89" t="n">
         <v>0</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>원정승</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Switzerland U21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Estonia U21</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>26</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Switzerland U19</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Norway U19</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Finland U21</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Cyprus U21</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G92" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>5 : 0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Romania U21</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>San Marino U21</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Latvia U19</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Belgium U19</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Portugal U19</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>England U19</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Romania U19</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ukraine U19</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G97" t="n">
+        <v>43</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>5 : 0</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Betting Tips - Tuesday, 31 March 2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Czech Republic U21</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Gibraltar U21</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>0 : 4</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U93"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,36 +526,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="F2" t="n">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.45</v>
+        <v>10.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,22 +586,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>77.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,38 +609,38 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>77.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="F3" t="n">
-        <v>5.05</v>
+        <v>4.45</v>
       </c>
       <c r="G3" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -680,17 +680,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>75.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -698,42 +698,42 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>75.59999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Radnicki NIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.85</v>
+        <v>1.3</v>
       </c>
       <c r="F4" t="n">
-        <v>3.58</v>
+        <v>4.55</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -754,75 +754,75 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>74.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="S4" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>74.09999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>HNK Gorica</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.65</v>
+        <v>7.4</v>
       </c>
       <c r="F5" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -853,22 +853,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>27</v>
       </c>
       <c r="R5" t="n">
-        <v>74.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -876,42 +876,42 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>74.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.65</v>
+        <v>1.29</v>
       </c>
       <c r="F6" t="n">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -932,85 +932,85 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>74.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="S6" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>74.09999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Independ. Rivadavia</t>
+          <t>Stirling University</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Caledonian Braves</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.44</v>
+        <v>4.15</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1021,75 +1021,75 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>68.7</v>
+        <v>66.7</v>
       </c>
       <c r="S7" t="n">
-        <v>16.9</v>
+        <v>66.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>68.7</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Johor Darul Takzim FC</t>
+          <t>Tekstilshchik</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur FA</t>
+          <t>Torpedo Miass</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="F8" t="n">
-        <v>6.7</v>
+        <v>3.32</v>
       </c>
       <c r="G8" t="n">
-        <v>13.5</v>
+        <v>7.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1120,22 +1120,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="R8" t="n">
-        <v>66.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>14.3</v>
+        <v>17.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1143,38 +1143,38 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>66.7</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cliftonville FC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1191,7 +1191,12 @@
           <t>1 : 2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>미결</t>
@@ -1218,13 +1223,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>64.7</v>
+        <v>62.9</v>
       </c>
       <c r="S9" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1232,42 +1237,42 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>64.7</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Volgar Astrakhan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>3.58</v>
       </c>
       <c r="F10" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1277,7 +1282,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1298,22 +1303,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>64.3</v>
+        <v>62.5</v>
       </c>
       <c r="S10" t="n">
-        <v>7.1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1321,42 +1326,42 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>64.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Juticalpa</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>5.65</v>
+        <v>5.05</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>1.28</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1366,7 +1371,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1377,75 +1382,75 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="R11" t="n">
-        <v>63.3</v>
+        <v>61.1</v>
       </c>
       <c r="S11" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>63.3</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La Fiorita</t>
+          <t>Al Diriyah</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>San Giovanni</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="F12" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1455,7 +1460,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1476,22 +1481,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>62.3</v>
+        <v>60</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1499,13 +1504,13 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>62.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1515,26 +1520,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.68</v>
+        <v>9.5</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.96</v>
+        <v>1.21</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>0 : 3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1555,75 +1560,75 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>61.5</v>
+        <v>57.6</v>
       </c>
       <c r="S13" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>61.5</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WDSC Wolves</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gold Coast United</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.61</v>
+        <v>5.05</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1633,7 +1638,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1644,85 +1649,85 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R14" t="n">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>60</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Magic United</t>
+          <t>Holywell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Moreton City Excelsior</t>
+          <t>Newtown AFC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.4</v>
+        <v>1.48</v>
       </c>
       <c r="F15" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.33</v>
+        <v>5.05</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>3 : 2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1733,85 +1738,85 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="R15" t="n">
-        <v>58.8</v>
+        <v>53.6</v>
       </c>
       <c r="S15" t="n">
-        <v>17.6</v>
+        <v>7.1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>58.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leicesterfield</t>
+          <t>Rio Ave U23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hungry Lions</t>
+          <t>Marítimo U23</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.89</v>
+        <v>1.69</v>
       </c>
       <c r="F16" t="n">
-        <v>2.68</v>
+        <v>3.72</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>3.96</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1822,75 +1827,75 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="R16" t="n">
-        <v>57.6</v>
+        <v>52.3</v>
       </c>
       <c r="S16" t="n">
-        <v>10.2</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>57.6</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>BG Pathum United</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.11</v>
+        <v>1.42</v>
       </c>
       <c r="F17" t="n">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1921,7 +1926,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1930,13 +1935,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="R17" t="n">
-        <v>56.4</v>
+        <v>52.3</v>
       </c>
       <c r="S17" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1944,55 +1949,60 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>56.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Albion Rovers</t>
+          <t>SC Braga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>East Stirlingshire</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="F18" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="G18" t="n">
-        <v>4.85</v>
+        <v>2.86</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3 : 1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2010,22 +2020,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4</v>
+        <v>52.3</v>
       </c>
       <c r="S18" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2033,42 +2043,42 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>56.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spokane Velocity</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HNK Hajduk Split</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="F19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.64</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2078,7 +2088,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2089,75 +2099,75 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="R19" t="n">
-        <v>56</v>
+        <v>51.4</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>56</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>5.85</v>
+        <v>3.16</v>
       </c>
       <c r="G20" t="n">
-        <v>18.5</v>
+        <v>3.38</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2188,7 +2198,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2197,13 +2207,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="R20" t="n">
-        <v>53.8</v>
+        <v>51.4</v>
       </c>
       <c r="S20" t="n">
-        <v>15.4</v>
+        <v>22</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2211,42 +2221,42 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>53.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>LDU de Quito</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="F21" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="G21" t="n">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2256,15 +2266,10 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>PRE
-VIEW</t>
-        </is>
-      </c>
+          <t>3 : 1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2272,75 +2277,75 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="R21" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="S21" t="n">
-        <v>13.8</v>
+        <v>16.8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leixões U23</t>
+          <t>Real Calepina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Torreense U23</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="F22" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2350,7 +2355,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2371,22 +2376,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="R22" t="n">
-        <v>52.7</v>
+        <v>50</v>
       </c>
       <c r="S22" t="n">
-        <v>22.3</v>
+        <v>19.6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2394,38 +2399,38 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>52.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FC Aarau</t>
+          <t>Chornomorets</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Inhulets</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="G23" t="n">
-        <v>5.15</v>
+        <v>5.9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2465,17 +2470,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="R23" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
       <c r="S23" t="n">
-        <v>25.3</v>
+        <v>23.9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2483,38 +2488,38 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Mashuk-KMV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vasco DA Gama</t>
+          <t>Irtysh Omsk</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="F24" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2528,7 +2533,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2554,17 +2559,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="R24" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
       <c r="S24" t="n">
-        <v>25.3</v>
+        <v>23.9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2572,38 +2577,38 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hodd</t>
+          <t>Termoli Calcio</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sandnes ULF</t>
+          <t>Sammaurese</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>11.75</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2617,7 +2622,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2643,17 +2648,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="R25" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
       <c r="S25" t="n">
-        <v>25.3</v>
+        <v>23.9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2661,38 +2666,38 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>52.2</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>HNK Rijeka</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>NK Slaven Belupo</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="F26" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="G26" t="n">
-        <v>3.32</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2706,15 +2711,10 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3 : 1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PRE
-VIEW</t>
-        </is>
-      </c>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2737,17 +2737,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="R26" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
       <c r="S26" t="n">
-        <v>17</v>
+        <v>25.8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2771,26 +2771,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FC Saarbrücken</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="F27" t="n">
-        <v>3.66</v>
+        <v>3.38</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2821,22 +2821,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="R27" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
       <c r="S27" t="n">
-        <v>17</v>
+        <v>21.3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2844,52 +2844,52 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SSV Jahn Regensburg</t>
+          <t>Coriano</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>6.55</v>
       </c>
       <c r="F28" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="G28" t="n">
-        <v>3.12</v>
+        <v>1.49</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2900,71 +2900,71 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
-        <v>51.9</v>
+        <v>47.6</v>
       </c>
       <c r="S28" t="n">
-        <v>17</v>
+        <v>28.6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>51.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Slovan Ljubljana</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Ilirija</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.89</v>
+        <v>2.35</v>
       </c>
       <c r="F29" t="n">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="G29" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2978,15 +2978,10 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PRE
-VIEW</t>
-        </is>
-      </c>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2994,12 +2989,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3009,70 +3004,70 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>35</v>
+        <v>283</v>
       </c>
       <c r="R29" t="n">
-        <v>51.4</v>
+        <v>47.3</v>
       </c>
       <c r="S29" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>51.4</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tapatío</t>
+          <t>Al Anwar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tlaxcala</t>
+          <t>Al Wehda Club</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="F30" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3093,22 +3088,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="R30" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
       <c r="S30" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3116,42 +3111,42 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.93</v>
+        <v>2.91</v>
       </c>
       <c r="F31" t="n">
-        <v>3.68</v>
+        <v>3.12</v>
       </c>
       <c r="G31" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3172,17 +3167,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3191,27 +3186,27 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="R31" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
       <c r="S31" t="n">
-        <v>19.7</v>
+        <v>26.7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,22 +3216,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Çorum FK</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="F32" t="n">
-        <v>3.82</v>
+        <v>3.98</v>
       </c>
       <c r="G32" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -3276,17 +3271,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="R32" t="n">
-        <v>51.1</v>
+        <v>46.5</v>
       </c>
       <c r="S32" t="n">
-        <v>19.7</v>
+        <v>27.9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3294,52 +3289,52 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>51.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mixco</t>
+          <t>PWD Bamenda</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Marquense</t>
+          <t>Victoria United</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="F33" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>3.72</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -3360,22 +3355,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="R33" t="n">
-        <v>50.3</v>
+        <v>46.5</v>
       </c>
       <c r="S33" t="n">
-        <v>23.2</v>
+        <v>27.9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3383,52 +3378,52 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>50.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Folgore</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cosmos</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="F34" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="G34" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -3449,22 +3444,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="R34" t="n">
-        <v>50.3</v>
+        <v>46.5</v>
       </c>
       <c r="S34" t="n">
-        <v>23.2</v>
+        <v>27.9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3472,52 +3467,52 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>50.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Krylia Sovetov</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.85</v>
+        <v>1.89</v>
       </c>
       <c r="F35" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="G35" t="n">
-        <v>1.75</v>
+        <v>3.98</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1:4</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -3528,85 +3523,85 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="R35" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="S35" t="n">
-        <v>30</v>
+        <v>22.3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faetano</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Domagnano</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.15</v>
+        <v>1.87</v>
       </c>
       <c r="F36" t="n">
-        <v>4.15</v>
+        <v>2.96</v>
       </c>
       <c r="G36" t="n">
-        <v>1.41</v>
+        <v>4.85</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3617,85 +3612,85 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="R36" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="S36" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dynamo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sabah FA</t>
+          <t>FC Krasnodar</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="F37" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="G37" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -3706,75 +3701,75 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="R37" t="n">
-        <v>50</v>
+        <v>44.1</v>
       </c>
       <c r="S37" t="n">
-        <v>22.2</v>
+        <v>29.7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>50</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>União Leiria U23</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Black Leopards</t>
+          <t>Portimonense U23</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="F38" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2</v>
+        <v>3.24</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3784,7 +3779,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3805,22 +3800,22 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="R38" t="n">
-        <v>48.6</v>
+        <v>43.5</v>
       </c>
       <c r="S38" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3828,38 +3823,38 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>48.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FC WIL 1900</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax FC</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="F39" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3873,7 +3868,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -3899,17 +3894,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="R39" t="n">
-        <v>46.8</v>
+        <v>43.5</v>
       </c>
       <c r="S39" t="n">
-        <v>24.8</v>
+        <v>21.2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3917,52 +3912,52 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>46.8</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rhyl</t>
+          <t>Larisa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Gresford Athletic</t>
+          <t>Panetolikos</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="F40" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="G40" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3983,22 +3978,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="R40" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="S40" t="n">
-        <v>24.7</v>
+        <v>23</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4006,52 +4001,52 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Municipal Grecia</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Quepos Cambute</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="F41" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="G41" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4062,75 +4057,75 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="R41" t="n">
-        <v>45.8</v>
+        <v>41.9</v>
       </c>
       <c r="S41" t="n">
-        <v>24.2</v>
+        <v>37.2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>45.8</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="G42" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4140,7 +4135,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4161,22 +4156,22 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="R42" t="n">
-        <v>45.8</v>
+        <v>41.7</v>
       </c>
       <c r="S42" t="n">
-        <v>16.9</v>
+        <v>29.2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4184,38 +4179,38 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>45.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FC Schweinfurt 05</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Rot-Weiß Essen</t>
+          <t>Al-Raed</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="F43" t="n">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="G43" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4229,7 +4224,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -4255,17 +4250,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="R43" t="n">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
       <c r="S43" t="n">
-        <v>16.9</v>
+        <v>24.7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4273,42 +4268,42 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cailungo</t>
+          <t>Club Queretaro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pennarossa</t>
+          <t>FC Juarez</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="F44" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="G44" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4318,7 +4313,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -4339,22 +4334,22 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="R44" t="n">
-        <v>45.8</v>
+        <v>39.7</v>
       </c>
       <c r="S44" t="n">
-        <v>24.2</v>
+        <v>20.6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4362,42 +4357,42 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>45.8</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Municipal Liberia</t>
+          <t>Milford FC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Casric Stars</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="F45" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="G45" t="n">
-        <v>3.92</v>
+        <v>2.57</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4407,7 +4402,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -4418,71 +4413,71 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="R45" t="n">
-        <v>45.5</v>
+        <v>39.7</v>
       </c>
       <c r="S45" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>45.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Coleraine FC</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="F46" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="G46" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4496,7 +4491,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -4522,17 +4517,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="R46" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
       <c r="S46" t="n">
-        <v>29.4</v>
+        <v>33.1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4540,52 +4535,52 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Juazeirense</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.75</v>
+        <v>1.26</v>
       </c>
       <c r="F47" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="G47" t="n">
-        <v>2.21</v>
+        <v>10.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -4596,75 +4591,75 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>89</v>
+        <v>278</v>
       </c>
       <c r="R47" t="n">
-        <v>44.9</v>
+        <v>37.8</v>
       </c>
       <c r="S47" t="n">
-        <v>29.2</v>
+        <v>33.1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>44.9</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>America-RN</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.73</v>
+        <v>3.18</v>
       </c>
       <c r="F48" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G48" t="n">
-        <v>4.55</v>
+        <v>2.33</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4685,17 +4680,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4704,56 +4699,56 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="R48" t="n">
-        <v>44.4</v>
+        <v>37.1</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>34.3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>44.4</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Marino Academy</t>
+          <t>Dinamo Tirana</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fiorentino</t>
+          <t>Vllaznia Shkodër</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.78</v>
+        <v>2.67</v>
       </c>
       <c r="F49" t="n">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4763,7 +4758,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -4784,22 +4779,22 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="R49" t="n">
-        <v>44.3</v>
+        <v>36.8</v>
       </c>
       <c r="S49" t="n">
-        <v>28.3</v>
+        <v>21.1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4807,42 +4802,42 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>44.3</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>University of Pretoria</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Highbury</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="F50" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="G50" t="n">
-        <v>3.24</v>
+        <v>1.52</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4852,7 +4847,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -4863,75 +4858,75 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q50" t="n">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="R50" t="n">
-        <v>43.4</v>
+        <v>35.7</v>
       </c>
       <c r="S50" t="n">
-        <v>23.3</v>
+        <v>35.7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>43.4</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TSV 1860 München</t>
+          <t>Lerumo Lions</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="F51" t="n">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="G51" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4941,7 +4936,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4962,22 +4957,22 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="R51" t="n">
-        <v>43.4</v>
+        <v>34.7</v>
       </c>
       <c r="S51" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4985,42 +4980,42 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>43.4</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rajasthan United</t>
+          <t>Les Herbiers</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Gokulam</t>
+          <t>Poitiers</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="F52" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="G52" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5030,7 +5025,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -5051,22 +5046,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="R52" t="n">
-        <v>43.4</v>
+        <v>34.7</v>
       </c>
       <c r="S52" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5074,52 +5069,52 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>43.4</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Celtic II</t>
+          <t>Chonburi FC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Linlithgow Rose</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="F53" t="n">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="G53" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -5140,22 +5135,22 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="R53" t="n">
-        <v>42.4</v>
+        <v>34.3</v>
       </c>
       <c r="S53" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5163,42 +5158,42 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>42.4</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Godoy Cruz Res.</t>
+          <t>Formartine United</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Rosario Central Res.</t>
+          <t>Banks O' Dee</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.7</v>
+        <v>2.01</v>
       </c>
       <c r="F54" t="n">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="G54" t="n">
-        <v>1.64</v>
+        <v>2.86</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5208,7 +5203,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -5219,85 +5214,85 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R54" t="n">
-        <v>41.7</v>
+        <v>34.2</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>41.7</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Academico Viseu U23</t>
+          <t>Libertas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Famalicão U23</t>
+          <t>Juvenes / Dogana</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="F55" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="G55" t="n">
-        <v>2.93</v>
+        <v>2.01</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -5308,85 +5303,85 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="R55" t="n">
-        <v>41.4</v>
+        <v>34.1</v>
       </c>
       <c r="S55" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>41.4</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vukovar</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NK Lokomotiva Zagreb</t>
+          <t>Pafos</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="F56" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="G56" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -5407,22 +5402,22 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="R56" t="n">
-        <v>40.3</v>
+        <v>33.9</v>
       </c>
       <c r="S56" t="n">
-        <v>28.4</v>
+        <v>14.3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5430,42 +5425,42 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>40.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Melbourne City</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Spartak Moscow</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="F57" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="G57" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5475,7 +5470,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2 : 2</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -5496,22 +5491,22 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="R57" t="n">
-        <v>39</v>
+        <v>30.2</v>
       </c>
       <c r="S57" t="n">
-        <v>31.7</v>
+        <v>30.2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5519,38 +5514,38 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>39</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ayr Utd</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.18</v>
+        <v>3.76</v>
       </c>
       <c r="F58" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="G58" t="n">
-        <v>2.97</v>
+        <v>2.04</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5564,7 +5559,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -5575,12 +5570,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5590,60 +5585,60 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="R58" t="n">
-        <v>37.7</v>
+        <v>29.8</v>
       </c>
       <c r="S58" t="n">
-        <v>33.3</v>
+        <v>23.4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>37.7</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deportivo Universitario</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1.79</v>
       </c>
       <c r="F59" t="n">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="G59" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5653,7 +5648,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -5674,22 +5669,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>276</v>
+        <v>57</v>
       </c>
       <c r="R59" t="n">
-        <v>37.7</v>
+        <v>28.1</v>
       </c>
       <c r="S59" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5697,42 +5692,42 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>37.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tochigi SC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="F60" t="n">
-        <v>3.64</v>
+        <v>2.8</v>
       </c>
       <c r="G60" t="n">
-        <v>2.34</v>
+        <v>2.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5742,15 +5737,10 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>PRE
-VIEW</t>
-        </is>
-      </c>
+          <t>0 : 2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>미결</t>
@@ -5758,75 +5748,75 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="R60" t="n">
-        <v>36.5</v>
+        <v>28</v>
       </c>
       <c r="S60" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U60" t="n">
-        <v>36.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vizela U23</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Estoril U23</t>
+          <t>Milazzo</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="F61" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="G61" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5836,7 +5826,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -5857,22 +5847,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="R61" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="S61" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5880,52 +5870,52 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Cumbayá</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Gualaceo SC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="F62" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="G62" t="n">
-        <v>2.64</v>
+        <v>3.22</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5946,22 +5936,22 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="R62" t="n">
-        <v>32.4</v>
+        <v>27.7</v>
       </c>
       <c r="S62" t="n">
-        <v>23.5</v>
+        <v>21.8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5969,52 +5959,52 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>32.4</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dempo</t>
+          <t>Zawisza Bydgoszcz</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Shillong Lajong</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.76</v>
+        <v>7.3</v>
       </c>
       <c r="F63" t="n">
-        <v>3.58</v>
+        <v>4.55</v>
       </c>
       <c r="G63" t="n">
-        <v>3.76</v>
+        <v>1.4</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -6025,75 +6015,75 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="R63" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="S63" t="n">
-        <v>23.5</v>
+        <v>54.5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara U23</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Benfica U23</t>
+          <t>9 de Octubre</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2.79</v>
+        <v>1.73</v>
       </c>
       <c r="F64" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="G64" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6114,17 +6104,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6133,56 +6123,56 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="R64" t="n">
-        <v>32.1</v>
+        <v>26</v>
       </c>
       <c r="S64" t="n">
-        <v>21.4</v>
+        <v>27.2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>32.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>SSV Ulm 1846</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="F65" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="G65" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6192,7 +6182,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -6213,22 +6203,22 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="R65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S65" t="n">
-        <v>22</v>
+        <v>27.2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6236,52 +6226,52 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Traiskirchen</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Krems / Rehberg</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="F66" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="G66" t="n">
-        <v>2.57</v>
+        <v>3.65</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -6302,22 +6292,22 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="R66" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="S66" t="n">
-        <v>22.2</v>
+        <v>25.9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6325,42 +6315,42 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Al Jubail</t>
+          <t>Vorskla Poltava</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Al Jandal</t>
+          <t>Probiy Horodenka</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="F67" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6370,7 +6360,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -6391,22 +6381,22 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="R67" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
       <c r="S67" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6414,52 +6404,52 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Juventus U23</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VfL Osnabrück</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="F68" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="G68" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1 : 3</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -6470,85 +6460,85 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="R68" t="n">
-        <v>26.7</v>
+        <v>24.5</v>
       </c>
       <c r="S68" t="n">
-        <v>15.6</v>
+        <v>24.5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>26.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FC Nordsjaelland</t>
+          <t>Sousa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="F69" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -6569,65 +6559,65 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="R69" t="n">
-        <v>26.1</v>
+        <v>24.4</v>
       </c>
       <c r="S69" t="n">
-        <v>26.1</v>
+        <v>35.6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>26.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Farense U23</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Estrela U23</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="F70" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G70" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6637,7 +6627,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -6658,22 +6648,22 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="R70" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
       <c r="S70" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6681,52 +6671,52 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>AF Elbasani</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="F71" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="G71" t="n">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -6747,22 +6737,22 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="R71" t="n">
-        <v>25.5</v>
+        <v>24.1</v>
       </c>
       <c r="S71" t="n">
-        <v>26.1</v>
+        <v>24.1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6770,52 +6760,52 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>25.5</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estudiantes de Rio Cuarto</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>San Martin Tucuman</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.41</v>
+        <v>1.66</v>
       </c>
       <c r="F72" t="n">
-        <v>2.65</v>
+        <v>3.48</v>
       </c>
       <c r="G72" t="n">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -6836,65 +6826,65 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="R72" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="S72" t="n">
-        <v>36.4</v>
+        <v>24.1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U72" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="F73" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="G73" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6925,22 +6915,22 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q73" t="n">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="R73" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="S73" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6948,13 +6938,13 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6964,26 +6954,26 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Javor</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Enppi</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="F74" t="n">
-        <v>2.61</v>
+        <v>2.92</v>
       </c>
       <c r="G74" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6993,7 +6983,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -7004,71 +6994,71 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="R74" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="S74" t="n">
-        <v>24.4</v>
+        <v>17.5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Unión Santa Fe Res.</t>
+          <t>TSC Backa Topola</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>San Lorenzo Res.</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2.59</v>
+        <v>1.89</v>
       </c>
       <c r="F75" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="G75" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7112,13 +7102,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="R75" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="S75" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7126,39 +7116,39 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Crusaders FC</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="F76" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G76" t="n">
         <v>3.28</v>
       </c>
-      <c r="G76" t="n">
-        <v>2.6</v>
-      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>0:1</t>
@@ -7171,7 +7161,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -7197,17 +7187,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="R76" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="S76" t="n">
-        <v>27.7</v>
+        <v>28.8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7215,52 +7205,52 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UNAN Managua</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Jalapa</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="F77" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="G77" t="n">
-        <v>5.1</v>
+        <v>2.14</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -7271,75 +7261,75 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="R77" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="S77" t="n">
-        <v>27.7</v>
+        <v>23.3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U77" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>FK Liepaja</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="F78" t="n">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="G78" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7360,75 +7350,75 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q78" t="n">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="R78" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="S78" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U78" t="n">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Bsk Bijelo Brdo</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="F79" t="n">
-        <v>2.82</v>
+        <v>3.42</v>
       </c>
       <c r="G79" t="n">
-        <v>2.58</v>
+        <v>3.82</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7438,7 +7428,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -7449,85 +7439,85 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="R79" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="S79" t="n">
-        <v>21.2</v>
+        <v>27.5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U79" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>UCSA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Ahrobiznes Volochysk</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="F80" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="G80" t="n">
-        <v>4.15</v>
+        <v>2.73</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -7548,22 +7538,22 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="R80" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="S80" t="n">
-        <v>31.5</v>
+        <v>33.8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7571,52 +7561,52 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lanús Res.</t>
+          <t>Vitez</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Deportivo Riestra Res.</t>
+          <t>Jedinstvo Bihać</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="F81" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="G81" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -7637,22 +7627,22 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="R81" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="S81" t="n">
-        <v>31.5</v>
+        <v>33.8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7660,52 +7650,52 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Şamaxı FK</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="F82" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="G82" t="n">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -7726,22 +7716,22 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="R82" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="S82" t="n">
-        <v>31.5</v>
+        <v>33.8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7749,52 +7739,52 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Al-Arabi SC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.4</v>
+        <v>1.86</v>
       </c>
       <c r="F83" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="G83" t="n">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -7805,71 +7795,71 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="Q83" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="R83" t="n">
-        <v>18.7</v>
+        <v>20.8</v>
       </c>
       <c r="S83" t="n">
-        <v>18.7</v>
+        <v>32.6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U83" t="n">
-        <v>18.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kaluga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rapperswil</t>
+          <t>Rodina Moskva II</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.35</v>
+        <v>3.14</v>
       </c>
       <c r="F84" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="G84" t="n">
-        <v>6.35</v>
+        <v>2.08</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -7883,7 +7873,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -7894,12 +7884,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7909,70 +7899,70 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="R84" t="n">
-        <v>17.1</v>
+        <v>20.7</v>
       </c>
       <c r="S84" t="n">
-        <v>17.1</v>
+        <v>20.7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U84" t="n">
-        <v>17.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Glenavon FC</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="F85" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="G85" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -7993,22 +7983,22 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="R85" t="n">
-        <v>16.8</v>
+        <v>19.1</v>
       </c>
       <c r="S85" t="n">
-        <v>16.8</v>
+        <v>12.8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8016,13 +8006,13 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>16.8</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8032,26 +8022,26 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vizela</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Marino</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="F86" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G86" t="n">
-        <v>3.48</v>
+        <v>4.55</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8061,7 +8051,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>2 : 2</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -8082,22 +8072,22 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="R86" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="S86" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8105,42 +8095,42 @@
         </is>
       </c>
       <c r="U86" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Sassuolo U20</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Atalanta U20</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2.09</v>
+        <v>3.04</v>
       </c>
       <c r="F87" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G87" t="n">
-        <v>2.77</v>
+        <v>2</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8150,7 +8140,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -8161,75 +8151,75 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="R87" t="n">
-        <v>15.9</v>
+        <v>18.3</v>
       </c>
       <c r="S87" t="n">
-        <v>25.5</v>
+        <v>18.3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U87" t="n">
-        <v>15.9</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Midlands Wanderers</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Baroka FC</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="F88" t="n">
-        <v>2.82</v>
+        <v>3.52</v>
       </c>
       <c r="G88" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8239,7 +8229,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -8260,22 +8250,22 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="R88" t="n">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
       <c r="S88" t="n">
-        <v>25.5</v>
+        <v>9.1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8283,42 +8273,42 @@
         </is>
       </c>
       <c r="U88" t="n">
-        <v>15.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="F89" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="G89" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8328,7 +8318,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2 : 2</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -8349,75 +8339,75 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="R89" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="S89" t="n">
-        <v>11.1</v>
+        <v>36.7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ferroviario</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jacuipense</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2.12</v>
+        <v>2.51</v>
       </c>
       <c r="F90" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -8438,61 +8428,61 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R90" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="S90" t="n">
-        <v>30.3</v>
+        <v>36.7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>SV Wehen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="F91" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="G91" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -8506,7 +8496,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -8532,17 +8522,17 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>36</v>
+        <v>201</v>
       </c>
       <c r="R91" t="n">
-        <v>8.300000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="S91" t="n">
-        <v>8.300000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -8550,42 +8540,42 @@
         </is>
       </c>
       <c r="U91" t="n">
-        <v>8.300000000000001</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>FC Ingolstadt 04</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>FC Viktoria Köln</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="F92" t="n">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="G92" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8593,12 +8583,12 @@
           <t>언더</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>미결</t>
@@ -8616,65 +8606,75 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>201</v>
+      </c>
+      <c r="R92" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>16.4</v>
+      </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Betting Tips - Tuesday, 7 April 2026</t>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.25</v>
+        <v>2.49</v>
       </c>
       <c r="F93" t="n">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="G93" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -8695,29 +8695,464 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>201</v>
+      </c>
+      <c r="R93" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S93" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Inter U23</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Trento</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>27</v>
+      </c>
+      <c r="R94" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S94" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="Q93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="inlineStr">
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>75</v>
+      </c>
+      <c r="R95" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S95" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="T95" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="U93" t="n">
+      <c r="U95" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2 : 2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>55</v>
+      </c>
+      <c r="R96" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TS Galaxy</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Polokwane City</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>37</v>
+      </c>
+      <c r="R97" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Betting Tips - Wednesday, 8 April 2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bagatelle</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>St. Andrew Lions</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U98"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,36 +526,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Fratria</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Lokomotiv G. Oryahovitsa</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
         <v>10.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,22 +586,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
-        <v>82.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,38 +609,38 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>82.40000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Los Angeles Galaxy</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="n">
-        <v>4.45</v>
+        <v>6.05</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -680,17 +680,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="R3" t="n">
-        <v>80</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -698,38 +698,38 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>80</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Pompiers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Radnicki NIS</t>
+          <t>Inter Nouakchott</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="F4" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3 : 0</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -769,17 +769,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="R4" t="n">
-        <v>72.2</v>
+        <v>74.5</v>
       </c>
       <c r="S4" t="n">
-        <v>13.9</v>
+        <v>10.6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -787,42 +787,42 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>72.2</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HNK Gorica</t>
+          <t>FK Crvena Zvezda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>FK Spartak Zdrepceva KRV</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4.55</v>
+        <v>13.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.38</v>
+        <v>27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0 : 3</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -843,75 +843,75 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="R5" t="n">
-        <v>70.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="S5" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>70.40000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8.699999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>3 : 0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -942,22 +942,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="R6" t="n">
-        <v>69</v>
+        <v>72.5</v>
       </c>
       <c r="S6" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -965,52 +965,52 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>69</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stirling University</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Caledonian Braves</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.15</v>
+        <v>1.29</v>
       </c>
       <c r="F7" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1021,75 +1021,75 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="R7" t="n">
-        <v>66.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>66.7</v>
+        <v>16.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>66.7</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tekstilshchik</t>
+          <t>Krylya Sovetov II</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Torpedo Miass</t>
+          <t>Dinamo Barnaul</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="F8" t="n">
-        <v>3.32</v>
+        <v>4.05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>5.85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1120,22 +1120,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
-        <v>65.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>17.5</v>
+        <v>14.3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1143,327 +1143,327 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>65.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.4</v>
+        <v>1.05</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72</v>
+        <v>19</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4 : 0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>1:4</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>오버</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>1 : 2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>36</v>
+      </c>
+      <c r="R10" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Real Estelí</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Managua</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>127</v>
+      </c>
+      <c r="R11" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3 : 0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>PRE
 VIEW</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>62.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Volgar Astrakhan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Leningradets</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0:4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Montana</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0:5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>18</v>
-      </c>
-      <c r="R11" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Al Diriyah</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Al Jabalain</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>미결</t>
@@ -1481,22 +1481,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="R12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1504,42 +1504,42 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sarmiento Res.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Instituto Res.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.5</v>
+        <v>2.47</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>1.21</v>
+        <v>2.83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0 : 3</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1560,75 +1560,75 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="R13" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="S13" t="n">
-        <v>15.2</v>
+        <v>21.5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>H&amp;H Export</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Real Madriz</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.05</v>
+        <v>1.69</v>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>3 : 1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1649,85 +1649,85 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R14" t="n">
-        <v>56.7</v>
+        <v>57.5</v>
       </c>
       <c r="S14" t="n">
-        <v>11.7</v>
+        <v>7.5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>56.7</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Holywell</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Newtown AFC</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.05</v>
+        <v>11.25</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1748,22 +1748,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>28</v>
       </c>
       <c r="R15" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
       <c r="S15" t="n">
-        <v>7.1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1771,42 +1771,42 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rio Ave U23</t>
+          <t>Argentinos Juniors Res.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Marítimo U23</t>
+          <t>Racing Club Res.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="F16" t="n">
-        <v>3.72</v>
+        <v>3.12</v>
       </c>
       <c r="G16" t="n">
-        <v>3.96</v>
+        <v>3.28</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="R16" t="n">
-        <v>52.3</v>
+        <v>56.3</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1860,55 +1860,60 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>52.3</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Damac</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BG Pathum United</t>
+          <t>Al-Qadisiyah FC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.42</v>
+        <v>6.65</v>
       </c>
       <c r="F17" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>미결</t>
@@ -1916,75 +1921,75 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="R17" t="n">
-        <v>52.3</v>
+        <v>56</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>52.3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SC Braga</t>
+          <t>Matagalpa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Diriangén</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.58</v>
+        <v>4.4</v>
       </c>
       <c r="F18" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1994,193 +1999,193 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>1 : 3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>53</v>
+      </c>
+      <c r="R18" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>63</v>
+      </c>
+      <c r="R19" t="n">
+        <v>54</v>
+      </c>
+      <c r="S19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0 : 1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>PRE
 VIEW</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>256</v>
-      </c>
-      <c r="R18" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>52.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Spokane Velocity</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>173</v>
-      </c>
-      <c r="R19" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>22</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Veles</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Novosibirsk</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2188,71 +2193,71 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="R20" t="n">
-        <v>51.4</v>
+        <v>54</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>14.3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>51.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Huracán Res.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LDU de Quito</t>
+          <t>Estudiantes La Plata Res</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="F21" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="G21" t="n">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2292,17 +2297,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>107</v>
+        <v>258</v>
       </c>
       <c r="R21" t="n">
-        <v>51.4</v>
+        <v>53.1</v>
       </c>
       <c r="S21" t="n">
-        <v>16.8</v>
+        <v>25.2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2310,42 +2315,42 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>51.4</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Real Calepina</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Al-Faisaly FC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2355,7 +2360,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2376,22 +2381,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="R22" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="S22" t="n">
-        <v>19.6</v>
+        <v>22.8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2399,52 +2404,52 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chornomorets</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Inhulets</t>
+          <t>Arda Kardzhali</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="F23" t="n">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2465,22 +2470,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q23" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="R23" t="n">
-        <v>49.5</v>
+        <v>51.7</v>
       </c>
       <c r="S23" t="n">
-        <v>23.9</v>
+        <v>21.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2488,47 +2493,47 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>49.5</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mashuk-KMV</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Irtysh Omsk</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="F24" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58</v>
+        <v>2.91</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2554,7 +2559,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2563,13 +2568,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="R24" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="S24" t="n">
-        <v>23.9</v>
+        <v>20.3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2577,47 +2582,47 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Termoli Calcio</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sammaurese</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>1.25</v>
       </c>
       <c r="F25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="G25" t="n">
         <v>11.75</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2643,7 +2648,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2652,13 +2657,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="R25" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="S25" t="n">
-        <v>23.9</v>
+        <v>20.3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2666,38 +2671,38 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HNK Rijeka</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NK Slaven Belupo</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="F26" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2711,10 +2716,15 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>1 : 0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2737,17 +2747,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="R26" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="S26" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2755,52 +2765,52 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FC Saarbrücken</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>3.38</v>
+        <v>4.75</v>
       </c>
       <c r="G27" t="n">
-        <v>2.83</v>
+        <v>1.25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2811,88 +2821,93 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="S27" t="n">
-        <v>21.3</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coriano</t>
+          <t>FC Porto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.55</v>
+        <v>2.19</v>
       </c>
       <c r="F28" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="G28" t="n">
-        <v>1.49</v>
+        <v>3.56</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1:4</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0 : 2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>2 : 0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>미결</t>
@@ -2900,75 +2915,75 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="R28" t="n">
-        <v>47.6</v>
+        <v>49.2</v>
       </c>
       <c r="S28" t="n">
-        <v>28.6</v>
+        <v>25.7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>47.6</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovan Ljubljana</t>
+          <t>Aldosivi Res.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ilirija</t>
+          <t>River Plate Res.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="G29" t="n">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2978,7 +2993,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2989,88 +3004,93 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>283</v>
+        <v>60</v>
       </c>
       <c r="R29" t="n">
-        <v>47.3</v>
+        <v>48.3</v>
       </c>
       <c r="S29" t="n">
-        <v>25.1</v>
+        <v>16.7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>47.3</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Al Anwar</t>
+          <t>SC Freiburg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Al Wehda Club</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>미결</t>
@@ -3088,22 +3108,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="R30" t="n">
-        <v>46.7</v>
+        <v>47.9</v>
       </c>
       <c r="S30" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3111,42 +3131,42 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>46.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al-Adalah</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Al Baten</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="F31" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="G31" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3156,7 +3176,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3167,71 +3187,71 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>303</v>
       </c>
       <c r="R31" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="S31" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Cherno More Varna</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="F32" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="G32" t="n">
-        <v>6.05</v>
+        <v>9</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3275,13 +3295,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R32" t="n">
         <v>46.5</v>
       </c>
       <c r="S32" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3295,46 +3315,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PWD Bamenda</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Victoria United</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="F33" t="n">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="G33" t="n">
-        <v>3.72</v>
+        <v>6.15</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -3355,22 +3375,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="R33" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="S33" t="n">
-        <v>27.9</v>
+        <v>23.1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3378,52 +3398,52 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Folgore</t>
+          <t>Al Ula</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cosmos</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="F34" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="G34" t="n">
-        <v>3.88</v>
+        <v>3.14</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -3444,22 +3464,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="R34" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
       <c r="S34" t="n">
-        <v>27.9</v>
+        <v>21.3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3467,42 +3487,42 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="F35" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="G35" t="n">
-        <v>3.98</v>
+        <v>5.25</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3512,10 +3532,15 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1 : 0</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>0 : 0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>미결</t>
@@ -3533,22 +3558,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="R35" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="S35" t="n">
-        <v>22.3</v>
+        <v>16.4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3556,38 +3581,38 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="F36" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="G36" t="n">
-        <v>4.85</v>
+        <v>3.24</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3601,7 +3626,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -3627,17 +3652,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="R36" t="n">
-        <v>45.6</v>
+        <v>44.4</v>
       </c>
       <c r="S36" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3645,42 +3670,42 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>45.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dynamo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FC Krasnodar</t>
+          <t>FK Partizan</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="F37" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="G37" t="n">
-        <v>2.63</v>
+        <v>2.22</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3690,7 +3715,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -3701,75 +3726,75 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="R37" t="n">
-        <v>44.1</v>
+        <v>43.4</v>
       </c>
       <c r="S37" t="n">
-        <v>29.7</v>
+        <v>18.9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>44.1</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>União Leiria U23</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Portimonense U23</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.96</v>
+        <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="G38" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3790,17 +3815,17 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3809,52 +3834,52 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="R38" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="S38" t="n">
-        <v>23</v>
+        <v>18.9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.05</v>
+        <v>1.14</v>
       </c>
       <c r="F39" t="n">
-        <v>3.15</v>
+        <v>5.95</v>
       </c>
       <c r="G39" t="n">
-        <v>3.25</v>
+        <v>14.75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3898,13 +3923,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R39" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="S39" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3912,42 +3937,42 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Larisa</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Panetolikos</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="F40" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="G40" t="n">
-        <v>3.54</v>
+        <v>2.61</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3957,7 +3982,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -3968,80 +3993,80 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="R40" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="S40" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>AO Itabaiana</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="F41" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="G41" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4067,7 +4092,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4076,66 +4101,66 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R41" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="S41" t="n">
-        <v>37.2</v>
+        <v>23.7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Naft</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Gharraf</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.6</v>
+        <v>1.98</v>
       </c>
       <c r="F42" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="G42" t="n">
-        <v>1.86</v>
+        <v>3.58</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4146,71 +4171,71 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="R42" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="S42" t="n">
-        <v>29.2</v>
+        <v>23.7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Al-Raed</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="F43" t="n">
-        <v>3.78</v>
+        <v>2.96</v>
       </c>
       <c r="G43" t="n">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4254,13 +4279,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R43" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="S43" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4268,38 +4293,38 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Club Queretaro</t>
+          <t>Cusco</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.85</v>
+        <v>4.65</v>
       </c>
       <c r="F44" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G44" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4343,13 +4368,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R44" t="n">
-        <v>39.7</v>
+        <v>38.5</v>
       </c>
       <c r="S44" t="n">
-        <v>20.6</v>
+        <v>23.1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4357,38 +4382,38 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>39.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milford FC</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Casric Stars</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="F45" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="G45" t="n">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4432,13 +4457,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R45" t="n">
-        <v>39.7</v>
+        <v>38.5</v>
       </c>
       <c r="S45" t="n">
-        <v>20.6</v>
+        <v>23.1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4446,38 +4471,38 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>39.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="F46" t="n">
         <v>2.76</v>
       </c>
       <c r="G46" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4521,13 +4546,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R46" t="n">
-        <v>37.8</v>
+        <v>38.4</v>
       </c>
       <c r="S46" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4535,52 +4560,52 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>37.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>XV de Piracicaba</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Juazeirense</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.26</v>
+        <v>1.96</v>
       </c>
       <c r="F47" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="G47" t="n">
-        <v>10.5</v>
+        <v>3.62</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -4601,22 +4626,22 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="R47" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="S47" t="n">
-        <v>33.1</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4624,42 +4649,42 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>UCV</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Libertad Asuncion</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="F48" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G48" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4669,7 +4694,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -4690,75 +4715,75 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="R48" t="n">
-        <v>37.1</v>
+        <v>36.4</v>
       </c>
       <c r="S48" t="n">
-        <v>34.3</v>
+        <v>36.4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>37.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dinamo Tirana</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vllaznia Shkodër</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.67</v>
+        <v>3.4</v>
       </c>
       <c r="F49" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G49" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -4779,22 +4804,22 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="R49" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
       <c r="S49" t="n">
-        <v>21.1</v>
+        <v>28.9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4802,13 +4827,13 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4818,31 +4843,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Atletico Torque</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.8</v>
+        <v>3.08</v>
       </c>
       <c r="F50" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="G50" t="n">
-        <v>1.52</v>
+        <v>2.39</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4868,7 +4893,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4877,56 +4902,56 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R50" t="n">
-        <v>35.7</v>
+        <v>35</v>
       </c>
       <c r="S50" t="n">
-        <v>35.7</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>35.7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>A. Italiano</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lerumo Lions</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.9</v>
+        <v>3.28</v>
       </c>
       <c r="F51" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="G51" t="n">
-        <v>3.75</v>
+        <v>2.31</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4936,7 +4961,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4947,46 +4972,46 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="R51" t="n">
-        <v>34.7</v>
+        <v>33.3</v>
       </c>
       <c r="S51" t="n">
-        <v>16.7</v>
+        <v>14</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>34.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4996,22 +5021,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Les Herbiers</t>
+          <t>Esenler Erokspor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Poitiers</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="F52" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G52" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5025,7 +5050,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>2 : 3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -5051,17 +5076,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="R52" t="n">
-        <v>34.7</v>
+        <v>31.6</v>
       </c>
       <c r="S52" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5069,47 +5094,47 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>34.7</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chonburi FC</t>
+          <t>Atlético Choloma</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="F53" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="G53" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5135,7 +5160,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5144,13 +5169,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R53" t="n">
-        <v>34.3</v>
+        <v>27.7</v>
       </c>
       <c r="S53" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5158,38 +5183,38 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>34.3</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Formartine United</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Banks O' Dee</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="F54" t="n">
-        <v>3.76</v>
+        <v>2.72</v>
       </c>
       <c r="G54" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -5203,7 +5228,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -5214,12 +5239,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5229,65 +5254,65 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R54" t="n">
-        <v>34.2</v>
+        <v>26.5</v>
       </c>
       <c r="S54" t="n">
-        <v>23.3</v>
+        <v>19.3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>34.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Libertas</t>
+          <t>FC Isloch Minsk R.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Juvenes / Dogana</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="F55" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="G55" t="n">
-        <v>2.01</v>
+        <v>3.02</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5303,17 +5328,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5322,61 +5347,61 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="R55" t="n">
-        <v>34.1</v>
+        <v>26.4</v>
       </c>
       <c r="S55" t="n">
-        <v>24.4</v>
+        <v>27</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>34.1</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pafos</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.15</v>
+        <v>2.38</v>
       </c>
       <c r="F56" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="G56" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5392,85 +5417,85 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
       <c r="Q56" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="R56" t="n">
-        <v>33.9</v>
+        <v>26.1</v>
       </c>
       <c r="S56" t="n">
-        <v>14.3</v>
+        <v>34.8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U56" t="n">
-        <v>33.9</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Spartak Moscow</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="F57" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="G57" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3 : 1</t>
+          <t>2 : 1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -5491,22 +5516,22 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="R57" t="n">
-        <v>30.2</v>
+        <v>25.2</v>
       </c>
       <c r="S57" t="n">
-        <v>30.2</v>
+        <v>26.4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5514,52 +5539,52 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>30.2</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Atlético Tucumán Res.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Tigre Res.</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.76</v>
+        <v>2.01</v>
       </c>
       <c r="F58" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="G58" t="n">
-        <v>2.04</v>
+        <v>3.38</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -5570,75 +5595,75 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="R58" t="n">
-        <v>29.8</v>
+        <v>24.4</v>
       </c>
       <c r="S58" t="n">
-        <v>23.4</v>
+        <v>11.5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>29.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="F59" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="G59" t="n">
-        <v>4.35</v>
+        <v>3.28</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5648,7 +5673,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -5669,22 +5694,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>57</v>
+        <v>190</v>
       </c>
       <c r="R59" t="n">
-        <v>28.1</v>
+        <v>24.2</v>
       </c>
       <c r="S59" t="n">
-        <v>28.1</v>
+        <v>24.2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5692,42 +5717,42 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>28.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tochigi SC</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="F60" t="n">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="G60" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5737,10 +5762,15 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0 : 2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>미결</t>
@@ -5758,22 +5788,22 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="R60" t="n">
-        <v>28</v>
+        <v>24.2</v>
       </c>
       <c r="S60" t="n">
-        <v>30</v>
+        <v>24.2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5781,42 +5811,42 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>28</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>FSV Mainz 05</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Milazzo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="F61" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="G61" t="n">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5826,10 +5856,15 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0 : 2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>1 : 1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>미결</t>
@@ -5847,22 +5882,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="R61" t="n">
-        <v>28</v>
+        <v>24.1</v>
       </c>
       <c r="S61" t="n">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5870,38 +5905,38 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>28</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cumbayá</t>
+          <t>Chernomorets 1919 Burgas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Gualaceo SC</t>
+          <t>Pirin Blagoevgrad</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="F62" t="n">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="G62" t="n">
-        <v>3.22</v>
+        <v>3.82</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5915,7 +5950,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5941,17 +5976,17 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="R62" t="n">
-        <v>27.7</v>
+        <v>24.1</v>
       </c>
       <c r="S62" t="n">
-        <v>21.8</v>
+        <v>28.4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5959,42 +5994,42 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>27.7</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Zawisza Bydgoszcz</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="F63" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4</v>
+        <v>3.34</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6015,17 +6050,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6034,66 +6069,66 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="R63" t="n">
-        <v>27.3</v>
+        <v>21.7</v>
       </c>
       <c r="S63" t="n">
-        <v>54.5</v>
+        <v>21.7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>27.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Diyala</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9 de Octubre</t>
+          <t>Naft Maysan</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="F64" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="G64" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -6114,22 +6149,22 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="R64" t="n">
-        <v>26</v>
+        <v>20.9</v>
       </c>
       <c r="S64" t="n">
-        <v>27.2</v>
+        <v>31.8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6137,13 +6172,13 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>26</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6153,36 +6188,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SSV Ulm 1846</t>
+          <t>Radnicki 1923</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="F65" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="G65" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -6203,22 +6238,22 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="R65" t="n">
-        <v>26</v>
+        <v>20.9</v>
       </c>
       <c r="S65" t="n">
-        <v>27.2</v>
+        <v>31.8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6226,38 +6261,38 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>26</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="F66" t="n">
         <v>3.38</v>
       </c>
       <c r="G66" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -6271,7 +6306,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -6297,17 +6332,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="R66" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
       <c r="S66" t="n">
-        <v>25.9</v>
+        <v>31.8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6315,52 +6350,52 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vorskla Poltava</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Probiy Horodenka</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="F67" t="n">
-        <v>2.88</v>
+        <v>3.46</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>1 : 1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -6381,22 +6416,22 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q67" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="R67" t="n">
-        <v>24.5</v>
+        <v>20.9</v>
       </c>
       <c r="S67" t="n">
-        <v>24.5</v>
+        <v>31.8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6404,52 +6439,52 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>24.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Juventus U23</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="G68" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2 : 0</t>
+          <t>2 : 2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -6470,22 +6505,22 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="R68" t="n">
-        <v>24.5</v>
+        <v>18.8</v>
       </c>
       <c r="S68" t="n">
-        <v>24.5</v>
+        <v>14.6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6493,52 +6528,52 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>24.5</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sousa</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.22</v>
+        <v>4.45</v>
       </c>
       <c r="F69" t="n">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="G69" t="n">
-        <v>3.32</v>
+        <v>1.6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -6549,85 +6584,85 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="R69" t="n">
-        <v>24.4</v>
+        <v>18.2</v>
       </c>
       <c r="S69" t="n">
-        <v>35.6</v>
+        <v>18.2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>24.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Farense U23</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Estrela U23</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="F70" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="G70" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>2 : 3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -6648,22 +6683,22 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="R70" t="n">
-        <v>24.1</v>
+        <v>17.6</v>
       </c>
       <c r="S70" t="n">
-        <v>24.1</v>
+        <v>17.6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6671,42 +6706,42 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>24.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Sevlievo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AF Elbasani</t>
+          <t>Spartak Pleven</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="F71" t="n">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
       <c r="G71" t="n">
-        <v>2.83</v>
+        <v>5.2</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6716,7 +6751,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -6737,61 +6772,61 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q71" t="n">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="R71" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
       <c r="S71" t="n">
-        <v>24.1</v>
+        <v>35.4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>AEK Athens FC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="F72" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="G72" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -6805,10 +6840,15 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>2 : 1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PRE
+VIEW</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>미결</t>
@@ -6831,17 +6871,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="R72" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
       <c r="S72" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6849,42 +6889,42 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>24.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Sarmiento Junin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Tristan Suarez</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="F73" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="G73" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6894,7 +6934,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -6915,75 +6955,75 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="R73" t="n">
-        <v>24.1</v>
+        <v>16.1</v>
       </c>
       <c r="S73" t="n">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U73" t="n">
-        <v>24.1</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Javor</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="F74" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="G74" t="n">
-        <v>2.53</v>
+        <v>5.3</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0 : 2</t>
+          <t>2 : 0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -6994,75 +7034,75 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
       <c r="Q74" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="R74" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S74" t="n">
         <v>23.8</v>
       </c>
-      <c r="S74" t="n">
-        <v>17.5</v>
-      </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TSC Backa Topola</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.89</v>
+        <v>3.54</v>
       </c>
       <c r="F75" t="n">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7072,7 +7112,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>0 : 2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -7083,75 +7123,75 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="R75" t="n">
-        <v>23.7</v>
+        <v>12.1</v>
       </c>
       <c r="S75" t="n">
-        <v>28.8</v>
+        <v>12.1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>23.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="F76" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="G76" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7161,7 +7201,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1 : 1</t>
+          <t>1 : 2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -7182,22 +7222,22 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="R76" t="n">
-        <v>23.7</v>
+        <v>11.9</v>
       </c>
       <c r="S76" t="n">
-        <v>28.8</v>
+        <v>29.9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7205,42 +7245,42 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>23.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UNAN Managua</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jalapa</t>
+          <t>Erzurumspor FK</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="F77" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7250,7 +7290,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>1 : 3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -7271,22 +7311,22 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="R77" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="S77" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7294,42 +7334,42 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
+          <t>Betting Tips - Thursday, 9 April 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FK Liepaja</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="F78" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="G78" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7337,12 +7377,12 @@
           <t>언더</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>미결</t>
@@ -7360,1799 +7400,19 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q78" t="n">
-        <v>206</v>
-      </c>
-      <c r="R78" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S78" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>분석중</t>
         </is>
       </c>
       <c r="U78" t="n">
-        <v>23.3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Barranquilla</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Real Santander</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F79" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="G79" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>120</v>
-      </c>
-      <c r="R79" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S79" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U79" t="n">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>UCSA</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Ahrobiznes Volochysk</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>68</v>
-      </c>
-      <c r="R80" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U80" t="n">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Vitez</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Jedinstvo Bihać</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="F81" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="G81" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>68</v>
-      </c>
-      <c r="R81" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U81" t="n">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Atletico Madrid</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F82" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G82" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>68</v>
-      </c>
-      <c r="R82" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S82" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U82" t="n">
-        <v>22.1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Al-Arabi SC</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Qatar SC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F83" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="G83" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>144</v>
-      </c>
-      <c r="R83" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S83" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U83" t="n">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Kaluga</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Rodina Moskva II</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="F84" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>1 : 1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>87</v>
-      </c>
-      <c r="R84" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="S84" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U84" t="n">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Club America</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F85" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="G85" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2 : 2</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>47</v>
-      </c>
-      <c r="R85" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S85" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tamaraceite</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Marino</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="F86" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G86" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2 : 2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>53</v>
-      </c>
-      <c r="R86" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S86" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U86" t="n">
-        <v>18.9</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Sassuolo U20</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Atalanta U20</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>1 : 2</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>109</v>
-      </c>
-      <c r="R87" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S87" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U87" t="n">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Verl</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Hansa Rostock</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2 : 3</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>11</v>
-      </c>
-      <c r="R88" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S88" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Lanus</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="F89" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>30</v>
-      </c>
-      <c r="R89" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="S89" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Kedus Giorgis</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Mebrat Hayl</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F90" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>0 : 1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>30</v>
-      </c>
-      <c r="R90" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="S90" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SV Wehen</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Havelse</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F91" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>5</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>201</v>
-      </c>
-      <c r="R91" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S91" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>FC Ingolstadt 04</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>FC Viktoria Köln</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="F92" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="G92" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>201</v>
-      </c>
-      <c r="R92" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S92" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="F93" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="G93" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>201</v>
-      </c>
-      <c r="R93" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S93" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Inter U23</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Trento</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="F94" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>2 : 1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>27</v>
-      </c>
-      <c r="R94" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S94" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Deportes Tolima</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Universitario</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G95" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2 : 0</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>75</v>
-      </c>
-      <c r="R95" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S95" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Nueva Chicago</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F96" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="G96" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2 : 2</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>55</v>
-      </c>
-      <c r="R96" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>10.9</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>TS Galaxy</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Polokwane City</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="F97" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="G97" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>0 : 0</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>37</v>
-      </c>
-      <c r="R97" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="S97" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Betting Tips - Wednesday, 8 April 2026</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Bagatelle</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>St. Andrew Lions</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>분석중</t>
-        </is>
-      </c>
-      <c r="U98" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U91"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,36 +526,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FAS</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dragón</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="F2" t="n">
-        <v>5.45</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1</v>
+        <v>10.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3 : 0(2 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="R2" t="n">
-        <v>72.7</v>
+        <v>74.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -613,42 +613,42 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>72.7</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Deportivo Saprissa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Levadia Tallinn</t>
+          <t>Guadalupe FC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>1.12</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24</v>
+        <v>14</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,75 +673,75 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="R3" t="n">
-        <v>71.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>71.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Al-Hilal Saudi FC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="F4" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>11.25</v>
+        <v>18.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -776,22 +776,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -799,42 +799,42 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="F5" t="n">
-        <v>4.25</v>
+        <v>7.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>11.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -869,22 +869,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="S5" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -892,42 +892,42 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Zorya Luhansk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>4.33</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>1.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>0:5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -952,75 +952,75 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="S6" t="n">
-        <v>8.699999999999999</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ohrid</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>1.48</v>
       </c>
       <c r="F7" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.27</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0:5</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,75 +1045,75 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="R7" t="n">
-        <v>63.2</v>
+        <v>57.1</v>
       </c>
       <c r="S7" t="n">
-        <v>15.8</v>
+        <v>11.7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>63.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Surkhon</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="F8" t="n">
-        <v>3.75</v>
+        <v>4.85</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1148,22 +1148,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="R8" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1171,42 +1171,42 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kalju Nomme</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="F9" t="n">
-        <v>4.65</v>
+        <v>3.78</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="R9" t="n">
-        <v>60</v>
+        <v>56.8</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1264,38 +1264,38 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>60</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Damac</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Al Okhdood</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="F10" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="G10" t="n">
-        <v>5.15</v>
+        <v>4.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="R10" t="n">
-        <v>57.2</v>
+        <v>56.4</v>
       </c>
       <c r="S10" t="n">
-        <v>16.7</v>
+        <v>22.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1357,57 +1357,57 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>57.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FK Sarajevo</t>
+          <t>Inter Moengotapoe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leo Victor</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="G11" t="n">
-        <v>12.25</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>3 : 2(0 : 1)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1427,22 +1427,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="R11" t="n">
-        <v>56.7</v>
+        <v>51.9</v>
       </c>
       <c r="S11" t="n">
-        <v>26.7</v>
+        <v>16.9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1450,52 +1450,52 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>56.7</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Flora Tallinn</t>
+          <t>Aalborg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>B 93</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="F12" t="n">
         <v>4.05</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="R12" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="S12" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1543,57 +1543,57 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York City FC</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1 : 0(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="R13" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="S13" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1636,42 +1636,42 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Jose Earthquakes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="E14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G14" t="n">
         <v>6.05</v>
       </c>
-      <c r="F14" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.48</v>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1696,90 +1696,90 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="R14" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="S14" t="n">
-        <v>14.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gumi Sportstoto</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Suwon FMC</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>4 : 1(1 : 0)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
       <c r="Q15" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="S15" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1838,26 +1838,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sonderjyske</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Independiente del Valle</t>
+          <t>FC Midtjylland</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="F16" t="n">
-        <v>3.06</v>
+        <v>4.05</v>
       </c>
       <c r="G16" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1892,22 +1892,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="S16" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1915,52 +1915,52 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Start Brno</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hodonín</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.3</v>
+        <v>2.69</v>
       </c>
       <c r="F17" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="R17" t="n">
-        <v>47.4</v>
+        <v>48.5</v>
       </c>
       <c r="S17" t="n">
-        <v>21.1</v>
+        <v>11.9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2008,52 +2008,52 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>47.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>IBV Vestmannaeyjar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
-        <v>6.85</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2068,85 +2068,85 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="R18" t="n">
-        <v>46.4</v>
+        <v>48.4</v>
       </c>
       <c r="S18" t="n">
-        <v>21.7</v>
+        <v>12.9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>46.4</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Muras United</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al Kuwait</t>
+          <t>SC Braga</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="F19" t="n">
-        <v>3.22</v>
+        <v>3.95</v>
       </c>
       <c r="G19" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2161,75 +2161,75 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="R19" t="n">
-        <v>46.4</v>
+        <v>47</v>
       </c>
       <c r="S19" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>46.4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Independiente Medellin</t>
+          <t>GO Ahead Eagles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chico</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>2.94</v>
       </c>
       <c r="F20" t="n">
-        <v>5.05</v>
+        <v>3.68</v>
       </c>
       <c r="G20" t="n">
-        <v>9.699999999999999</v>
+        <v>2.17</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2254,75 +2254,75 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="R20" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
       <c r="S20" t="n">
-        <v>17.9</v>
+        <v>20.8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atlante FC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Tepatitlán</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="F21" t="n">
-        <v>7.8</v>
+        <v>4.15</v>
       </c>
       <c r="G21" t="n">
-        <v>12.25</v>
+        <v>6.15</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="S21" t="n">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2380,42 +2380,42 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Al-Nassr</t>
+          <t>Zakho</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al Ahli Doha</t>
+          <t>Al Kahrabaa</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="F22" t="n">
-        <v>7.6</v>
+        <v>3.28</v>
       </c>
       <c r="G22" t="n">
-        <v>15.25</v>
+        <v>4.85</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="R22" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
       <c r="S22" t="n">
-        <v>23.1</v>
+        <v>18.9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2473,38 +2473,38 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1 : 0(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R23" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="S23" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2566,38 +2566,38 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Liège</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="F24" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="G24" t="n">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="R24" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="S24" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2659,42 +2659,42 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ZESCO United</t>
+          <t>Gais</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nkana</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.96</v>
+        <v>3.04</v>
       </c>
       <c r="F25" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="G25" t="n">
-        <v>3.86</v>
+        <v>2.29</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2719,85 +2719,85 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="R25" t="n">
-        <v>45.9</v>
+        <v>45.1</v>
       </c>
       <c r="S25" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U25" t="n">
-        <v>45.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pafos</t>
+          <t>Spartak Moscow</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>FC Krasnodar</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="F26" t="n">
-        <v>3.88</v>
+        <v>3.52</v>
       </c>
       <c r="G26" t="n">
-        <v>5.65</v>
+        <v>3.08</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2822,22 +2822,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="R26" t="n">
-        <v>44.9</v>
+        <v>44.3</v>
       </c>
       <c r="S26" t="n">
-        <v>17.4</v>
+        <v>18.6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2845,47 +2845,47 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>44.9</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="F27" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="G27" t="n">
-        <v>7.9</v>
+        <v>3.76</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2924,13 +2924,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="R27" t="n">
-        <v>44.9</v>
+        <v>43.7</v>
       </c>
       <c r="S27" t="n">
-        <v>17.4</v>
+        <v>21.8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2938,47 +2938,47 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>44.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>03:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Guadalajara Chivas</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.63</v>
+        <v>5.15</v>
       </c>
       <c r="F28" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="G28" t="n">
-        <v>5.05</v>
+        <v>1.53</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2 : 2(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2998,17 +2998,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3017,61 +3017,61 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="R28" t="n">
-        <v>44.3</v>
+        <v>43.5</v>
       </c>
       <c r="S28" t="n">
-        <v>18.6</v>
+        <v>24.3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>44.3</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Maleyet Kafr El Zayiat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bhayangkara FC</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.27</v>
+        <v>4.35</v>
       </c>
       <c r="F29" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="G29" t="n">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3110,52 +3110,52 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="R29" t="n">
-        <v>44.3</v>
+        <v>43.5</v>
       </c>
       <c r="S29" t="n">
-        <v>18.6</v>
+        <v>24.3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>44.3</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FC UFA</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="F30" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
-        <v>3.12</v>
+        <v>4.45</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>314</v>
       </c>
       <c r="R30" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="S30" t="n">
         <v>22</v>
@@ -3217,38 +3217,38 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AL Masry</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Enppi</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.13</v>
+        <v>1.53</v>
       </c>
       <c r="F31" t="n">
-        <v>2.67</v>
+        <v>3.94</v>
       </c>
       <c r="G31" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>4 : 1(1 : 0)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>314</v>
       </c>
       <c r="R31" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="S31" t="n">
         <v>22</v>
@@ -3310,52 +3310,52 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Radnicki NIS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Javor</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.86</v>
+        <v>1.89</v>
       </c>
       <c r="F32" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="G32" t="n">
-        <v>1.82</v>
+        <v>3.82</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3370,75 +3370,75 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>140</v>
+        <v>314</v>
       </c>
       <c r="R32" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S32" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gwangju FC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="F33" t="n">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="G33" t="n">
-        <v>5.9</v>
+        <v>3.58</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="R33" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="S33" t="n">
-        <v>26.7</v>
+        <v>21.4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3496,57 +3496,57 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FC Porto</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.35</v>
+        <v>1.34</v>
       </c>
       <c r="F34" t="n">
-        <v>3.04</v>
+        <v>4.6</v>
       </c>
       <c r="G34" t="n">
-        <v>3.22</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2 : 0(0 : 0)</t>
+          <t>1 : 3(1 : 1)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3566,22 +3566,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>342</v>
       </c>
       <c r="R34" t="n">
-        <v>40</v>
+        <v>42.4</v>
       </c>
       <c r="S34" t="n">
-        <v>26.7</v>
+        <v>24.9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3589,42 +3589,42 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>40</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CSKA Sofia II</t>
+          <t>Difai Ağsu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hebar 1918</t>
+          <t>Səbail</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.64</v>
+        <v>6.9</v>
       </c>
       <c r="F35" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="G35" t="n">
-        <v>4.4</v>
+        <v>1.37</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3649,90 +3649,90 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="R35" t="n">
-        <v>39</v>
+        <v>42.4</v>
       </c>
       <c r="S35" t="n">
-        <v>20.3</v>
+        <v>27.3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>39</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.47</v>
+        <v>1.85</v>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="G36" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1 : 4(1 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>342</v>
       </c>
       <c r="R36" t="n">
-        <v>38.3</v>
+        <v>42.4</v>
       </c>
       <c r="S36" t="n">
-        <v>18.3</v>
+        <v>24.9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3775,57 +3775,57 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>38.3</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="F37" t="n">
-        <v>3.58</v>
+        <v>4.9</v>
       </c>
       <c r="G37" t="n">
-        <v>4.75</v>
+        <v>1.39</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2 : 3(1 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3835,90 +3835,90 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="R37" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="S37" t="n">
-        <v>30</v>
+        <v>21.6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>AIK Stockholm</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="F38" t="n">
-        <v>3.92</v>
+        <v>3.26</v>
       </c>
       <c r="G38" t="n">
-        <v>4.9</v>
+        <v>2.38</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0 : 3(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3928,87 +3928,87 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="R38" t="n">
-        <v>37.4</v>
+        <v>38.8</v>
       </c>
       <c r="S38" t="n">
-        <v>26.7</v>
+        <v>16.4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>37.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Şimal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Baku Sportinq</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.42</v>
+        <v>8.9</v>
       </c>
       <c r="F39" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="G39" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -4031,22 +4031,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="Q39" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="R39" t="n">
-        <v>37.3</v>
+        <v>38.1</v>
       </c>
       <c r="S39" t="n">
-        <v>14.9</v>
+        <v>25.7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4054,42 +4054,42 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>37.3</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.85</v>
+        <v>2.3</v>
       </c>
       <c r="F40" t="n">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="G40" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4114,75 +4114,75 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="R40" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="S40" t="n">
-        <v>14.9</v>
+        <v>18</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vukovar</t>
+          <t>Platense Res.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HNK Gorica</t>
+          <t>Argentinos Juniors Res.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="F41" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="G41" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4226,13 +4226,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R41" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="S41" t="n">
-        <v>14.9</v>
+        <v>22.9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4240,38 +4240,38 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Club Deportivo Los Chankas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="F42" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="G42" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4315,17 +4315,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="R42" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="S42" t="n">
-        <v>28.9</v>
+        <v>26.3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4333,42 +4333,42 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Union St. Gilloise</t>
+          <t>Proxy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>El Seka El Hadid</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.46</v>
+        <v>2.47</v>
       </c>
       <c r="F43" t="n">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="G43" t="n">
-        <v>6.45</v>
+        <v>3.48</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2 : 1(1 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4403,22 +4403,22 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R43" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="S43" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4426,42 +4426,42 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Al Talaba</t>
+          <t>FC Nordsjaelland</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Newroz</t>
+          <t>Aarhus</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.79</v>
+        <v>2.94</v>
       </c>
       <c r="F44" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="G44" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0 : 0(0 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4486,75 +4486,75 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="R44" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
       <c r="S44" t="n">
-        <v>20.2</v>
+        <v>25.3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>36.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atletico Grau</t>
+          <t>CDS Tampico Madero</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>CA La Paz</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.18</v>
+        <v>1.55</v>
       </c>
       <c r="F45" t="n">
-        <v>3.04</v>
+        <v>4.05</v>
       </c>
       <c r="G45" t="n">
-        <v>2.3</v>
+        <v>5.35</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4 : 1(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4579,85 +4579,85 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="R45" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="S45" t="n">
-        <v>21.8</v>
+        <v>19.8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jendouba Sport</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bouchamma</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="F46" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="G46" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4682,22 +4682,22 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>308</v>
+        <v>96</v>
       </c>
       <c r="R46" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="S46" t="n">
-        <v>29.2</v>
+        <v>19.8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4705,42 +4705,42 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympique Safi</t>
+          <t>Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.85</v>
+        <v>2.69</v>
       </c>
       <c r="F47" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="G47" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1 : 1(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4775,61 +4775,61 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>308</v>
+        <v>34</v>
       </c>
       <c r="R47" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="S47" t="n">
-        <v>29.2</v>
+        <v>35.3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="F48" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="G48" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1 : 0(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="R48" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="S48" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4891,57 +4891,57 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Stade Renard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>PWD Bamenda</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.28</v>
+        <v>2.44</v>
       </c>
       <c r="F49" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="G49" t="n">
-        <v>2.19</v>
+        <v>2.76</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0 : 2(0 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4951,75 +4951,75 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="R49" t="n">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
       <c r="S49" t="n">
-        <v>23.8</v>
+        <v>29</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Barra</t>
+          <t>El Dakhleya</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Baladiyyat Al Mehalla</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="R50" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="S50" t="n">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5077,38 +5077,38 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Al-Ittihad Kalba</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Baniyas SC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="F51" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="G51" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R51" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="S51" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5170,52 +5170,52 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FC Anyang</t>
+          <t>Aswan Sc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ulsan Hyundai FC</t>
+          <t>Masar</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="F52" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5240,22 +5240,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="R52" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="S52" t="n">
-        <v>12.8</v>
+        <v>30.8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5263,38 +5263,38 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="F53" t="n">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="G53" t="n">
-        <v>3.04</v>
+        <v>1.84</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -5308,12 +5308,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>1 : 4(0 : 3)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5338,56 +5338,56 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="R53" t="n">
-        <v>28</v>
+        <v>30.8</v>
       </c>
       <c r="S53" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>28</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FK Partizan</t>
+          <t>Radnicki 1923</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.17</v>
+        <v>3.26</v>
       </c>
       <c r="F54" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="G54" t="n">
-        <v>2.85</v>
+        <v>2.06</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5431,31 +5431,31 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="R54" t="n">
-        <v>26.9</v>
+        <v>30.8</v>
       </c>
       <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>30.8</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U54" t="n">
-        <v>26.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5465,36 +5465,36 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Leicesterfield</t>
+          <t>Raya Ghazl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lerumo Lions</t>
+          <t>El Mansura</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.58</v>
+        <v>3.22</v>
       </c>
       <c r="F55" t="n">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="G55" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>26.7</v>
+        <v>30.8</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5542,47 +5542,47 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>26.7</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2 : 1(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5621,13 +5621,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="R56" t="n">
-        <v>25.3</v>
+        <v>30.4</v>
       </c>
       <c r="S56" t="n">
-        <v>19.8</v>
+        <v>24.1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5635,42 +5635,42 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>25.3</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="F57" t="n">
-        <v>6.35</v>
+        <v>4.05</v>
       </c>
       <c r="G57" t="n">
-        <v>10.5</v>
+        <v>3.04</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2 : 41 : 1(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5714,13 +5714,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="R57" t="n">
-        <v>25</v>
+        <v>29.8</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5728,54 +5728,54 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>25</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CS Cartagines</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.56</v>
+        <v>3.72</v>
       </c>
       <c r="F58" t="n">
-        <v>3.65</v>
+        <v>3.36</v>
       </c>
       <c r="G58" t="n">
-        <v>5.1</v>
+        <v>2.15</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -5788,75 +5788,75 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Q58" t="n">
-        <v>205</v>
+        <v>11</v>
       </c>
       <c r="R58" t="n">
-        <v>23.4</v>
+        <v>27.3</v>
       </c>
       <c r="S58" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>23.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Pyunik Yerevan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Shinnik Yaroslavl</t>
+          <t>FC Urartu</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="F59" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="G59" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5891,22 +5891,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="R59" t="n">
-        <v>22.7</v>
+        <v>26.8</v>
       </c>
       <c r="S59" t="n">
-        <v>21</v>
+        <v>26.8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5914,52 +5914,52 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>22.7</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FC Orenburg</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nizhny Novgorod</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="F60" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="G60" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5984,22 +5984,22 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="R60" t="n">
-        <v>21.9</v>
+        <v>25.9</v>
       </c>
       <c r="S60" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6007,52 +6007,52 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>21.9</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mineros de Zacatecas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Monarcas</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="F61" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="G61" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6077,22 +6077,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="R61" t="n">
-        <v>21.9</v>
+        <v>25.7</v>
       </c>
       <c r="S61" t="n">
-        <v>22.4</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6100,57 +6100,57 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>21.9</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cukaricki</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.96</v>
+        <v>7.1</v>
       </c>
       <c r="F62" t="n">
-        <v>3.32</v>
+        <v>4.85</v>
       </c>
       <c r="G62" t="n">
-        <v>3.34</v>
+        <v>1.31</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1 : 1(0 : 1)</t>
+          <t>2 : 3(2 : 2)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6160,85 +6160,85 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="R62" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="S62" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U62" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Malženice</t>
+          <t>Zamalek SC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Slávia TU Košice</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="F63" t="n">
-        <v>3.44</v>
+        <v>2.81</v>
       </c>
       <c r="G63" t="n">
-        <v>3.55</v>
+        <v>2.41</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6253,80 +6253,80 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="R63" t="n">
-        <v>21.1</v>
+        <v>24.7</v>
       </c>
       <c r="S63" t="n">
-        <v>15.5</v>
+        <v>19.4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>21.1</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Tersana</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jeju United FC</t>
+          <t>Asyut Petrol</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="F64" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="G64" t="n">
-        <v>4.75</v>
+        <v>2.48</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6365,56 +6365,56 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="R64" t="n">
-        <v>21</v>
+        <v>24.7</v>
       </c>
       <c r="S64" t="n">
-        <v>21</v>
+        <v>19.4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>21</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>LDU de Quito</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="F65" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
       <c r="G65" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6449,75 +6449,75 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>196</v>
+        <v>69</v>
       </c>
       <c r="R65" t="n">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="S65" t="n">
-        <v>20.9</v>
+        <v>36.2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부/역배</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lokomotíva Zvolen</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Slovan Bratislava II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="F66" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G66" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6532,75 +6532,75 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="R66" t="n">
-        <v>20.9</v>
+        <v>24.5</v>
       </c>
       <c r="S66" t="n">
-        <v>20.9</v>
+        <v>15.1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>20.9</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NK Varazdin</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HNK Rijeka</t>
+          <t>Beerschot VA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="F67" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="G67" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6635,22 +6635,22 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="R67" t="n">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
       <c r="S67" t="n">
-        <v>16.7</v>
+        <v>25.2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6658,42 +6658,42 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>20.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>St. Truiden</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Anderlecht</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="F68" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="G68" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6728,22 +6728,22 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="R68" t="n">
-        <v>20.1</v>
+        <v>23.3</v>
       </c>
       <c r="S68" t="n">
-        <v>23.7</v>
+        <v>13.3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6751,42 +6751,42 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>20.1</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Larisa</t>
+          <t>Huracán Res.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>San Lorenzo Res.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="F69" t="n">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="G69" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6821,22 +6821,22 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="R69" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
       <c r="S69" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6844,42 +6844,42 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FH hafnarfjordur</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Valur Reykjavik</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="F70" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="G70" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6914,22 +6914,22 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="R70" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
       <c r="S70" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6937,52 +6937,52 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baroka FC</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Gomora United FC</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="F71" t="n">
-        <v>2.77</v>
+        <v>3.32</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6997,75 +6997,75 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="R71" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Petržalka</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Baník Lehota p.Vtáčnikom</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.56</v>
+        <v>2.07</v>
       </c>
       <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
         <v>3.8</v>
       </c>
-      <c r="G72" t="n">
-        <v>4.8</v>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7100,22 +7100,22 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="R72" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="S72" t="n">
-        <v>12.2</v>
+        <v>21.5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7123,38 +7123,38 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FK Sokol Saratov</t>
+          <t>Van</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Enisey</t>
+          <t>BKMA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.2</v>
+        <v>2.07</v>
       </c>
       <c r="F73" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="G73" t="n">
-        <v>1.93</v>
+        <v>3.18</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7198,60 +7198,60 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>67</v>
+        <v>219</v>
       </c>
       <c r="R73" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="S73" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U73" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>PSM Makassar</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="F74" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="G74" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="R74" t="n">
-        <v>19.2</v>
+        <v>21.5</v>
       </c>
       <c r="S74" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7309,57 +7309,57 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>19.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:06</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sporting San Jose</t>
+          <t>Club Tijuana</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Municipal Liberia</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.92</v>
+        <v>2.86</v>
       </c>
       <c r="F75" t="n">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="G75" t="n">
-        <v>3.56</v>
+        <v>2.26</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1 : 2(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7369,90 +7369,90 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="R75" t="n">
-        <v>18.3</v>
+        <v>21.2</v>
       </c>
       <c r="S75" t="n">
-        <v>18.3</v>
+        <v>20.5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>18.3</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Barracas Central Res.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Deportivo Riestra Res.</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="F76" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="G76" t="n">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>0 : 0(0 : 0)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7472,22 +7472,22 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q76" t="n">
-        <v>105</v>
+        <v>237</v>
       </c>
       <c r="R76" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="S76" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7495,38 +7495,38 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FK Neftekhimik</t>
+          <t>Talleres Córdoba Res.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Chernomorets</t>
+          <t>Belgrano Córdoba Res.</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>2.01</v>
       </c>
       <c r="F77" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="G77" t="n">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7570,17 +7570,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R77" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="S77" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7588,57 +7588,57 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="F78" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="G78" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>3 : 2(2 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7658,22 +7658,22 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="R78" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="S78" t="n">
-        <v>28.1</v>
+        <v>15.3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7681,54 +7681,54 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ferizaj</t>
+          <t>Al Quwa Al Jawiya</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Llapi</t>
+          <t>Erbil</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="F79" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="G79" t="n">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -7751,22 +7751,22 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q79" t="n">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="R79" t="n">
-        <v>18.1</v>
+        <v>20.7</v>
       </c>
       <c r="S79" t="n">
-        <v>18.1</v>
+        <v>20.7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7774,42 +7774,42 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>18.1</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="F80" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="G80" t="n">
-        <v>3.08</v>
+        <v>3.98</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R80" t="n">
-        <v>15</v>
+        <v>20.7</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20.7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7867,42 +7867,42 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>15</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="F81" t="n">
-        <v>3.52</v>
+        <v>2.84</v>
       </c>
       <c r="G81" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0 : 1(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7937,22 +7937,22 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="R81" t="n">
-        <v>14.5</v>
+        <v>20.1</v>
       </c>
       <c r="S81" t="n">
-        <v>26.3</v>
+        <v>25.4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7960,38 +7960,38 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>14.5</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>RB Bragantino</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ska-khabarovsk</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="F82" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="G82" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>3 : 1(2 : 1)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8035,17 +8035,17 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R82" t="n">
-        <v>13.8</v>
+        <v>20</v>
       </c>
       <c r="S82" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8053,54 +8053,54 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>13.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US Tataouine</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CS Hammam-Lif</t>
+          <t>Olmaliq</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="F83" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="G83" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -8123,22 +8123,22 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q83" t="n">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="R83" t="n">
-        <v>12.2</v>
+        <v>19.5</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8146,42 +8146,42 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>12.2</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Sepsi OSK Sfantu Gheorghe</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3.48</v>
+        <v>2.97</v>
       </c>
       <c r="F84" t="n">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="G84" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8216,22 +8216,22 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R84" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="S84" t="n">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8239,13 +8239,13 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8255,22 +8255,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlton</t>
+          <t>VfB Stuttgart</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>SC Freiburg</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>1.64</v>
       </c>
       <c r="F85" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="G85" t="n">
-        <v>1.68</v>
+        <v>5.25</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -8284,12 +8284,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0 : 2(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8314,56 +8314,56 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="R85" t="n">
-        <v>10.8</v>
+        <v>18.4</v>
       </c>
       <c r="S85" t="n">
-        <v>10.8</v>
+        <v>18.4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U85" t="n">
-        <v>10.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Akhmat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="F86" t="n">
-        <v>3.74</v>
+        <v>3.16</v>
       </c>
       <c r="G86" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8407,72 +8407,72 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="R86" t="n">
-        <v>8.6</v>
+        <v>15.8</v>
       </c>
       <c r="S86" t="n">
-        <v>8.6</v>
+        <v>15.8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U86" t="n">
-        <v>8.6</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Club America</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3.32</v>
+        <v>1.97</v>
       </c>
       <c r="F87" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="G87" t="n">
-        <v>2.14</v>
+        <v>3.34</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -8485,85 +8485,85 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="Q87" t="n">
-        <v>12</v>
+        <v>239</v>
       </c>
       <c r="R87" t="n">
-        <v>8.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="S87" t="n">
-        <v>8.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U87" t="n">
-        <v>8.300000000000001</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="F88" t="n">
-        <v>2.89</v>
+        <v>3.58</v>
       </c>
       <c r="G88" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8588,75 +8588,75 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="S88" t="n">
-        <v>36.4</v>
+        <v>14.6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Sharjah FC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dunajska Streda</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="F89" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="G89" t="n">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8671,83 +8671,87 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Club Queretaro</t>
+          <t>Randers FC</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>FC Fredericia</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="F90" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="G90" t="n">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -8760,122 +8764,941 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>173</v>
+      </c>
+      <c r="R90" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="S90" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>분석중</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Betting Tips - Wednesday, 22 April 2026</t>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Duhok</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Gharraf</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>21</v>
+      </c>
+      <c r="R91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>21</v>
+      </c>
+      <c r="R92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Celaya</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Cimarrones</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>71</v>
+      </c>
+      <c r="R93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Vllaznia Shkodër</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Dinamo Tirana</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>45</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="S94" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>00:30</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Vasco DA Gama</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F91" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>33</v>
+      </c>
+      <c r="R95" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
         <v>1.75</v>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0:4</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
+      <c r="F96" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>33</v>
+      </c>
+      <c r="R96" t="n">
+        <v>3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>3</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Dinamo Makhachkala</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>오버</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>12</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Thor Akureyri</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fram Reykjavik</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>원정정배</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jacuipense</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>32</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
         <v>1</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="n">
+      <c r="S99" t="n">
         <v>0</v>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Betting Tips - Thursday, 23 April 2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Defensa Y Justicia</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>분석중</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U101"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,36 +526,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Radnicki 1923</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Spartak Zdrepceva KRV</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.28</v>
+        <v>16.5</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>8.699999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>0:4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -580,75 +580,75 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>04</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="R2" t="n">
-        <v>70.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="S2" t="n">
-        <v>9.300000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>70.40000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>Union Plaani</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al-Adalah</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.28</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,75 +673,75 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="R3" t="n">
-        <v>63.6</v>
+        <v>62.2</v>
       </c>
       <c r="S3" t="n">
-        <v>9.1</v>
+        <v>5.4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>63.6</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Persija Jakarta</t>
+          <t>VPS II</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.23</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>12.25</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -766,173 +766,173 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
       <c r="S4" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Budapest Honved</t>
+          <t>Independiente Medellín W</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Soroksar</t>
+          <t>Once Caldas W</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="F5" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="G5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2 : 0(0 : 0)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>미결</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>73</v>
+      </c>
+      <c r="R5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="S5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4:0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>109</v>
-      </c>
-      <c r="R5" t="n">
-        <v>55</v>
-      </c>
-      <c r="S5" t="n">
-        <v>12.8</v>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>55</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Javor</t>
+          <t>Al Khaleej Saihat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>1.42</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="G6" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="R6" t="n">
-        <v>52.4</v>
+        <v>55.8</v>
       </c>
       <c r="S6" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -985,42 +985,42 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>52.4</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khalidiya</t>
+          <t>Al-Hilal Saudi FC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Hidd</t>
+          <t>Damac</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="F7" t="n">
-        <v>4.85</v>
+        <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>10.75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1055,22 +1055,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="R7" t="n">
-        <v>48.1</v>
+        <v>55.8</v>
       </c>
       <c r="S7" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1078,42 +1078,42 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>48.1</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Universidad Catolica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1138,46 +1138,46 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="R8" t="n">
-        <v>47.4</v>
+        <v>53.4</v>
       </c>
       <c r="S8" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>47.4</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1187,26 +1187,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Al Jandal</t>
+          <t>Al Bukayriyah</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.25</v>
+        <v>1.7</v>
       </c>
       <c r="F9" t="n">
         <v>3.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>4.15</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1231,90 +1231,90 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="R9" t="n">
-        <v>47.4</v>
+        <v>53.4</v>
       </c>
       <c r="S9" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>47.4</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palmeiras W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Santos W</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="G10" t="n">
         <v>7.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3 : 0(2 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1334,22 +1334,22 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="R10" t="n">
-        <v>47</v>
+        <v>52.7</v>
       </c>
       <c r="S10" t="n">
-        <v>18.1</v>
+        <v>15.8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1357,52 +1357,52 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>47</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Provincial Ovalle</t>
+          <t>IFK Norrkoping</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Santiago City</t>
+          <t>Landskrona BoIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="F11" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>5.25</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1427,22 +1427,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>51.6</v>
       </c>
       <c r="S11" t="n">
-        <v>18.1</v>
+        <v>10.9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1450,42 +1450,42 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>47</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IF Elfsborg</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.57</v>
+        <v>1.36</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="G12" t="n">
-        <v>2.78</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1 : 1(1 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="R12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="S12" t="n">
-        <v>18.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1543,57 +1543,57 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bochum II</t>
+          <t>SalPa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach II</t>
+          <t>Turku PS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.21</v>
+        <v>5.65</v>
       </c>
       <c r="F13" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2 : 1(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1603,46 +1603,46 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="S13" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1652,41 +1652,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Atlantis</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Honka</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>1.23</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3 : 0(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1696,75 +1696,75 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="R14" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="S14" t="n">
-        <v>14.8</v>
+        <v>12.5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bashkimi Kumanovo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.07</v>
+        <v>3.02</v>
       </c>
       <c r="F15" t="n">
-        <v>7.7</v>
+        <v>2.96</v>
       </c>
       <c r="G15" t="n">
-        <v>19.5</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1789,71 +1789,71 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="R15" t="n">
-        <v>45.3</v>
+        <v>46.1</v>
       </c>
       <c r="S15" t="n">
-        <v>14.1</v>
+        <v>11.3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>45.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Hednesford Town</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Stockton Town</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>3.68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1897,17 +1897,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="R16" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="S16" t="n">
-        <v>18.6</v>
+        <v>5.7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1915,52 +1915,52 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Malkiya</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1975,85 +1975,85 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="R17" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
       <c r="S17" t="n">
-        <v>12.6</v>
+        <v>20.9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Gharraf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Minaa Basra</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.33</v>
+        <v>2.01</v>
       </c>
       <c r="F18" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>3.04</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2068,75 +2068,75 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="R18" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
       <c r="S18" t="n">
-        <v>12.6</v>
+        <v>20.9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIL Vicente</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="F19" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="G19" t="n">
-        <v>5.7</v>
+        <v>3.92</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="R19" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="S19" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2194,42 +2194,42 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gjøvik-Lyn</t>
+          <t>Gimnasia La Plata Res.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sandefjord II</t>
+          <t>Tigre Res.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="F20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G20" t="n">
         <v>4.2</v>
       </c>
-      <c r="G20" t="n">
-        <v>3.94</v>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>9 : 0(6 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="R20" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="S20" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2287,52 +2287,52 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Duhail SC</t>
+          <t>Surkhon</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.82</v>
+        <v>1.91</v>
       </c>
       <c r="F21" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72</v>
+        <v>3.62</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2347,75 +2347,75 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R21" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="S21" t="n">
-        <v>13.5</v>
+        <v>19.4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="F22" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2440,36 +2440,36 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="R22" t="n">
         <v>42.9</v>
       </c>
       <c r="S22" t="n">
-        <v>19</v>
+        <v>14.3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -2479,48 +2479,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Inter San Carlos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Pitbulls Santa Barbara FC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="G23" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>2:1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -2543,22 +2543,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q23" t="n">
-        <v>172</v>
+        <v>319</v>
       </c>
       <c r="R23" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="S23" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2566,52 +2566,52 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Portimonense U23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Farense U23</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.44</v>
+        <v>3.38</v>
       </c>
       <c r="F24" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2626,71 +2626,71 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="R24" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="S24" t="n">
-        <v>20.7</v>
+        <v>18.7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U24" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Génesis</t>
+          <t>Torreense U23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sporting Braga U23</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="F25" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="G25" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R25" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="S25" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2752,47 +2752,47 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tapatío</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="F26" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>0 : 1(0 : 0)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2831,13 +2831,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="R26" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
       <c r="S26" t="n">
-        <v>18.6</v>
+        <v>23.4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2845,52 +2845,52 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>LDU de Quito</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="F27" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="G27" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2915,22 +2915,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>322</v>
+        <v>37</v>
       </c>
       <c r="R27" t="n">
-        <v>41.9</v>
+        <v>40.5</v>
       </c>
       <c r="S27" t="n">
-        <v>18.6</v>
+        <v>10.8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2938,52 +2938,52 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>41.9</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Kalaâ Sport</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Redeyef</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="F28" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>3.72</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3008,22 +3008,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="R28" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
       <c r="S28" t="n">
-        <v>17.9</v>
+        <v>19.9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3031,52 +3031,52 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1899 Hoffenheim W</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Koln W</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="F29" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3101,22 +3101,22 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="R29" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
       <c r="S29" t="n">
-        <v>17.9</v>
+        <v>19.9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3124,42 +3124,42 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liège</t>
+          <t>Wiener SC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Retz</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.98</v>
+        <v>1.24</v>
       </c>
       <c r="F30" t="n">
-        <v>3.52</v>
+        <v>5.15</v>
       </c>
       <c r="G30" t="n">
-        <v>2.04</v>
+        <v>8.9</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3184,75 +3184,75 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="R30" t="n">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
       <c r="S30" t="n">
-        <v>18.3</v>
+        <v>20.7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="F31" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
-        <v>3.48</v>
+        <v>2.48</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3277,71 +3277,71 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="R31" t="n">
-        <v>40.7</v>
+        <v>38.5</v>
       </c>
       <c r="S31" t="n">
-        <v>20.3</v>
+        <v>26</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>40.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Bahrain SC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="F32" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1 : 0(1 : 0)</t>
+          <t>1 : 1(1 : 1)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3385,17 +3385,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="R32" t="n">
-        <v>40.5</v>
+        <v>35.8</v>
       </c>
       <c r="S32" t="n">
-        <v>7.1</v>
+        <v>19.4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3403,52 +3403,52 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>40.5</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>East Bengal II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.05</v>
+        <v>1.23</v>
       </c>
       <c r="F33" t="n">
-        <v>3.14</v>
+        <v>5.6</v>
       </c>
       <c r="G33" t="n">
-        <v>3.66</v>
+        <v>8.4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="R33" t="n">
-        <v>40.2</v>
+        <v>35.6</v>
       </c>
       <c r="S33" t="n">
-        <v>20.5</v>
+        <v>25.4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3496,38 +3496,38 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>40.2</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>Al Zulfi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="F34" t="n">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="G34" t="n">
-        <v>6.8</v>
+        <v>3.48</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="R34" t="n">
-        <v>40.2</v>
+        <v>34.8</v>
       </c>
       <c r="S34" t="n">
-        <v>20.5</v>
+        <v>24.8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3589,52 +3589,52 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>40.2</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Karsiyaka</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ayvalikgucu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="F35" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="G35" t="n">
-        <v>2.17</v>
+        <v>3.22</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3649,75 +3649,75 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="R35" t="n">
-        <v>40</v>
+        <v>34.8</v>
       </c>
       <c r="S35" t="n">
-        <v>25.6</v>
+        <v>18.1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>40</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="F36" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="G36" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1 : 0(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3742,85 +3742,85 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="R36" t="n">
-        <v>40</v>
+        <v>33.9</v>
       </c>
       <c r="S36" t="n">
-        <v>40</v>
+        <v>30.5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>무승부/역배</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>40</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sportivo Carapeguá</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deportivo Santani</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="F37" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="G37" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3835,75 +3835,75 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>39.2</v>
+        <v>33.3</v>
       </c>
       <c r="S37" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>39.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AIK Stockholm</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="F38" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="G38" t="n">
-        <v>2.77</v>
+        <v>2.23</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3 : 0(0 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3928,75 +3928,75 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="R38" t="n">
-        <v>39.2</v>
+        <v>32.9</v>
       </c>
       <c r="S38" t="n">
-        <v>20.8</v>
+        <v>23.5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>39.2</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>America Mineiro W</t>
+          <t>Hemel Hempstead Town</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>São Paulo W</t>
+          <t>Weston-super-Mare</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>16.75</v>
+        <v>2.44</v>
       </c>
       <c r="F39" t="n">
-        <v>7.1</v>
+        <v>3.12</v>
       </c>
       <c r="G39" t="n">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4021,75 +4021,75 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>105</v>
+        <v>322</v>
       </c>
       <c r="R39" t="n">
-        <v>38.1</v>
+        <v>32.9</v>
       </c>
       <c r="S39" t="n">
-        <v>25.7</v>
+        <v>27.3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>38.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="F40" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="G40" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4124,22 +4124,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="R40" t="n">
-        <v>37.7</v>
+        <v>32.9</v>
       </c>
       <c r="S40" t="n">
-        <v>15.9</v>
+        <v>23.5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4147,57 +4147,57 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>37.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UMM Salal</t>
+          <t>Santa Clara U23</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Al Ahli Doha</t>
+          <t>Sporting CP U23</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="F41" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="G41" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>2 : 1(0 : 1)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4207,75 +4207,75 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="R41" t="n">
-        <v>37.5</v>
+        <v>32.7</v>
       </c>
       <c r="S41" t="n">
-        <v>20.8</v>
+        <v>30.9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>37.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.28</v>
+        <v>2.16</v>
       </c>
       <c r="F42" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="G42" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4300,85 +4300,85 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="R42" t="n">
-        <v>37.5</v>
+        <v>32.4</v>
       </c>
       <c r="S42" t="n">
-        <v>20.8</v>
+        <v>27.5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>37.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Estoril U23</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Gil Vicente U23</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="F43" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="G43" t="n">
-        <v>4.33</v>
+        <v>2.09</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4393,85 +4393,85 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="R43" t="n">
-        <v>37.2</v>
+        <v>32.3</v>
       </c>
       <c r="S43" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>37.2</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hammarby Talang</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vasalund</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="F44" t="n">
-        <v>3.82</v>
+        <v>3.28</v>
       </c>
       <c r="G44" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4486,71 +4486,71 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="R44" t="n">
-        <v>35</v>
+        <v>31.6</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>35</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>União Leiria U23</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rio Ave U23</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="F45" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="G45" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4594,17 +4594,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="R45" t="n">
-        <v>34.5</v>
+        <v>31</v>
       </c>
       <c r="S45" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>34.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4628,26 +4628,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Al Anwar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Al Ula</t>
+          <t>Al-Fateh</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.85</v>
+        <v>1.7</v>
       </c>
       <c r="F46" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="G46" t="n">
-        <v>1.42</v>
+        <v>3.74</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0 : 1(0 : 0)</t>
+          <t>1 : 1(1 : 1)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4672,85 +4672,85 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="R46" t="n">
-        <v>34.4</v>
+        <v>30.8</v>
       </c>
       <c r="S46" t="n">
-        <v>21.1</v>
+        <v>15.4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>34.4</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Marítimo U23</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ypiranga-RS</t>
+          <t>Estrela U23</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.81</v>
+        <v>2.81</v>
       </c>
       <c r="F47" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="G47" t="n">
-        <v>4.55</v>
+        <v>2.17</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4765,90 +4765,90 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R47" t="n">
-        <v>34.3</v>
+        <v>29.2</v>
       </c>
       <c r="S47" t="n">
-        <v>34.3</v>
+        <v>20.8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>34.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Newell's Old Boys Res.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Central Córdoba SdE Res.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="F48" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="G48" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>1 : 1(0 : 0)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="R48" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="S48" t="n">
-        <v>28.9</v>
+        <v>15.9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4891,52 +4891,52 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Benfica U23</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Famalicão U23</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.98</v>
+        <v>2.16</v>
       </c>
       <c r="F49" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="G49" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4951,71 +4951,71 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="R49" t="n">
-        <v>33.8</v>
+        <v>24.8</v>
       </c>
       <c r="S49" t="n">
-        <v>20.8</v>
+        <v>15.9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>33.8</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Buxton</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AL Masry</t>
+          <t>Scarborough Athletic</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.18</v>
+        <v>1.78</v>
       </c>
       <c r="F50" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="G50" t="n">
-        <v>2.42</v>
+        <v>3.92</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5059,70 +5059,70 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R50" t="n">
-        <v>33.8</v>
+        <v>23.1</v>
       </c>
       <c r="S50" t="n">
-        <v>20.8</v>
+        <v>17.9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>33.8</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Arema FC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Club Deportivo Los Chankas</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="F51" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="G51" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5147,22 +5147,22 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="R51" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="S51" t="n">
-        <v>31.5</v>
+        <v>22.7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5170,42 +5170,42 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Molinos El Pirata</t>
+          <t>Bahia W</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cesar Vallejo</t>
+          <t>Gremio W</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.12</v>
+        <v>1.93</v>
       </c>
       <c r="F52" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G52" t="n">
-        <v>2.02</v>
+        <v>3.32</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>2 : 2(0 : 2)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5230,90 +5230,90 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="R52" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
       <c r="S52" t="n">
-        <v>27.8</v>
+        <v>22.8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U52" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="F53" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="G53" t="n">
-        <v>5.55</v>
+        <v>1.94</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1 : 1(1 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5323,71 +5323,71 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>328</v>
+        <v>60</v>
       </c>
       <c r="R53" t="n">
-        <v>32.6</v>
+        <v>21.7</v>
       </c>
       <c r="S53" t="n">
-        <v>26.8</v>
+        <v>13.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>32.6</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Eskişehirspor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Balıkesirspor</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="F54" t="n">
-        <v>3.08</v>
+        <v>4.85</v>
       </c>
       <c r="G54" t="n">
-        <v>3.04</v>
+        <v>9.4</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>328</v>
+        <v>37</v>
       </c>
       <c r="R54" t="n">
-        <v>32.6</v>
+        <v>21.6</v>
       </c>
       <c r="S54" t="n">
-        <v>26.8</v>
+        <v>18.9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5449,42 +5449,42 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>32.6</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="F55" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="G55" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>328</v>
+        <v>127</v>
       </c>
       <c r="R55" t="n">
-        <v>32.6</v>
+        <v>21.3</v>
       </c>
       <c r="S55" t="n">
-        <v>26.8</v>
+        <v>19.7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5542,52 +5542,52 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>32.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>HPS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.85</v>
+        <v>18.75</v>
       </c>
       <c r="F56" t="n">
-        <v>3.34</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5602,75 +5602,75 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>20</v>
       </c>
       <c r="S56" t="n">
-        <v>26.8</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U56" t="n">
-        <v>32.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Sarmiento Res.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Guarani Campinas</t>
+          <t>River Plate Res.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="F57" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="G57" t="n">
-        <v>2.29</v>
+        <v>1.69</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5705,22 +5705,22 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="R57" t="n">
-        <v>32.2</v>
+        <v>20</v>
       </c>
       <c r="S57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5728,57 +5728,57 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>32.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Internacional de Bogota</t>
+          <t>Mount Pleasant Academy</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chico</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="F58" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="G58" t="n">
-        <v>6.3</v>
+        <v>4.25</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1 : 0(0 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5798,22 +5798,22 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>88</v>
+        <v>232</v>
       </c>
       <c r="R58" t="n">
-        <v>31.8</v>
+        <v>19.8</v>
       </c>
       <c r="S58" t="n">
-        <v>23.9</v>
+        <v>19.8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5821,42 +5821,42 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>31.8</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Al-Raed</t>
+          <t>Libertad Asuncion</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Al-Faisaly FC</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="F59" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="G59" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>3 : 2(2 : 0)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5900,71 +5900,71 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="R59" t="n">
-        <v>30</v>
+        <v>19.6</v>
       </c>
       <c r="S59" t="n">
-        <v>22.5</v>
+        <v>18.6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U59" t="n">
-        <v>30</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="F60" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="G60" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>1 : 2(1 : 0)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5984,22 +5984,22 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="R60" t="n">
-        <v>29.6</v>
+        <v>19.3</v>
       </c>
       <c r="S60" t="n">
-        <v>22.6</v>
+        <v>18.6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6007,38 +6007,38 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>29.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lyn II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Elverum</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="F61" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="G61" t="n">
-        <v>1.61</v>
+        <v>4.6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -6052,12 +6052,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>9 : 0(6 : 0)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6082,60 +6082,60 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="R61" t="n">
-        <v>28.6</v>
+        <v>18.7</v>
       </c>
       <c r="S61" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U61" t="n">
-        <v>28.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HNK Gorica</t>
+          <t>Academico Viseu U23</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Leixões U23</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="F62" t="n">
-        <v>3.36</v>
+        <v>4.15</v>
       </c>
       <c r="G62" t="n">
-        <v>3.88</v>
+        <v>5.5</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="R62" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>18.3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6193,42 +6193,42 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cruzeiro U20</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nautico Recife</t>
+          <t>Palmeiras U20</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="G63" t="n">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1 : 2(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6253,75 +6253,75 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R63" t="n">
-        <v>25</v>
+        <v>17.4</v>
       </c>
       <c r="S63" t="n">
-        <v>28.6</v>
+        <v>13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>25</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.8</v>
+        <v>2.29</v>
       </c>
       <c r="F64" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="G64" t="n">
-        <v>2.08</v>
+        <v>2.94</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6346,75 +6346,75 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="R64" t="n">
-        <v>23.5</v>
+        <v>15.9</v>
       </c>
       <c r="S64" t="n">
-        <v>23.5</v>
+        <v>13.6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>23.5</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>FK Liepaja</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FH hafnarfjordur</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="F65" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="G65" t="n">
-        <v>4.8</v>
+        <v>5.65</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6449,22 +6449,22 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="R65" t="n">
-        <v>22.6</v>
+        <v>13.5</v>
       </c>
       <c r="S65" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6472,42 +6472,42 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>22.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlético Tembetary</t>
+          <t>Votuporanguense</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3 de Noviembre</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="F66" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="G66" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6542,22 +6542,22 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>124</v>
+        <v>259</v>
       </c>
       <c r="R66" t="n">
-        <v>21.8</v>
+        <v>13.5</v>
       </c>
       <c r="S66" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6565,42 +6565,42 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>21.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>NEOM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al-Hazm</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="F67" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="G67" t="n">
-        <v>3.52</v>
+        <v>5</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>3 : 2(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6635,22 +6635,22 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="R67" t="n">
-        <v>21.7</v>
+        <v>12.4</v>
       </c>
       <c r="S67" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6658,38 +6658,38 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>21.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Defensa y Justicia Res.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Estudiantes La Plata Res</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="F68" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="G68" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6703,12 +6703,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0 : 3(0 : 2)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6733,17 +6733,17 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="R68" t="n">
-        <v>21.2</v>
+        <v>10.6</v>
       </c>
       <c r="S68" t="n">
-        <v>21.2</v>
+        <v>10.6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6751,42 +6751,42 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>21.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Radnicki NIS</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="F69" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="G69" t="n">
-        <v>3.88</v>
+        <v>2.85</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>0 : 1(0 : 1)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6821,22 +6821,22 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="R69" t="n">
-        <v>19.9</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>24.1</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6844,42 +6844,42 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>19.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>United of Manchester</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Rylands</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="F70" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="G70" t="n">
-        <v>5.1</v>
+        <v>3.42</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>1 : 0(1 : 0)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6914,22 +6914,22 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="R70" t="n">
-        <v>19.9</v>
+        <v>2.8</v>
       </c>
       <c r="S70" t="n">
-        <v>24.1</v>
+        <v>2.8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6937,52 +6937,52 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>19.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Johor Darul Takzim FC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.65</v>
+        <v>32</v>
       </c>
       <c r="F71" t="n">
-        <v>2.77</v>
+        <v>10.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.67</v>
+        <v>1.02</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6997,46 +6997,46 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7046,26 +7046,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>A'Ali</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Sitra</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="F72" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="G72" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7090,90 +7090,90 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>213</v>
+        <v>19</v>
       </c>
       <c r="R72" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>20.2</v>
+        <v>10.5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U72" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fram Reykjavik</t>
+          <t>Levadia U19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>IBV Vestmannaeyjar</t>
+          <t>Tartu Kalev</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="F73" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="G73" t="n">
-        <v>3.52</v>
+        <v>2.03</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>7 : 0(4 : 0)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7183,85 +7183,85 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>213</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U73" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TSC Backa Topola</t>
+          <t>Töölön Taisto</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>JäPS</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.59</v>
+        <v>22</v>
       </c>
       <c r="F74" t="n">
-        <v>3.54</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>5.05</v>
+        <v>1.05</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7276,87 +7276,87 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="R74" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>GBK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FF Jaro</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.65</v>
+        <v>32</v>
       </c>
       <c r="F75" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>1:2</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -7369,85 +7369,85 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Q75" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
+          <t>Betting Tips - Tuesday, 28 April 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>PEPO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PSM Makassar</t>
+          <t>JJK</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7462,2364 +7462,33 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>76</v>
-      </c>
-      <c r="R76" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="S76" t="n">
-        <v>14.5</v>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>분석중</t>
         </is>
       </c>
       <c r="U76" t="n">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>FK Vozdovac</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Zemun</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="G77" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>233</v>
-      </c>
-      <c r="R77" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="S77" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U77" t="n">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Metaloglobus</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Unirea Slobozia</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F78" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="G78" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>77</v>
-      </c>
-      <c r="R78" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S78" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U78" t="n">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Central Ballester</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>El Porvenir</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F79" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G79" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>212</v>
-      </c>
-      <c r="R79" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S79" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U79" t="n">
-        <v>19.3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Bogota FC</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Union Magdalena</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="F80" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>162</v>
-      </c>
-      <c r="R80" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U80" t="n">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Al-Rayyan SC</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Al-Arabi SC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F81" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>184</v>
-      </c>
-      <c r="R81" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S81" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U81" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Zamalek SC</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Enppi</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="F82" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="G82" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>1 : 0(0 : 0)</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>184</v>
-      </c>
-      <c r="R82" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U82" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Çorluspor 1947</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Bursa Yıldırımspor</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F83" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="G83" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>34</v>
-      </c>
-      <c r="R83" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S83" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U83" t="n">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Montana</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Dobrudzha</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F84" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>0:1</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>23</v>
-      </c>
-      <c r="R84" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S84" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U84" t="n">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Zorya Luhansk</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Veres Rivne</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="F85" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G85" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>183</v>
-      </c>
-      <c r="R85" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S85" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Septemvri Sofia</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="F86" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="G86" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>256</v>
-      </c>
-      <c r="R86" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S86" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U86" t="n">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>BFC Daugavpils</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Super Nova</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="G87" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>102</v>
-      </c>
-      <c r="R87" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S87" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U87" t="n">
-        <v>12.7</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Progreso</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G88" t="n">
-        <v>4</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>119</v>
-      </c>
-      <c r="R88" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S88" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Egersund</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Ranheim</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="F89" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>18</v>
-      </c>
-      <c r="R89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Stjarnan</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Valur Reykjavik</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="F90" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G90" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>187</v>
-      </c>
-      <c r="R90" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U90" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Al Sadd</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Al Shamal</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F91" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G91" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>187</v>
-      </c>
-      <c r="R91" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U91" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Al Wakrah</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Al-Sailiya</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F92" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="G92" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>57</v>
-      </c>
-      <c r="R92" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S92" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U92" t="n">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Beerschot VA</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Patro Eisden</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F93" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="G93" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2 : 1(1 : 0)</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>31</v>
-      </c>
-      <c r="R93" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S93" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>9.699999999999999</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Balestier Khalsa</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Hougang United</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F94" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>13</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S94" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U94" t="n">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Pyramids FC</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Al Ahly</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F95" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G95" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>49</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="S95" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Jong Aruba</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Estrella</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="F96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>3:4</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>1</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Vikingur Reykjavik</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>IA Akranes</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F97" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G97" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>2:3</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>3 : 2(1 : 1)</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>2</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="n">
-        <v>50</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Thor Akureyri</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F98" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="G98" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2 : 0(2 : 0)</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>8</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>50</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Sporting Ben Arous</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Mégrine</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F99" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>3:4</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Sabah FA</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Karvan</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F100" t="n">
-        <v>9</v>
-      </c>
-      <c r="G100" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>3:0</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>1</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 27 April 2026</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Juticalpa</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Lobos Upnfm</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="F101" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>5</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>40</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>무승부/역배</t>
-        </is>
-      </c>
-      <c r="U101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,46 +526,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Khalidiya</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Muharraq</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="F2" t="n">
-        <v>2.91</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.18</v>
+        <v>1.35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -580,46 +580,46 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>54.1</v>
+        <v>66.7</v>
       </c>
       <c r="S2" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>54.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -629,26 +629,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FK Liepaja</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AFC Hermannstadt</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6.8</v>
+        <v>1.33</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>6.85</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1:5</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,87 +673,87 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="R3" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rapperswil</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="G4" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>3:0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -776,22 +776,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="R4" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="S4" t="n">
-        <v>16.3</v>
+        <v>10.8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -799,42 +799,42 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>41</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="R5" t="n">
-        <v>49.7</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>16.3</v>
+        <v>7.4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -892,42 +892,42 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>49.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Racing Club Res.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Vélez Sársfield Res.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.65</v>
+        <v>2.62</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -985,52 +985,52 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slask Wroclaw</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.89</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="G7" t="n">
-        <v>3.44</v>
+        <v>1.29</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,75 +1045,75 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>03</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>43.3</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
-        <v>13.4</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>43.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIL Vicente</t>
+          <t>Gwangju FC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.68</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7</v>
+        <v>1.37</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1138,90 +1138,90 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>41.6</v>
+        <v>44.4</v>
       </c>
       <c r="S8" t="n">
-        <v>15.4</v>
+        <v>22.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>41.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RB Leipzig W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen W</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.95</v>
+        <v>1.26</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>11.25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>1 : 0(0 : 0)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1231,85 +1231,85 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="S9" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Ahli Jeddah</t>
+          <t>Al Okhdood</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.85</v>
+        <v>1.48</v>
       </c>
       <c r="F10" t="n">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73</v>
+        <v>5.15</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1324,85 +1324,85 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="S10" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="F11" t="n">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1427,22 +1427,22 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>181</v>
+        <v>97</v>
       </c>
       <c r="R11" t="n">
-        <v>40.3</v>
+        <v>41.2</v>
       </c>
       <c r="S11" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1450,52 +1450,52 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>40.3</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Servette FC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.24</v>
+        <v>1.82</v>
       </c>
       <c r="F12" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1510,85 +1510,85 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="R12" t="n">
-        <v>39.5</v>
+        <v>41.2</v>
       </c>
       <c r="S12" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>39.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cracovia Krakow</t>
+          <t>Palmeiras W</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Atlético Mineiro W</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="F13" t="n">
-        <v>3.34</v>
+        <v>6.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.82</v>
+        <v>14.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>39.3</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>20.1</v>
+        <v>15.6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1636,42 +1636,42 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>39.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Internacional Palmira</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>LDU de Quito</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
       <c r="F14" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="G14" t="n">
-        <v>3.54</v>
+        <v>2.33</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1696,85 +1696,85 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>234</v>
+        <v>153</v>
       </c>
       <c r="R14" t="n">
-        <v>39.3</v>
+        <v>40.5</v>
       </c>
       <c r="S14" t="n">
-        <v>20.1</v>
+        <v>10.5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>39.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Al-Jazira</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al-Wasl FC</t>
+          <t>Kryvbas KR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="F15" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="G15" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1789,85 +1789,85 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="R15" t="n">
-        <v>38.6</v>
+        <v>40.4</v>
       </c>
       <c r="S15" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>38.6</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Molinos El Pirata</t>
+          <t>Domagnano</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Academia Cantolao</t>
+          <t>Virtus</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="F16" t="n">
-        <v>3.32</v>
+        <v>4.85</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1882,85 +1882,85 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>233</v>
+        <v>97</v>
       </c>
       <c r="R16" t="n">
-        <v>38.6</v>
+        <v>40.2</v>
       </c>
       <c r="S16" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>38.6</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Panetolikos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Larisa</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.18</v>
+        <v>2.31</v>
       </c>
       <c r="F17" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>13.25</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1985,22 +1985,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>351</v>
+        <v>184</v>
       </c>
       <c r="R17" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
       </c>
       <c r="S17" t="n">
-        <v>17.4</v>
+        <v>16.3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2008,52 +2008,52 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>El Gouna FC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="F18" t="n">
-        <v>3.92</v>
+        <v>2.83</v>
       </c>
       <c r="G18" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2078,22 +2078,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>351</v>
+        <v>184</v>
       </c>
       <c r="R18" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
       </c>
       <c r="S18" t="n">
-        <v>17.4</v>
+        <v>16.3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2101,38 +2101,38 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>38.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.53</v>
+        <v>1.12</v>
       </c>
       <c r="F19" t="n">
-        <v>3.38</v>
+        <v>6.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.94</v>
+        <v>14.25</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>371</v>
+        <v>184</v>
       </c>
       <c r="R19" t="n">
-        <v>38.3</v>
+        <v>39.7</v>
       </c>
       <c r="S19" t="n">
-        <v>22.1</v>
+        <v>16.3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2194,52 +2194,52 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>38.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2264,22 +2264,22 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>371</v>
+        <v>234</v>
       </c>
       <c r="R20" t="n">
-        <v>38.3</v>
+        <v>39.3</v>
       </c>
       <c r="S20" t="n">
-        <v>22.1</v>
+        <v>20.1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2287,52 +2287,52 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>38.3</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SC Braga</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="F21" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="R21" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2380,42 +2380,42 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="F22" t="n">
-        <v>6.3</v>
+        <v>4.33</v>
       </c>
       <c r="G22" t="n">
-        <v>9.9</v>
+        <v>5.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="R22" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
       <c r="S22" t="n">
-        <v>8.300000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2473,38 +2473,38 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.89</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2548,17 +2548,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>129</v>
+        <v>373</v>
       </c>
       <c r="R23" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="S23" t="n">
-        <v>19.4</v>
+        <v>22</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2566,38 +2566,38 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>FC Luzern</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="F24" t="n">
-        <v>3.52</v>
+        <v>4.85</v>
       </c>
       <c r="G24" t="n">
-        <v>3.94</v>
+        <v>5.25</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>129</v>
+        <v>373</v>
       </c>
       <c r="R24" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="S24" t="n">
-        <v>19.4</v>
+        <v>22</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2659,52 +2659,52 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="F25" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="R25" t="n">
-        <v>36.1</v>
+        <v>37.8</v>
       </c>
       <c r="S25" t="n">
-        <v>18.6</v>
+        <v>15.9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2752,42 +2752,42 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>36.1</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shinnik Yaroslavl</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="F26" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2822,22 +2822,22 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>355</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
       <c r="S26" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2845,38 +2845,38 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Al-Khabourah</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="F27" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G27" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2944,36 +2944,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ittihad Kalba U23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Al Nasr U23</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="F28" t="n">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="G28" t="n">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>355</v>
+        <v>40</v>
       </c>
       <c r="R28" t="n">
-        <v>36.1</v>
+        <v>35</v>
       </c>
       <c r="S28" t="n">
-        <v>18.6</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3031,38 +3031,38 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>36.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Artis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="F29" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3106,17 +3106,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>355</v>
+        <v>106</v>
       </c>
       <c r="R29" t="n">
-        <v>36.1</v>
+        <v>32.1</v>
       </c>
       <c r="S29" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3124,57 +3124,57 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>36.1</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Once Caldas W</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Orsomarso W</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.72</v>
+        <v>1.33</v>
       </c>
       <c r="F30" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="G30" t="n">
-        <v>1.87</v>
+        <v>9</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0 : 1(0 : 1)</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3184,75 +3184,75 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="R30" t="n">
-        <v>35.2</v>
+        <v>30</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>35.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nizhny Novgorod</t>
+          <t>Gimnasia La Plata Res.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CSKA Moscow</t>
+          <t>Banfield Res.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.48</v>
+        <v>2.19</v>
       </c>
       <c r="F31" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3277,85 +3277,85 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="R31" t="n">
-        <v>35.2</v>
+        <v>29.9</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>35.2</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Gangwon FC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.5</v>
+        <v>2.13</v>
       </c>
       <c r="F32" t="n">
-        <v>6.35</v>
+        <v>3.18</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22</v>
+        <v>3.48</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0:4</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3370,87 +3370,87 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="R32" t="n">
-        <v>35.1</v>
+        <v>29.6</v>
       </c>
       <c r="S32" t="n">
-        <v>13.5</v>
+        <v>25.9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>35.1</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pusamania Borneo</t>
+          <t>Arda Kardzhali</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.94</v>
+        <v>2.13</v>
       </c>
       <c r="F33" t="n">
-        <v>4.2</v>
+        <v>2.93</v>
       </c>
       <c r="G33" t="n">
-        <v>1.61</v>
+        <v>3.72</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>0:2</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -3463,75 +3463,75 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
           <t>02</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="Q33" t="n">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="R33" t="n">
-        <v>35.1</v>
+        <v>28.8</v>
       </c>
       <c r="S33" t="n">
-        <v>19.5</v>
+        <v>22.7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>35.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dynamo</t>
+          <t>Al-Nassr</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FC Krasnodar</t>
+          <t>Al-Hilal Saudi FC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3.84</v>
+        <v>2.24</v>
       </c>
       <c r="F34" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3556,85 +3556,85 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="R34" t="n">
-        <v>33.3</v>
+        <v>28.8</v>
       </c>
       <c r="S34" t="n">
-        <v>14.7</v>
+        <v>22.7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>33.3</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enisey</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="F35" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="R35" t="n">
-        <v>32.4</v>
+        <v>27.9</v>
       </c>
       <c r="S35" t="n">
-        <v>16.9</v>
+        <v>20.9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3682,54 +3682,54 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>32.4</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Defensores De Belgrano</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.91</v>
+        <v>2.83</v>
       </c>
       <c r="F36" t="n">
-        <v>2.76</v>
+        <v>3.12</v>
       </c>
       <c r="G36" t="n">
-        <v>4.45</v>
+        <v>2.51</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>2:0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -3742,85 +3742,85 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
       <c r="Q36" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
-        <v>32.4</v>
+        <v>27.8</v>
       </c>
       <c r="S36" t="n">
-        <v>20.3</v>
+        <v>11.1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>32.4</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>San Marcos de Arica</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="F37" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="G37" t="n">
-        <v>4.85</v>
+        <v>2.49</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>언더</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3845,22 +3845,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="R37" t="n">
-        <v>32.4</v>
+        <v>25.9</v>
       </c>
       <c r="S37" t="n">
-        <v>20.3</v>
+        <v>11.1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3868,42 +3868,42 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>32.4</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Namdhari</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Gokulam</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.03</v>
+        <v>2.62</v>
       </c>
       <c r="F38" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="G38" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3928,85 +3928,85 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="R38" t="n">
-        <v>31</v>
+        <v>25.5</v>
       </c>
       <c r="S38" t="n">
-        <v>21.5</v>
+        <v>10.6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>31</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FC Rostov</t>
+          <t>Hamilton Academical</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="F39" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="G39" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4031,22 +4031,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="R39" t="n">
-        <v>31</v>
+        <v>21.5</v>
       </c>
       <c r="S39" t="n">
-        <v>19</v>
+        <v>20.7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4054,42 +4054,42 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>31</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="F40" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="G40" t="n">
-        <v>3.88</v>
+        <v>3.22</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4124,22 +4124,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="R40" t="n">
-        <v>31</v>
+        <v>20.5</v>
       </c>
       <c r="S40" t="n">
-        <v>24.3</v>
+        <v>20.5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4147,42 +4147,42 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>31</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grasshoppers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FC Winterthur</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="F41" t="n">
-        <v>3.24</v>
+        <v>3.88</v>
       </c>
       <c r="G41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>342</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
-        <v>31</v>
+        <v>19.4</v>
       </c>
       <c r="S41" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4240,42 +4240,42 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>31</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Mlada Boleslav</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Al-Ittihad Kalba</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="F42" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="G42" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="R42" t="n">
-        <v>30</v>
+        <v>19.4</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4333,38 +4333,38 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>30</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estrela</t>
+          <t>Zagłębie Lubin II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Carina Gubin</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.65</v>
+        <v>1.61</v>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="G43" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4408,70 +4408,70 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="R43" t="n">
-        <v>29.5</v>
+        <v>19.3</v>
       </c>
       <c r="S43" t="n">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>29.5</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Cherno More Varna</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FC WIL 1900</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.89</v>
+        <v>1.94</v>
       </c>
       <c r="F44" t="n">
         <v>3.2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.21</v>
+        <v>3.98</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4486,75 +4486,75 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>51</v>
+        <v>225</v>
       </c>
       <c r="R44" t="n">
-        <v>29.4</v>
+        <v>18.7</v>
       </c>
       <c r="S44" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>29.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Olympique Safi</t>
+          <t>RED Star FC 93</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="F45" t="n">
-        <v>2.9</v>
+        <v>3.92</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4589,22 +4589,22 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="R45" t="n">
-        <v>28.9</v>
+        <v>18.7</v>
       </c>
       <c r="S45" t="n">
-        <v>14.5</v>
+        <v>18.7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4612,52 +4612,52 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>28.9</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malkiya</t>
+          <t>IFK Varnamo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Al Riffa</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.65</v>
+        <v>1.93</v>
       </c>
       <c r="F46" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G46" t="n">
-        <v>1.52</v>
+        <v>3.64</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4672,75 +4672,75 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="R46" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="S46" t="n">
-        <v>23</v>
+        <v>18.7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.78</v>
+        <v>1.63</v>
       </c>
       <c r="F47" t="n">
-        <v>3.74</v>
+        <v>3.12</v>
       </c>
       <c r="G47" t="n">
-        <v>1.72</v>
+        <v>5.65</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4765,85 +4765,85 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="R47" t="n">
-        <v>22</v>
+        <v>18.1</v>
       </c>
       <c r="S47" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>22</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Corinthians W</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Al-Hidd</t>
+          <t>São Paulo W</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.69</v>
+        <v>1.48</v>
       </c>
       <c r="F48" t="n">
-        <v>2.97</v>
+        <v>3.88</v>
       </c>
       <c r="G48" t="n">
-        <v>2.47</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4858,75 +4858,75 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="R48" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
       <c r="S48" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Tre Penne</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>La Fiorita</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="F49" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="G49" t="n">
-        <v>4.15</v>
+        <v>2.62</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4961,22 +4961,22 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>84</v>
+        <v>270</v>
       </c>
       <c r="R49" t="n">
-        <v>21.4</v>
+        <v>17.8</v>
       </c>
       <c r="S49" t="n">
-        <v>16.7</v>
+        <v>18.5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4984,52 +4984,52 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>21.4</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Deportivo Tachira FC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Metropolitanos FC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="F50" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74</v>
+        <v>4.6</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="R50" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="S50" t="n">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5093,26 +5093,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Landskrona BoIS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ODD Ballklubb</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="G51" t="n">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5147,22 +5147,22 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="R51" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5170,42 +5170,42 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Club Guarani</t>
+          <t>Sepsi OSK Sfantu Gheorghe</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="F52" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="G52" t="n">
-        <v>4.15</v>
+        <v>2.68</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5240,22 +5240,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="R52" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="S52" t="n">
-        <v>20.9</v>
+        <v>17.2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5263,47 +5263,47 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlético Tembetary</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deportivo Santani</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="F53" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="G53" t="n">
-        <v>3.62</v>
+        <v>2.35</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5323,17 +5323,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5342,61 +5342,61 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="R53" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
       <c r="S53" t="n">
-        <v>19.1</v>
+        <v>10.3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Zlin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="F54" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="G54" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5435,66 +5435,66 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="R54" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
       <c r="S54" t="n">
-        <v>19.1</v>
+        <v>10.3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madrid CFF W</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="F55" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="G55" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5509,75 +5509,75 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="R55" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="S55" t="n">
-        <v>19.1</v>
+        <v>16.5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>ST Mirren</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="F56" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="G56" t="n">
-        <v>2.53</v>
+        <v>3.24</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="R56" t="n">
-        <v>18.6</v>
+        <v>16.5</v>
       </c>
       <c r="S56" t="n">
-        <v>18.6</v>
+        <v>19.8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5635,38 +5635,38 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>18.6</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spartak Moscow</t>
+          <t>UCV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Rubin</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.56</v>
+        <v>2.78</v>
       </c>
       <c r="F57" t="n">
-        <v>4.25</v>
+        <v>2.99</v>
       </c>
       <c r="G57" t="n">
-        <v>6.35</v>
+        <v>2.39</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5714,27 +5714,27 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>246</v>
+        <v>109</v>
       </c>
       <c r="R57" t="n">
-        <v>18.3</v>
+        <v>16.5</v>
       </c>
       <c r="S57" t="n">
-        <v>18.3</v>
+        <v>16.5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U57" t="n">
-        <v>18.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chernomorets 1919 Burgas</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="F58" t="n">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="G58" t="n">
-        <v>3.96</v>
+        <v>4.9</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5803,17 +5803,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="R58" t="n">
-        <v>18.3</v>
+        <v>16.3</v>
       </c>
       <c r="S58" t="n">
-        <v>18.3</v>
+        <v>16.3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5821,52 +5821,52 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>18.3</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fratria</t>
+          <t>Defensa y Justicia Res.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Platense Res.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.47</v>
+        <v>1.95</v>
       </c>
       <c r="F59" t="n">
-        <v>2.96</v>
+        <v>3.34</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5891,22 +5891,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="R59" t="n">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
       <c r="S59" t="n">
-        <v>13.6</v>
+        <v>16.2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5914,42 +5914,42 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>18.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="F60" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G60" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5974,87 +5974,87 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>268</v>
+        <v>25</v>
       </c>
       <c r="R60" t="n">
-        <v>17.9</v>
+        <v>16</v>
       </c>
       <c r="S60" t="n">
-        <v>18.7</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U60" t="n">
-        <v>17.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Zakho</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Diyala</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="F61" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="G61" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>오버</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2:0</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -6077,22 +6077,22 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="Q61" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="R61" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="S61" t="n">
-        <v>17.2</v>
+        <v>24.5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6100,42 +6100,42 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Randers FC</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Odense</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="F62" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="G62" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="R62" t="n">
-        <v>17.2</v>
+        <v>14.9</v>
       </c>
       <c r="S62" t="n">
-        <v>17.2</v>
+        <v>14.9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6193,38 +6193,38 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>17.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="F63" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="G63" t="n">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6268,72 +6268,72 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="R63" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="S63" t="n">
-        <v>31.6</v>
+        <v>3.7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Flamengo W</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ferroviaria W</t>
+          <t>Future FC</t>
         </is>
       </c>
       <c r="E64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G64" t="n">
         <v>2.32</v>
       </c>
-      <c r="F64" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="G64" t="n">
-        <v>2.69</v>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>0:0</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -6346,71 +6346,71 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="Q64" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="R64" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="S64" t="n">
-        <v>15.2</v>
+        <v>33.3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="F65" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="G65" t="n">
-        <v>4.65</v>
+        <v>3.54</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6454,17 +6454,17 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="R65" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="S65" t="n">
-        <v>27.4</v>
+        <v>24.4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6472,52 +6472,52 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>Escorpiones Belén</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FC Aarau</t>
+          <t>Inter San Carlos</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="F66" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="G66" t="n">
-        <v>2.36</v>
+        <v>3.66</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6532,75 +6532,75 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="R66" t="n">
-        <v>13.9</v>
+        <v>10.1</v>
       </c>
       <c r="S66" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>13.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SOL DE America</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Guairena FC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.15</v>
+        <v>6.9</v>
       </c>
       <c r="F67" t="n">
-        <v>3.16</v>
+        <v>4.75</v>
       </c>
       <c r="G67" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6625,71 +6625,71 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="R67" t="n">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S67" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>13.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bhayangkara FC</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Persepam Madura Utd</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="F68" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84</v>
+        <v>3.54</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6733,17 +6733,17 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>278</v>
+        <v>87</v>
       </c>
       <c r="R68" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="S68" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6751,42 +6751,42 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CS Hammam-Lif</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ES Hammam-Sousse</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="F69" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="G69" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6821,22 +6821,22 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="R69" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="S69" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6844,42 +6844,42 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>12.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>East Bengal II</t>
+          <t>Sport Boys</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.71</v>
+        <v>4.05</v>
       </c>
       <c r="F70" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="G70" t="n">
-        <v>4.15</v>
+        <v>1.93</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6887,11 +6887,7 @@
           <t>언더</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -6904,85 +6900,75 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>187</v>
-      </c>
-      <c r="R70" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S70" t="n">
-        <v>21.4</v>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>분석중</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
+          <t>Betting Tips - Tuesday, 12 May 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Internacional de Bogota</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="F71" t="n">
-        <v>3.36</v>
+        <v>4.45</v>
       </c>
       <c r="G71" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>오버</t>
+          <t>언더</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7007,22 +6993,22 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7030,285 +7016,6 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>NEOM</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Al Shabab</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="F72" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>85</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="S72" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="F73" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>언더</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>3:2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>40</v>
-      </c>
-      <c r="R73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U73" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Betting Tips - Monday, 11 May 2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Maringá</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Guarani Campinas</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F74" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>오버</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>3:3</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>미결</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>6</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="U74" t="n">
         <v>0</v>
       </c>
     </row>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>유사_최고실적</t>
+          <t>유사경기수</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         <v>42.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>67.2</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3">
@@ -744,7 +744,7 @@
         <v>45.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>69</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
         <v>37.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>66.40000000000001</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
@@ -938,7 +938,7 @@
         <v>52.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>85.09999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -1035,7 +1035,7 @@
         <v>48.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>91.40000000000001</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1132,7 +1132,7 @@
         <v>44.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>71.7</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -1229,7 +1229,7 @@
         <v>49.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>84.8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -1326,7 +1326,7 @@
         <v>43.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>69.59999999999999</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -1423,7 +1423,7 @@
         <v>49.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>74.59999999999999</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -1520,7 +1520,7 @@
         <v>38.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>66.40000000000001</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12">
@@ -1617,7 +1617,7 @@
         <v>39.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>66.09999999999999</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13">
@@ -1714,7 +1714,7 @@
         <v>26</v>
       </c>
       <c r="AA13" t="n">
-        <v>71.5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -1811,7 +1811,7 @@
         <v>35.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>67.7</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15">
@@ -1908,7 +1908,7 @@
         <v>42.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>66.59999999999999</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16">
@@ -2005,7 +2005,7 @@
         <v>48.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>70.2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -2102,7 +2102,7 @@
         <v>43.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>69.7</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18">
@@ -2199,7 +2199,7 @@
         <v>44.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>72.5</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19">
@@ -2296,7 +2296,7 @@
         <v>43.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>66.40000000000001</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20">
@@ -2393,7 +2393,7 @@
         <v>53</v>
       </c>
       <c r="AA20" t="n">
-        <v>75.8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -2490,7 +2490,7 @@
         <v>50.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>83.3</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
@@ -2587,7 +2587,7 @@
         <v>43.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>74.2</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23">
@@ -2684,7 +2684,7 @@
         <v>51.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>74</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
@@ -2781,7 +2781,7 @@
         <v>45.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>69.90000000000001</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25">
@@ -2878,7 +2878,7 @@
         <v>54.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>76.90000000000001</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26">
@@ -2975,7 +2975,7 @@
         <v>46.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>71.40000000000001</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27">
@@ -3072,7 +3072,7 @@
         <v>43.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>68.2</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28">
@@ -3169,7 +3169,7 @@
         <v>44.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
@@ -3266,7 +3266,7 @@
         <v>45.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>67</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
@@ -3363,7 +3363,7 @@
         <v>28.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>66.8</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31">
@@ -3460,7 +3460,7 @@
         <v>32.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>62.3</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32">
@@ -3557,7 +3557,7 @@
         <v>34.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>62.8</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33">
@@ -3654,7 +3654,7 @@
         <v>31.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>57.4</v>
+        <v>944</v>
       </c>
     </row>
     <row r="34">
@@ -3751,7 +3751,7 @@
         <v>34.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>61.9</v>
+        <v>749</v>
       </c>
     </row>
     <row r="35">
@@ -3848,7 +3848,7 @@
         <v>31.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>57.6</v>
+        <v>575</v>
       </c>
     </row>
     <row r="36">
@@ -3951,7 +3951,7 @@
         <v>32.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>64.5</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37">
@@ -4048,7 +4048,7 @@
         <v>35.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>61.8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38">
@@ -4145,7 +4145,7 @@
         <v>28.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>56.1</v>
+        <v>715</v>
       </c>
     </row>
     <row r="39">
@@ -4242,7 +4242,7 @@
         <v>35.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>63</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40">
@@ -4339,7 +4339,7 @@
         <v>32.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>57.2</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="41">
@@ -4436,7 +4436,7 @@
         <v>37</v>
       </c>
       <c r="AA41" t="n">
-        <v>63</v>
+        <v>729</v>
       </c>
     </row>
     <row r="42">
@@ -4533,7 +4533,7 @@
         <v>44.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>58.6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
@@ -4630,7 +4630,7 @@
         <v>40.3</v>
       </c>
       <c r="AA43" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44">
@@ -4727,7 +4727,7 @@
         <v>30.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>55.9</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="45">
@@ -4824,7 +4824,7 @@
         <v>34.9</v>
       </c>
       <c r="AA45" t="n">
-        <v>58.6</v>
+        <v>816</v>
       </c>
     </row>
     <row r="46">
@@ -4927,7 +4927,7 @@
         <v>45.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>61.1</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47">
@@ -5030,7 +5030,7 @@
         <v>38.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>62.1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48">
@@ -5127,7 +5127,7 @@
         <v>35.8</v>
       </c>
       <c r="AA48" t="n">
-        <v>60.9</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49">
@@ -5224,7 +5224,7 @@
         <v>39.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>56.2</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50">
@@ -5321,7 +5321,7 @@
         <v>34.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>61.7</v>
+        <v>757</v>
       </c>
     </row>
     <row r="51">
@@ -5418,7 +5418,7 @@
         <v>35.4</v>
       </c>
       <c r="AA51" t="n">
-        <v>61.4</v>
+        <v>823</v>
       </c>
     </row>
     <row r="52">
@@ -5515,7 +5515,7 @@
         <v>36.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>61.6</v>
+        <v>703</v>
       </c>
     </row>
     <row r="53">
@@ -5612,7 +5612,7 @@
         <v>33.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>61.6</v>
+        <v>713</v>
       </c>
     </row>
     <row r="54">
@@ -5709,7 +5709,7 @@
         <v>33.9</v>
       </c>
       <c r="AA54" t="n">
-        <v>60.3</v>
+        <v>879</v>
       </c>
     </row>
     <row r="55">
@@ -5812,7 +5812,7 @@
         <v>36</v>
       </c>
       <c r="AA55" t="n">
-        <v>57.4</v>
+        <v>835</v>
       </c>
     </row>
     <row r="56">
@@ -5915,7 +5915,7 @@
         <v>34.1</v>
       </c>
       <c r="AA56" t="n">
-        <v>57.1</v>
+        <v>592</v>
       </c>
     </row>
     <row r="57">
@@ -6012,7 +6012,7 @@
         <v>31.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>57.7</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58">
@@ -6109,7 +6109,7 @@
         <v>35</v>
       </c>
       <c r="AA58" t="n">
-        <v>61</v>
+        <v>792</v>
       </c>
     </row>
     <row r="59">
@@ -6206,7 +6206,7 @@
         <v>31.5</v>
       </c>
       <c r="AA59" t="n">
-        <v>59.8</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60">
@@ -6303,7 +6303,7 @@
         <v>33.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>56.7</v>
+        <v>649</v>
       </c>
     </row>
     <row r="61">
@@ -6406,7 +6406,7 @@
         <v>37.6</v>
       </c>
       <c r="AA61" t="n">
-        <v>58.5</v>
+        <v>407</v>
       </c>
     </row>
     <row r="62">
@@ -6509,7 +6509,7 @@
         <v>33.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>63.6</v>
+        <v>209</v>
       </c>
     </row>
     <row r="63">
@@ -6606,7 +6606,7 @@
         <v>30.6</v>
       </c>
       <c r="AA63" t="n">
-        <v>55.8</v>
+        <v>627</v>
       </c>
     </row>
     <row r="64">
@@ -6703,7 +6703,7 @@
         <v>28.8</v>
       </c>
       <c r="AA64" t="n">
-        <v>56.1</v>
+        <v>715</v>
       </c>
     </row>
     <row r="65">
@@ -6806,7 +6806,7 @@
         <v>39.6</v>
       </c>
       <c r="AA65" t="n">
-        <v>59.7</v>
+        <v>596</v>
       </c>
     </row>
     <row r="66">
@@ -6909,7 +6909,7 @@
         <v>37.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>61.5</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67">
@@ -7012,7 +7012,7 @@
         <v>36.1</v>
       </c>
       <c r="AA67" t="n">
-        <v>60.9</v>
+        <v>571</v>
       </c>
     </row>
     <row r="68">
@@ -7109,7 +7109,7 @@
         <v>30.4</v>
       </c>
       <c r="AA68" t="n">
-        <v>59.8</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69">
@@ -7212,7 +7212,7 @@
         <v>35.2</v>
       </c>
       <c r="AA69" t="n">
-        <v>58.1</v>
+        <v>744</v>
       </c>
     </row>
     <row r="70">
@@ -7315,7 +7315,7 @@
         <v>38.1</v>
       </c>
       <c r="AA70" t="n">
-        <v>57</v>
+        <v>653</v>
       </c>
     </row>
     <row r="71">
@@ -7418,7 +7418,7 @@
         <v>49.1</v>
       </c>
       <c r="AA71" t="n">
-        <v>63.5</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72">
@@ -7521,7 +7521,7 @@
         <v>40.3</v>
       </c>
       <c r="AA72" t="n">
-        <v>61.9</v>
+        <v>360</v>
       </c>
     </row>
     <row r="73">
@@ -7624,7 +7624,7 @@
         <v>41.7</v>
       </c>
       <c r="AA73" t="n">
-        <v>59.6</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74">
@@ -7721,7 +7721,7 @@
         <v>34.3</v>
       </c>
       <c r="AA74" t="n">
-        <v>60.4</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75">
@@ -7818,7 +7818,7 @@
         <v>34.8</v>
       </c>
       <c r="AA75" t="n">
-        <v>63.1</v>
+        <v>597</v>
       </c>
     </row>
     <row r="76">
@@ -7921,7 +7921,7 @@
         <v>35.1</v>
       </c>
       <c r="AA76" t="n">
-        <v>56.6</v>
+        <v>756</v>
       </c>
     </row>
     <row r="77">
@@ -8018,7 +8018,7 @@
         <v>35.9</v>
       </c>
       <c r="AA77" t="n">
-        <v>61.1</v>
+        <v>785</v>
       </c>
     </row>
     <row r="78">
@@ -8115,7 +8115,7 @@
         <v>31.8</v>
       </c>
       <c r="AA78" t="n">
-        <v>56.8</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="79">
@@ -8212,7 +8212,7 @@
         <v>35.1</v>
       </c>
       <c r="AA79" t="n">
-        <v>59.7</v>
+        <v>812</v>
       </c>
     </row>
     <row r="80">
@@ -8309,7 +8309,7 @@
         <v>36.4</v>
       </c>
       <c r="AA80" t="n">
-        <v>60.8</v>
+        <v>701</v>
       </c>
     </row>
     <row r="81">
@@ -8406,7 +8406,7 @@
         <v>36.2</v>
       </c>
       <c r="AA81" t="n">
-        <v>58.7</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82">
@@ -8503,7 +8503,7 @@
         <v>37.1</v>
       </c>
       <c r="AA82" t="n">
-        <v>62.9</v>
+        <v>693</v>
       </c>
     </row>
     <row r="83">
@@ -8606,7 +8606,7 @@
         <v>39.6</v>
       </c>
       <c r="AA83" t="n">
-        <v>57.6</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84">
@@ -8703,7 +8703,7 @@
         <v>32.9</v>
       </c>
       <c r="AA84" t="n">
-        <v>55.2</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="85">
@@ -8800,7 +8800,7 @@
         <v>29.9</v>
       </c>
       <c r="AA85" t="n">
-        <v>55.4</v>
+        <v>612</v>
       </c>
     </row>
     <row r="86">
@@ -8897,7 +8897,7 @@
         <v>38.5</v>
       </c>
       <c r="AA86" t="n">
-        <v>62.3</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87">
@@ -8994,7 +8994,7 @@
         <v>32.4</v>
       </c>
       <c r="AA87" t="n">
-        <v>55.5</v>
+        <v>679</v>
       </c>
     </row>
     <row r="88">
@@ -9091,7 +9091,7 @@
         <v>38.1</v>
       </c>
       <c r="AA88" t="n">
-        <v>59.2</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89">
@@ -9194,7 +9194,7 @@
         <v>36</v>
       </c>
       <c r="AA89" t="n">
-        <v>59.4</v>
+        <v>561</v>
       </c>
     </row>
     <row r="90">
@@ -9291,7 +9291,7 @@
         <v>43.2</v>
       </c>
       <c r="AA90" t="n">
-        <v>64.59999999999999</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91">
@@ -9388,7 +9388,7 @@
         <v>35.1</v>
       </c>
       <c r="AA91" t="n">
-        <v>59.7</v>
+        <v>812</v>
       </c>
     </row>
     <row r="92">
@@ -9485,7 +9485,7 @@
         <v>35</v>
       </c>
       <c r="AA92" t="n">
-        <v>57.6</v>
+        <v>838</v>
       </c>
     </row>
     <row r="93">
@@ -9582,7 +9582,7 @@
         <v>29</v>
       </c>
       <c r="AA93" t="n">
-        <v>56.8</v>
+        <v>651</v>
       </c>
     </row>
     <row r="94">
@@ -9679,7 +9679,7 @@
         <v>38.8</v>
       </c>
       <c r="AA94" t="n">
-        <v>61.2</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95">
@@ -9776,7 +9776,7 @@
         <v>32.2</v>
       </c>
       <c r="AA95" t="n">
-        <v>57.2</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="96">
@@ -9873,7 +9873,7 @@
         <v>38.8</v>
       </c>
       <c r="AA96" t="n">
-        <v>64.09999999999999</v>
+        <v>641</v>
       </c>
     </row>
     <row r="97">
@@ -9970,7 +9970,7 @@
         <v>34.7</v>
       </c>
       <c r="AA97" t="n">
-        <v>59.8</v>
+        <v>779</v>
       </c>
     </row>
     <row r="98">
@@ -10067,7 +10067,7 @@
         <v>30.9</v>
       </c>
       <c r="AA98" t="n">
-        <v>58.8</v>
+        <v>537</v>
       </c>
     </row>
     <row r="99">
@@ -10164,7 +10164,7 @@
         <v>34.3</v>
       </c>
       <c r="AA99" t="n">
-        <v>60.7</v>
+        <v>760</v>
       </c>
     </row>
     <row r="100">
@@ -10261,7 +10261,7 @@
         <v>33.3</v>
       </c>
       <c r="AA100" t="n">
-        <v>60.6</v>
+        <v>795</v>
       </c>
     </row>
     <row r="101">
@@ -10358,7 +10358,7 @@
         <v>36.8</v>
       </c>
       <c r="AA101" t="n">
-        <v>62.8</v>
+        <v>725</v>
       </c>
     </row>
     <row r="102">
@@ -10455,7 +10455,7 @@
         <v>42.7</v>
       </c>
       <c r="AA102" t="n">
-        <v>60.8</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103">
@@ -10552,7 +10552,7 @@
         <v>33.4</v>
       </c>
       <c r="AA103" t="n">
-        <v>62.1</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104">
@@ -10649,7 +10649,7 @@
         <v>35.9</v>
       </c>
       <c r="AA104" t="n">
-        <v>62.5</v>
+        <v>797</v>
       </c>
     </row>
     <row r="105">
@@ -10746,7 +10746,7 @@
         <v>30.1</v>
       </c>
       <c r="AA105" t="n">
-        <v>45</v>
+        <v>993</v>
       </c>
     </row>
     <row r="106">
@@ -10843,7 +10843,7 @@
         <v>34.6</v>
       </c>
       <c r="AA106" t="n">
-        <v>47.8</v>
+        <v>598</v>
       </c>
     </row>
     <row r="107">
@@ -10940,7 +10940,7 @@
         <v>26.3</v>
       </c>
       <c r="AA107" t="n">
-        <v>49.2</v>
+        <v>834</v>
       </c>
     </row>
     <row r="108">
@@ -11043,7 +11043,7 @@
         <v>31</v>
       </c>
       <c r="AA108" t="n">
-        <v>49.7</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="109">
@@ -11146,7 +11146,7 @@
         <v>32</v>
       </c>
       <c r="AA109" t="n">
-        <v>50.6</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="110">
@@ -11243,7 +11243,7 @@
         <v>31.9</v>
       </c>
       <c r="AA110" t="n">
-        <v>53.3</v>
+        <v>749</v>
       </c>
     </row>
     <row r="111">
@@ -11346,7 +11346,7 @@
         <v>33.6</v>
       </c>
       <c r="AA111" t="n">
-        <v>54.1</v>
+        <v>891</v>
       </c>
     </row>
     <row r="112">
@@ -11449,7 +11449,7 @@
         <v>33</v>
       </c>
       <c r="AA112" t="n">
-        <v>48.1</v>
+        <v>790</v>
       </c>
     </row>
     <row r="113">
@@ -11546,7 +11546,7 @@
         <v>27.6</v>
       </c>
       <c r="AA113" t="n">
-        <v>45.5</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="114">
@@ -11643,7 +11643,7 @@
         <v>31.8</v>
       </c>
       <c r="AA114" t="n">
-        <v>48.6</v>
+        <v>796</v>
       </c>
     </row>
     <row r="115">
@@ -11740,7 +11740,7 @@
         <v>27.1</v>
       </c>
       <c r="AA115" t="n">
-        <v>48.4</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="116">
@@ -11843,7 +11843,7 @@
         <v>35.2</v>
       </c>
       <c r="AA116" t="n">
-        <v>51.6</v>
+        <v>608</v>
       </c>
     </row>
     <row r="117">
@@ -11940,7 +11940,7 @@
         <v>27.5</v>
       </c>
       <c r="AA117" t="n">
-        <v>48.2</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="118">
@@ -12037,7 +12037,7 @@
         <v>29.7</v>
       </c>
       <c r="AA118" t="n">
-        <v>49.5</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="119">
@@ -12134,7 +12134,7 @@
         <v>32.6</v>
       </c>
       <c r="AA119" t="n">
-        <v>54.7</v>
+        <v>678</v>
       </c>
     </row>
     <row r="120">
@@ -12237,7 +12237,7 @@
         <v>36.3</v>
       </c>
       <c r="AA120" t="n">
-        <v>51.9</v>
+        <v>576</v>
       </c>
     </row>
     <row r="121">
@@ -12340,7 +12340,7 @@
         <v>27</v>
       </c>
       <c r="AA121" t="n">
-        <v>45.3</v>
+        <v>684</v>
       </c>
     </row>
     <row r="122">
@@ -12437,7 +12437,7 @@
         <v>26.7</v>
       </c>
       <c r="AA122" t="n">
-        <v>47.7</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="123">
@@ -12540,7 +12540,7 @@
         <v>35.1</v>
       </c>
       <c r="AA123" t="n">
-        <v>47.3</v>
+        <v>885</v>
       </c>
     </row>
     <row r="124">
@@ -12643,7 +12643,7 @@
         <v>34.7</v>
       </c>
       <c r="AA124" t="n">
-        <v>46.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125">
@@ -12740,7 +12740,7 @@
         <v>28.9</v>
       </c>
       <c r="AA125" t="n">
-        <v>54.1</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="126">
@@ -12837,7 +12837,7 @@
         <v>28.3</v>
       </c>
       <c r="AA126" t="n">
-        <v>50</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="127">
@@ -12934,7 +12934,7 @@
         <v>27.6</v>
       </c>
       <c r="AA127" t="n">
-        <v>47.4</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="128">
@@ -13031,7 +13031,7 @@
         <v>30.4</v>
       </c>
       <c r="AA128" t="n">
-        <v>46.4</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="129">
@@ -13134,7 +13134,7 @@
         <v>33.7</v>
       </c>
       <c r="AA129" t="n">
-        <v>51.4</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="130">
@@ -13237,7 +13237,7 @@
         <v>37.9</v>
       </c>
       <c r="AA130" t="n">
-        <v>46.7</v>
+        <v>478</v>
       </c>
     </row>
     <row r="131">
@@ -13334,7 +13334,7 @@
         <v>26.4</v>
       </c>
       <c r="AA131" t="n">
-        <v>49.5</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="132">
@@ -13437,7 +13437,7 @@
         <v>34</v>
       </c>
       <c r="AA132" t="n">
-        <v>49.8</v>
+        <v>952</v>
       </c>
     </row>
     <row r="133">
@@ -13540,7 +13540,7 @@
         <v>36.8</v>
       </c>
       <c r="AA133" t="n">
-        <v>53.6</v>
+        <v>429</v>
       </c>
     </row>
     <row r="134">
@@ -13637,7 +13637,7 @@
         <v>27.6</v>
       </c>
       <c r="AA134" t="n">
-        <v>45.5</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="135">
@@ -13734,7 +13734,7 @@
         <v>34.4</v>
       </c>
       <c r="AA135" t="n">
-        <v>48.5</v>
+        <v>588</v>
       </c>
     </row>
     <row r="136">
@@ -13831,7 +13831,7 @@
         <v>30.6</v>
       </c>
       <c r="AA136" t="n">
-        <v>48.2</v>
+        <v>978</v>
       </c>
     </row>
     <row r="137">
@@ -13928,7 +13928,7 @@
         <v>28.8</v>
       </c>
       <c r="AA137" t="n">
-        <v>50.3</v>
+        <v>888</v>
       </c>
     </row>
     <row r="138">
@@ -14025,7 +14025,7 @@
         <v>27.2</v>
       </c>
       <c r="AA138" t="n">
-        <v>47</v>
+        <v>983</v>
       </c>
     </row>
     <row r="139">
@@ -14128,7 +14128,7 @@
         <v>34.2</v>
       </c>
       <c r="AA139" t="n">
-        <v>49.3</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="140">
@@ -14231,7 +14231,7 @@
         <v>32</v>
       </c>
       <c r="AA140" t="n">
-        <v>47.9</v>
+        <v>653</v>
       </c>
     </row>
     <row r="141">
@@ -14334,7 +14334,7 @@
         <v>32.6</v>
       </c>
       <c r="AA141" t="n">
-        <v>46.3</v>
+        <v>884</v>
       </c>
     </row>
     <row r="142">
@@ -14437,7 +14437,7 @@
         <v>33.1</v>
       </c>
       <c r="AA142" t="n">
-        <v>45.6</v>
+        <v>848</v>
       </c>
     </row>
     <row r="143">
@@ -14540,7 +14540,7 @@
         <v>31.4</v>
       </c>
       <c r="AA143" t="n">
-        <v>45.2</v>
+        <v>912</v>
       </c>
     </row>
     <row r="144">
@@ -14637,7 +14637,7 @@
         <v>30.4</v>
       </c>
       <c r="AA144" t="n">
-        <v>46.4</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="145">
@@ -14734,7 +14734,7 @@
         <v>30.3</v>
       </c>
       <c r="AA145" t="n">
-        <v>45.3</v>
+        <v>928</v>
       </c>
     </row>
     <row r="146">
@@ -14837,7 +14837,7 @@
         <v>36.1</v>
       </c>
       <c r="AA146" t="n">
-        <v>54.3</v>
+        <v>521</v>
       </c>
     </row>
     <row r="147">
@@ -14934,7 +14934,7 @@
         <v>27</v>
       </c>
       <c r="AA147" t="n">
-        <v>51.7</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="148">
@@ -15037,7 +15037,7 @@
         <v>35.9</v>
       </c>
       <c r="AA148" t="n">
-        <v>53.9</v>
+        <v>518</v>
       </c>
     </row>
     <row r="149">
@@ -15134,7 +15134,7 @@
         <v>26.2</v>
       </c>
       <c r="AA149" t="n">
-        <v>50.5</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="150">
@@ -15231,7 +15231,7 @@
         <v>29</v>
       </c>
       <c r="AA150" t="n">
-        <v>54</v>
+        <v>957</v>
       </c>
     </row>
     <row r="151">
@@ -15328,7 +15328,7 @@
         <v>26.2</v>
       </c>
       <c r="AA151" t="n">
-        <v>47.9</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="152">
@@ -15425,7 +15425,7 @@
         <v>26.9</v>
       </c>
       <c r="AA152" t="n">
-        <v>45.9</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="153">
@@ -15522,7 +15522,7 @@
         <v>26.2</v>
       </c>
       <c r="AA153" t="n">
-        <v>51.7</v>
+        <v>868</v>
       </c>
     </row>
     <row r="154">
@@ -15619,7 +15619,7 @@
         <v>30.7</v>
       </c>
       <c r="AA154" t="n">
-        <v>51.6</v>
+        <v>797</v>
       </c>
     </row>
     <row r="155">
@@ -15716,7 +15716,7 @@
         <v>27.1</v>
       </c>
       <c r="AA155" t="n">
-        <v>48.4</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="156">
@@ -15813,7 +15813,7 @@
         <v>26</v>
       </c>
       <c r="AA156" t="n">
-        <v>45</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="157">
@@ -15910,7 +15910,7 @@
         <v>31.1</v>
       </c>
       <c r="AA157" t="n">
-        <v>49.5</v>
+        <v>849</v>
       </c>
     </row>
     <row r="158">
@@ -16007,7 +16007,7 @@
         <v>27.6</v>
       </c>
       <c r="AA158" t="n">
-        <v>46.4</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="159">
@@ -16104,7 +16104,7 @@
         <v>31.8</v>
       </c>
       <c r="AA159" t="n">
-        <v>53.3</v>
+        <v>782</v>
       </c>
     </row>
     <row r="160">
@@ -16201,7 +16201,7 @@
         <v>25.2</v>
       </c>
       <c r="AA160" t="n">
-        <v>50.9</v>
+        <v>923</v>
       </c>
     </row>
     <row r="161">
@@ -16304,7 +16304,7 @@
         <v>34.3</v>
       </c>
       <c r="AA161" t="n">
-        <v>48.8</v>
+        <v>674</v>
       </c>
     </row>
     <row r="162">
@@ -16401,7 +16401,7 @@
         <v>36.4</v>
       </c>
       <c r="AA162" t="n">
-        <v>49.8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="163">
@@ -16504,7 +16504,7 @@
         <v>34.2</v>
       </c>
       <c r="AA163" t="n">
-        <v>45.8</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="164">
@@ -16607,7 +16607,7 @@
         <v>31</v>
       </c>
       <c r="AA164" t="n">
-        <v>47.8</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="165">
@@ -16704,7 +16704,7 @@
         <v>29.6</v>
       </c>
       <c r="AA165" t="n">
-        <v>46.1</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="166">
@@ -16801,7 +16801,7 @@
         <v>26.7</v>
       </c>
       <c r="AA166" t="n">
-        <v>45.3</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="167">
@@ -16898,7 +16898,7 @@
         <v>25.9</v>
       </c>
       <c r="AA167" t="n">
-        <v>50.7</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="168">
@@ -16995,7 +16995,7 @@
         <v>29</v>
       </c>
       <c r="AA168" t="n">
-        <v>53.8</v>
+        <v>606</v>
       </c>
     </row>
     <row r="169">
@@ -17092,7 +17092,7 @@
         <v>27.6</v>
       </c>
       <c r="AA169" t="n">
-        <v>49.6</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="170">
@@ -17195,7 +17195,7 @@
         <v>32.6</v>
       </c>
       <c r="AA170" t="n">
-        <v>54.1</v>
+        <v>916</v>
       </c>
     </row>
     <row r="171">
@@ -17292,7 +17292,7 @@
         <v>30.1</v>
       </c>
       <c r="AA171" t="n">
-        <v>50.4</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="172">
@@ -17389,7 +17389,7 @@
         <v>30.2</v>
       </c>
       <c r="AA172" t="n">
-        <v>48.6</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="173">
@@ -17486,7 +17486,7 @@
         <v>33.1</v>
       </c>
       <c r="AA173" t="n">
-        <v>51.8</v>
+        <v>785</v>
       </c>
     </row>
     <row r="174">
@@ -17583,7 +17583,7 @@
         <v>26.3</v>
       </c>
       <c r="AA174" t="n">
-        <v>48.4</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="175">
@@ -17680,7 +17680,7 @@
         <v>27.1</v>
       </c>
       <c r="AA175" t="n">
-        <v>51.4</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="176">
@@ -17777,7 +17777,7 @@
         <v>32.7</v>
       </c>
       <c r="AA176" t="n">
-        <v>51.4</v>
+        <v>698</v>
       </c>
     </row>
     <row r="177">
@@ -17874,7 +17874,7 @@
         <v>33.7</v>
       </c>
       <c r="AA177" t="n">
-        <v>53.7</v>
+        <v>867</v>
       </c>
     </row>
     <row r="178">
@@ -17971,7 +17971,7 @@
         <v>29.1</v>
       </c>
       <c r="AA178" t="n">
-        <v>51.2</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="179">
@@ -18068,7 +18068,7 @@
         <v>30.8</v>
       </c>
       <c r="AA179" t="n">
-        <v>49.6</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="180">
@@ -18165,7 +18165,7 @@
         <v>25.9</v>
       </c>
       <c r="AA180" t="n">
-        <v>50.7</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="181">
@@ -18262,7 +18262,7 @@
         <v>27.7</v>
       </c>
       <c r="AA181" t="n">
-        <v>51.6</v>
+        <v>675</v>
       </c>
     </row>
     <row r="182">
@@ -18359,7 +18359,7 @@
         <v>30.9</v>
       </c>
       <c r="AA182" t="n">
-        <v>53</v>
+        <v>825</v>
       </c>
     </row>
     <row r="183">
@@ -18456,7 +18456,7 @@
         <v>26.2</v>
       </c>
       <c r="AA183" t="n">
-        <v>50.4</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="184">
@@ -18553,7 +18553,7 @@
         <v>28.1</v>
       </c>
       <c r="AA184" t="n">
-        <v>48.6</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="185">
@@ -18650,7 +18650,7 @@
         <v>32.4</v>
       </c>
       <c r="AA185" t="n">
-        <v>54.8</v>
+        <v>695</v>
       </c>
     </row>
     <row r="186">
@@ -18747,7 +18747,7 @@
         <v>31.2</v>
       </c>
       <c r="AA186" t="n">
-        <v>50.9</v>
+        <v>792</v>
       </c>
     </row>
     <row r="187">
@@ -18844,7 +18844,7 @@
         <v>26.7</v>
       </c>
       <c r="AA187" t="n">
-        <v>52.2</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188">
@@ -18941,7 +18941,7 @@
         <v>31.4</v>
       </c>
       <c r="AA188" t="n">
-        <v>53.9</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="189">
@@ -19038,7 +19038,7 @@
         <v>27.5</v>
       </c>
       <c r="AA189" t="n">
-        <v>47.1</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="190">
@@ -19135,7 +19135,7 @@
         <v>30.6</v>
       </c>
       <c r="AA190" t="n">
-        <v>51.1</v>
+        <v>929</v>
       </c>
     </row>
     <row r="191">
@@ -19232,7 +19232,7 @@
         <v>26.4</v>
       </c>
       <c r="AA191" t="n">
-        <v>42.6</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="192">
@@ -19329,7 +19329,7 @@
         <v>27.3</v>
       </c>
       <c r="AA192" t="n">
-        <v>41.1</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="193">
@@ -19426,7 +19426,7 @@
         <v>23</v>
       </c>
       <c r="AA193" t="n">
-        <v>47.3</v>
+        <v>725</v>
       </c>
     </row>
     <row r="194">
@@ -19523,7 +19523,7 @@
         <v>25.3</v>
       </c>
       <c r="AA194" t="n">
-        <v>43.2</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="195">
@@ -19620,7 +19620,7 @@
         <v>22.6</v>
       </c>
       <c r="AA195" t="n">
-        <v>38.2</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="196">
@@ -19723,7 +19723,7 @@
         <v>34.3</v>
       </c>
       <c r="AA196" t="n">
-        <v>41.4</v>
+        <v>840</v>
       </c>
     </row>
     <row r="197">
@@ -19820,7 +19820,7 @@
         <v>23.2</v>
       </c>
       <c r="AA197" t="n">
-        <v>42.4</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="198">
@@ -19917,7 +19917,7 @@
         <v>25.9</v>
       </c>
       <c r="AA198" t="n">
-        <v>44.4</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="199">
@@ -20014,7 +20014,7 @@
         <v>19.7</v>
       </c>
       <c r="AA199" t="n">
-        <v>39.1</v>
+        <v>238</v>
       </c>
     </row>
     <row r="200">
@@ -20117,7 +20117,7 @@
         <v>27.6</v>
       </c>
       <c r="AA200" t="n">
-        <v>46.7</v>
+        <v>891</v>
       </c>
     </row>
     <row r="201">
@@ -20214,7 +20214,7 @@
         <v>30</v>
       </c>
       <c r="AA201" t="n">
-        <v>42.2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="202">
@@ -20311,7 +20311,7 @@
         <v>18.4</v>
       </c>
       <c r="AA202" t="n">
-        <v>39.3</v>
+        <v>425</v>
       </c>
     </row>
     <row r="203">
@@ -20414,7 +20414,7 @@
         <v>14.3</v>
       </c>
       <c r="AA203" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="204">
@@ -20517,7 +20517,7 @@
         <v>36</v>
       </c>
       <c r="AA204" t="n">
-        <v>41.5</v>
+        <v>530</v>
       </c>
     </row>
     <row r="205">
@@ -20614,7 +20614,7 @@
         <v>26.6</v>
       </c>
       <c r="AA205" t="n">
-        <v>41</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="206">
@@ -20717,7 +20717,7 @@
         <v>22.8</v>
       </c>
       <c r="AA206" t="n">
-        <v>40.3</v>
+        <v>632</v>
       </c>
     </row>
     <row r="207">
@@ -20814,7 +20814,7 @@
         <v>25.6</v>
       </c>
       <c r="AA207" t="n">
-        <v>43.9</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="208">
@@ -20911,7 +20911,7 @@
         <v>22.8</v>
       </c>
       <c r="AA208" t="n">
-        <v>41.3</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="209">
@@ -21008,7 +21008,7 @@
         <v>27</v>
       </c>
       <c r="AA209" t="n">
-        <v>41.5</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="210">
@@ -21105,7 +21105,7 @@
         <v>23.2</v>
       </c>
       <c r="AA210" t="n">
-        <v>42.4</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="211">
@@ -21202,7 +21202,7 @@
         <v>28</v>
       </c>
       <c r="AA211" t="n">
-        <v>43.1</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="212">
@@ -21305,7 +21305,7 @@
         <v>33.5</v>
       </c>
       <c r="AA212" t="n">
-        <v>43.4</v>
+        <v>999</v>
       </c>
     </row>
     <row r="213">
@@ -21402,7 +21402,7 @@
         <v>25.6</v>
       </c>
       <c r="AA213" t="n">
-        <v>44.4</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="214">
@@ -21505,7 +21505,7 @@
         <v>24.1</v>
       </c>
       <c r="AA214" t="n">
-        <v>40.3</v>
+        <v>759</v>
       </c>
     </row>
     <row r="215">
@@ -21608,7 +21608,7 @@
         <v>29</v>
       </c>
       <c r="AA215" t="n">
-        <v>46.6</v>
+        <v>994</v>
       </c>
     </row>
     <row r="216">
@@ -21705,7 +21705,7 @@
         <v>30.9</v>
       </c>
       <c r="AA216" t="n">
-        <v>41.6</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217">
@@ -21808,7 +21808,7 @@
         <v>32.9</v>
       </c>
       <c r="AA217" t="n">
-        <v>43.5</v>
+        <v>827</v>
       </c>
     </row>
     <row r="218">
@@ -21905,7 +21905,7 @@
         <v>24.5</v>
       </c>
       <c r="AA218" t="n">
-        <v>38.2</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="219">
@@ -22002,7 +22002,7 @@
         <v>26.9</v>
       </c>
       <c r="AA219" t="n">
-        <v>44.6</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="220">
@@ -22099,7 +22099,7 @@
         <v>33.2</v>
       </c>
       <c r="AA220" t="n">
-        <v>50.7</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221">
@@ -22196,7 +22196,7 @@
         <v>25.1</v>
       </c>
       <c r="AA221" t="n">
-        <v>43.3</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="222">
@@ -22293,7 +22293,7 @@
         <v>4.8</v>
       </c>
       <c r="AA222" t="n">
-        <v>47.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223">
@@ -22390,7 +22390,7 @@
         <v>23.5</v>
       </c>
       <c r="AA223" t="n">
-        <v>44.2</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="224">
@@ -22487,7 +22487,7 @@
         <v>27.3</v>
       </c>
       <c r="AA224" t="n">
-        <v>40.3</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="225">
@@ -22590,7 +22590,7 @@
         <v>31.3</v>
       </c>
       <c r="AA225" t="n">
-        <v>40.9</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="226">
@@ -22693,7 +22693,7 @@
         <v>27.4</v>
       </c>
       <c r="AA226" t="n">
-        <v>41</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="227">
@@ -22790,7 +22790,7 @@
         <v>24</v>
       </c>
       <c r="AA227" t="n">
-        <v>43.3</v>
+        <v>876</v>
       </c>
     </row>
     <row r="228">
@@ -22887,7 +22887,7 @@
         <v>22.8</v>
       </c>
       <c r="AA228" t="n">
-        <v>39.1</v>
+        <v>977</v>
       </c>
     </row>
     <row r="229">
@@ -22990,7 +22990,7 @@
         <v>24.6</v>
       </c>
       <c r="AA229" t="n">
-        <v>42</v>
+        <v>431</v>
       </c>
     </row>
     <row r="230">
@@ -23093,7 +23093,7 @@
         <v>25.1</v>
       </c>
       <c r="AA230" t="n">
-        <v>43.6</v>
+        <v>722</v>
       </c>
     </row>
     <row r="231">
@@ -23196,7 +23196,7 @@
         <v>28.5</v>
       </c>
       <c r="AA231" t="n">
-        <v>40</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="232">
@@ -23293,7 +23293,7 @@
         <v>24.6</v>
       </c>
       <c r="AA232" t="n">
-        <v>38.3</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="233">
@@ -23396,7 +23396,7 @@
         <v>35.9</v>
       </c>
       <c r="AA233" t="n">
-        <v>40.7</v>
+        <v>231</v>
       </c>
     </row>
     <row r="234">
@@ -23499,7 +23499,7 @@
         <v>27.9</v>
       </c>
       <c r="AA234" t="n">
-        <v>40.6</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="235">
@@ -23596,7 +23596,7 @@
         <v>25.2</v>
       </c>
       <c r="AA235" t="n">
-        <v>45.7</v>
+        <v>508</v>
       </c>
     </row>
     <row r="236">
@@ -23699,7 +23699,7 @@
         <v>31.1</v>
       </c>
       <c r="AA236" t="n">
-        <v>42.9</v>
+        <v>994</v>
       </c>
     </row>
     <row r="237">
@@ -23796,7 +23796,7 @@
         <v>20.8</v>
       </c>
       <c r="AA237" t="n">
-        <v>42.4</v>
+        <v>542</v>
       </c>
     </row>
     <row r="238">
@@ -23893,7 +23893,7 @@
         <v>23.7</v>
       </c>
       <c r="AA238" t="n">
-        <v>41.7</v>
+        <v>929</v>
       </c>
     </row>
     <row r="239">
@@ -23990,7 +23990,7 @@
         <v>26.3</v>
       </c>
       <c r="AA239" t="n">
-        <v>40.1</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="240">
@@ -24093,7 +24093,7 @@
         <v>33.8</v>
       </c>
       <c r="AA240" t="n">
-        <v>43</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="241">
@@ -24196,7 +24196,7 @@
         <v>32.5</v>
       </c>
       <c r="AA241" t="n">
-        <v>41.6</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="242">
@@ -24299,7 +24299,7 @@
         <v>34.3</v>
       </c>
       <c r="AA242" t="n">
-        <v>40.7</v>
+        <v>492</v>
       </c>
     </row>
     <row r="243">
@@ -24402,7 +24402,7 @@
         <v>30.8</v>
       </c>
       <c r="AA243" t="n">
-        <v>44.3</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="244">
@@ -24499,7 +24499,7 @@
         <v>27.7</v>
       </c>
       <c r="AA244" t="n">
-        <v>39.5</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="245">
@@ -24596,7 +24596,7 @@
         <v>30.5</v>
       </c>
       <c r="AA245" t="n">
-        <v>40.6</v>
+        <v>663</v>
       </c>
     </row>
     <row r="246">
@@ -24693,7 +24693,7 @@
         <v>23.8</v>
       </c>
       <c r="AA246" t="n">
-        <v>50.4</v>
+        <v>391</v>
       </c>
     </row>
     <row r="247">
@@ -24796,7 +24796,7 @@
         <v>35.4</v>
       </c>
       <c r="AA247" t="n">
-        <v>41.8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248">
@@ -24893,7 +24893,7 @@
         <v>18.4</v>
       </c>
       <c r="AA248" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249">
@@ -24990,7 +24990,7 @@
         <v>24.7</v>
       </c>
       <c r="AA249" t="n">
-        <v>42.8</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="250">
@@ -25087,7 +25087,7 @@
         <v>20.1</v>
       </c>
       <c r="AA250" t="n">
-        <v>40.9</v>
+        <v>328</v>
       </c>
     </row>
     <row r="251">
@@ -25184,7 +25184,7 @@
         <v>21</v>
       </c>
       <c r="AA251" t="n">
-        <v>38.7</v>
+        <v>768</v>
       </c>
     </row>
     <row r="252">
@@ -25281,7 +25281,7 @@
         <v>28.3</v>
       </c>
       <c r="AA252" t="n">
-        <v>44.3</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="253">
@@ -25384,7 +25384,7 @@
         <v>28.6</v>
       </c>
       <c r="AA253" t="n">
-        <v>40.2</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="254">
@@ -25481,7 +25481,7 @@
         <v>21</v>
       </c>
       <c r="AA254" t="n">
-        <v>43.4</v>
+        <v>514</v>
       </c>
     </row>
     <row r="255">
@@ -25578,7 +25578,7 @@
         <v>24.1</v>
       </c>
       <c r="AA255" t="n">
-        <v>50.3</v>
+        <v>676</v>
       </c>
     </row>
     <row r="256">
@@ -25681,7 +25681,7 @@
         <v>27</v>
       </c>
       <c r="AA256" t="n">
-        <v>40.8</v>
+        <v>693</v>
       </c>
     </row>
     <row r="257">
@@ -25784,7 +25784,7 @@
         <v>26.3</v>
       </c>
       <c r="AA257" t="n">
-        <v>44.1</v>
+        <v>463</v>
       </c>
     </row>
     <row r="258">
@@ -25887,7 +25887,7 @@
         <v>26.1</v>
       </c>
       <c r="AA258" t="n">
-        <v>44.7</v>
+        <v>628</v>
       </c>
     </row>
     <row r="259">
@@ -25990,7 +25990,7 @@
         <v>31.5</v>
       </c>
       <c r="AA259" t="n">
-        <v>42</v>
+        <v>987</v>
       </c>
     </row>
     <row r="260">
@@ -26093,7 +26093,7 @@
         <v>29.1</v>
       </c>
       <c r="AA260" t="n">
-        <v>40.1</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="261">
@@ -26196,7 +26196,7 @@
         <v>20.4</v>
       </c>
       <c r="AA261" t="n">
-        <v>39.3</v>
+        <v>392</v>
       </c>
     </row>
     <row r="262">
@@ -26293,7 +26293,7 @@
         <v>25.9</v>
       </c>
       <c r="AA262" t="n">
-        <v>42.3</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="263">
@@ -26390,7 +26390,7 @@
         <v>25.9</v>
       </c>
       <c r="AA263" t="n">
-        <v>41.2</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="264">
@@ -26493,7 +26493,7 @@
         <v>28.5</v>
       </c>
       <c r="AA264" t="n">
-        <v>47.2</v>
+        <v>943</v>
       </c>
     </row>
     <row r="265">
@@ -26590,7 +26590,7 @@
         <v>30.1</v>
       </c>
       <c r="AA265" t="n">
-        <v>41.6</v>
+        <v>764</v>
       </c>
     </row>
     <row r="266">
@@ -26693,7 +26693,7 @@
         <v>28.9</v>
       </c>
       <c r="AA266" t="n">
-        <v>42.3</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="267">
@@ -26790,7 +26790,7 @@
         <v>21.1</v>
       </c>
       <c r="AA267" t="n">
-        <v>39.9</v>
+        <v>963</v>
       </c>
     </row>
     <row r="268">
@@ -26893,7 +26893,7 @@
         <v>29.1</v>
       </c>
       <c r="AA268" t="n">
-        <v>39.8</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="269">
@@ -26996,7 +26996,7 @@
         <v>24.5</v>
       </c>
       <c r="AA269" t="n">
-        <v>42</v>
+        <v>519</v>
       </c>
     </row>
     <row r="270">
@@ -27099,7 +27099,7 @@
         <v>26.1</v>
       </c>
       <c r="AA270" t="n">
-        <v>39.2</v>
+        <v>597</v>
       </c>
     </row>
     <row r="271">
@@ -27196,7 +27196,7 @@
         <v>20.5</v>
       </c>
       <c r="AA271" t="n">
-        <v>41.5</v>
+        <v>434</v>
       </c>
     </row>
     <row r="272">
@@ -27299,7 +27299,7 @@
         <v>29.3</v>
       </c>
       <c r="AA272" t="n">
-        <v>40.2</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="273">
@@ -27402,7 +27402,7 @@
         <v>31.5</v>
       </c>
       <c r="AA273" t="n">
-        <v>39.9</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="274">
@@ -27505,7 +27505,7 @@
         <v>30.6</v>
       </c>
       <c r="AA274" t="n">
-        <v>41.2</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="275">
@@ -27608,7 +27608,7 @@
         <v>25.8</v>
       </c>
       <c r="AA275" t="n">
-        <v>41.9</v>
+        <v>938</v>
       </c>
     </row>
     <row r="276">
@@ -27705,7 +27705,7 @@
         <v>30.2</v>
       </c>
       <c r="AA276" t="n">
-        <v>43.4</v>
+        <v>705</v>
       </c>
     </row>
     <row r="277">
@@ -27808,7 +27808,7 @@
         <v>23.4</v>
       </c>
       <c r="AA277" t="n">
-        <v>38.1</v>
+        <v>197</v>
       </c>
     </row>
     <row r="278">
@@ -27911,7 +27911,7 @@
         <v>30.7</v>
       </c>
       <c r="AA278" t="n">
-        <v>39.3</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="279">
@@ -28014,7 +28014,7 @@
         <v>29.1</v>
       </c>
       <c r="AA279" t="n">
-        <v>42.8</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="280">
@@ -28117,7 +28117,7 @@
         <v>30.4</v>
       </c>
       <c r="AA280" t="n">
-        <v>39.8</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="281">
@@ -28220,7 +28220,7 @@
         <v>27.2</v>
       </c>
       <c r="AA281" t="n">
-        <v>46.4</v>
+        <v>801</v>
       </c>
     </row>
     <row r="282">
@@ -28317,7 +28317,7 @@
         <v>25.6</v>
       </c>
       <c r="AA282" t="n">
-        <v>43.8</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="283">
@@ -28414,7 +28414,7 @@
         <v>23.1</v>
       </c>
       <c r="AA283" t="n">
-        <v>44.1</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="284">
@@ -28511,7 +28511,7 @@
         <v>24.7</v>
       </c>
       <c r="AA284" t="n">
-        <v>41.9</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="285">
@@ -28614,7 +28614,7 @@
         <v>26.1</v>
       </c>
       <c r="AA285" t="n">
-        <v>40.1</v>
+        <v>751</v>
       </c>
     </row>
     <row r="286">
@@ -28711,7 +28711,7 @@
         <v>25.9</v>
       </c>
       <c r="AA286" t="n">
-        <v>42.3</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="287">
@@ -28808,7 +28808,7 @@
         <v>19.9</v>
       </c>
       <c r="AA287" t="n">
-        <v>38.4</v>
+        <v>632</v>
       </c>
     </row>
     <row r="288">
@@ -28905,7 +28905,7 @@
         <v>18.3</v>
       </c>
       <c r="AA288" t="n">
-        <v>38.6</v>
+        <v>350</v>
       </c>
     </row>
     <row r="289">
@@ -29008,7 +29008,7 @@
         <v>28.2</v>
       </c>
       <c r="AA289" t="n">
-        <v>47.2</v>
+        <v>950</v>
       </c>
     </row>
     <row r="290">
@@ -29105,7 +29105,7 @@
         <v>25</v>
       </c>
       <c r="AA290" t="n">
-        <v>48.1</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="291">
@@ -29202,7 +29202,7 @@
         <v>27</v>
       </c>
       <c r="AA291" t="n">
-        <v>41.5</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="292">
@@ -29299,7 +29299,7 @@
         <v>29</v>
       </c>
       <c r="AA292" t="n">
-        <v>43.8</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="293">
@@ -29396,7 +29396,7 @@
         <v>24.7</v>
       </c>
       <c r="AA293" t="n">
-        <v>42.8</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="294">
@@ -29493,7 +29493,7 @@
         <v>25.3</v>
       </c>
       <c r="AA294" t="n">
-        <v>43.6</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="295">
@@ -29590,7 +29590,7 @@
         <v>23.7</v>
       </c>
       <c r="AA295" t="n">
-        <v>41.6</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="296">
@@ -29687,7 +29687,7 @@
         <v>32.2</v>
       </c>
       <c r="AA296" t="n">
-        <v>41.6</v>
+        <v>397</v>
       </c>
     </row>
     <row r="297">
@@ -29784,7 +29784,7 @@
         <v>30</v>
       </c>
       <c r="AA297" t="n">
-        <v>43.2</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="298">
@@ -29881,7 +29881,7 @@
         <v>23.2</v>
       </c>
       <c r="AA298" t="n">
-        <v>47.9</v>
+        <v>685</v>
       </c>
     </row>
     <row r="299">
@@ -29978,7 +29978,7 @@
         <v>24.3</v>
       </c>
       <c r="AA299" t="n">
-        <v>44.9</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="300">
@@ -30075,7 +30075,7 @@
         <v>23.1</v>
       </c>
       <c r="AA300" t="n">
-        <v>44.1</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="301">
@@ -30172,7 +30172,7 @@
         <v>31.8</v>
       </c>
       <c r="AA301" t="n">
-        <v>40.9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="302">
@@ -30269,7 +30269,7 @@
         <v>28</v>
       </c>
       <c r="AA302" t="n">
-        <v>44.3</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="303">
@@ -30366,7 +30366,7 @@
         <v>25</v>
       </c>
       <c r="AA303" t="n">
-        <v>47.7</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="304">
@@ -30463,7 +30463,7 @@
         <v>23.6</v>
       </c>
       <c r="AA304" t="n">
-        <v>38.8</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="305">
@@ -30560,7 +30560,7 @@
         <v>25.9</v>
       </c>
       <c r="AA305" t="n">
-        <v>42.3</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="306">
@@ -30657,7 +30657,7 @@
         <v>25.8</v>
       </c>
       <c r="AA306" t="n">
-        <v>39.8</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="307">
@@ -30754,7 +30754,7 @@
         <v>27</v>
       </c>
       <c r="AA307" t="n">
-        <v>41.5</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="308">
@@ -30851,7 +30851,7 @@
         <v>21.4</v>
       </c>
       <c r="AA308" t="n">
-        <v>36.3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="309">
@@ -30948,7 +30948,7 @@
         <v>31.6</v>
       </c>
       <c r="AA309" t="n">
-        <v>41.3</v>
+        <v>453</v>
       </c>
     </row>
     <row r="310">
@@ -31045,7 +31045,7 @@
         <v>22.6</v>
       </c>
       <c r="AA310" t="n">
-        <v>38.6</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="311">
@@ -31142,7 +31142,7 @@
         <v>21</v>
       </c>
       <c r="AA311" t="n">
-        <v>38.7</v>
+        <v>768</v>
       </c>
     </row>
     <row r="312">
@@ -31239,7 +31239,7 @@
         <v>23.6</v>
       </c>
       <c r="AA312" t="n">
-        <v>42</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="313">
@@ -31328,7 +31328,7 @@
         <v>34.3</v>
       </c>
       <c r="AA313" t="n">
-        <v>43.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="314">
@@ -31417,7 +31417,7 @@
         <v>34.3</v>
       </c>
       <c r="AA314" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="315">
@@ -31506,7 +31506,7 @@
         <v>34.3</v>
       </c>
       <c r="AA315" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="316">
@@ -31595,7 +31595,7 @@
         <v>33.9</v>
       </c>
       <c r="AA316" t="n">
-        <v>43.8</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="317">
@@ -31684,7 +31684,7 @@
         <v>34.1</v>
       </c>
       <c r="AA317" t="n">
-        <v>43.6</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="318">
@@ -31773,7 +31773,7 @@
         <v>34.3</v>
       </c>
       <c r="AA318" t="n">
-        <v>43.8</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="319">
@@ -31862,7 +31862,7 @@
         <v>34.3</v>
       </c>
       <c r="AA319" t="n">
-        <v>43.8</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="320">
@@ -31951,7 +31951,7 @@
         <v>34.3</v>
       </c>
       <c r="AA320" t="n">
-        <v>43.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="321">
@@ -32040,7 +32040,7 @@
         <v>34.2</v>
       </c>
       <c r="AA321" t="n">
-        <v>43.9</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="322">
@@ -32129,7 +32129,7 @@
         <v>34.3</v>
       </c>
       <c r="AA322" t="n">
-        <v>43.8</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="323">
@@ -32218,7 +32218,7 @@
         <v>33.7</v>
       </c>
       <c r="AA323" t="n">
-        <v>43.7</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="324">
@@ -32307,7 +32307,7 @@
         <v>34.3</v>
       </c>
       <c r="AA324" t="n">
-        <v>43.8</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="325">
@@ -32396,7 +32396,7 @@
         <v>34</v>
       </c>
       <c r="AA325" t="n">
-        <v>43.7</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="326">
@@ -32485,7 +32485,7 @@
         <v>33.7</v>
       </c>
       <c r="AA326" t="n">
-        <v>43.7</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="327">
@@ -32574,7 +32574,7 @@
         <v>34</v>
       </c>
       <c r="AA327" t="n">
-        <v>43.5</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="328">
@@ -32663,7 +32663,7 @@
         <v>34</v>
       </c>
       <c r="AA328" t="n">
-        <v>43.8</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="329">
@@ -32752,7 +32752,7 @@
         <v>34.3</v>
       </c>
       <c r="AA329" t="n">
-        <v>43.8</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="330">
@@ -32841,7 +32841,7 @@
         <v>34.2</v>
       </c>
       <c r="AA330" t="n">
-        <v>43.9</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="331">
@@ -32930,7 +32930,7 @@
         <v>33.9</v>
       </c>
       <c r="AA331" t="n">
-        <v>43.6</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="332">
@@ -33019,7 +33019,7 @@
         <v>34.3</v>
       </c>
       <c r="AA332" t="n">
-        <v>43.5</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="333">
@@ -33108,7 +33108,7 @@
         <v>34.3</v>
       </c>
       <c r="AA333" t="n">
-        <v>43.8</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="334">
@@ -33197,7 +33197,7 @@
         <v>34.3</v>
       </c>
       <c r="AA334" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="335">
@@ -33286,7 +33286,7 @@
         <v>34.3</v>
       </c>
       <c r="AA335" t="n">
-        <v>43.6</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="336">
@@ -33375,7 +33375,7 @@
         <v>33.9</v>
       </c>
       <c r="AA336" t="n">
-        <v>43.9</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="337">
@@ -33464,7 +33464,7 @@
         <v>34.2</v>
       </c>
       <c r="AA337" t="n">
-        <v>43.8</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="338">
@@ -33553,7 +33553,7 @@
         <v>34.3</v>
       </c>
       <c r="AA338" t="n">
-        <v>43.6</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="339">
@@ -33642,7 +33642,7 @@
         <v>34</v>
       </c>
       <c r="AA339" t="n">
-        <v>43.8</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="340">
@@ -33731,7 +33731,7 @@
         <v>34.4</v>
       </c>
       <c r="AA340" t="n">
-        <v>43.7</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="341">
@@ -33814,7 +33814,7 @@
         <v>30.9</v>
       </c>
       <c r="AA341" t="n">
-        <v>43.3</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="342">
@@ -33903,7 +33903,7 @@
         <v>34.3</v>
       </c>
       <c r="AA342" t="n">
-        <v>43.8</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="343">
@@ -33992,7 +33992,7 @@
         <v>34</v>
       </c>
       <c r="AA343" t="n">
-        <v>43.7</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="344">
@@ -34081,7 +34081,7 @@
         <v>33.9</v>
       </c>
       <c r="AA344" t="n">
-        <v>43.8</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="345">
@@ -34170,7 +34170,7 @@
         <v>34</v>
       </c>
       <c r="AA345" t="n">
-        <v>43.8</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="346">
@@ -34259,7 +34259,7 @@
         <v>33.5</v>
       </c>
       <c r="AA346" t="n">
-        <v>43.7</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="347">
@@ -34348,7 +34348,7 @@
         <v>34.2</v>
       </c>
       <c r="AA347" t="n">
-        <v>43.7</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="348">
@@ -34437,7 +34437,7 @@
         <v>33.5</v>
       </c>
       <c r="AA348" t="n">
-        <v>43.7</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="349">
@@ -34526,7 +34526,7 @@
         <v>33.9</v>
       </c>
       <c r="AA349" t="n">
-        <v>43.8</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="350">
@@ -34615,7 +34615,7 @@
         <v>34</v>
       </c>
       <c r="AA350" t="n">
-        <v>43.6</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="351">
@@ -34704,7 +34704,7 @@
         <v>34.3</v>
       </c>
       <c r="AA351" t="n">
-        <v>43.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="352">
@@ -34793,7 +34793,7 @@
         <v>33.7</v>
       </c>
       <c r="AA352" t="n">
-        <v>43.9</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="353">
@@ -34882,7 +34882,7 @@
         <v>33.5</v>
       </c>
       <c r="AA353" t="n">
-        <v>43.6</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="354">
@@ -34971,7 +34971,7 @@
         <v>33.7</v>
       </c>
       <c r="AA354" t="n">
-        <v>43.5</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="355">
@@ -35060,7 +35060,7 @@
         <v>34.3</v>
       </c>
       <c r="AA355" t="n">
-        <v>43.9</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="356">
@@ -35149,7 +35149,7 @@
         <v>34.1</v>
       </c>
       <c r="AA356" t="n">
-        <v>43.5</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="357">
@@ -35238,7 +35238,7 @@
         <v>33.5</v>
       </c>
       <c r="AA357" t="n">
-        <v>43.7</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="358">
@@ -35327,7 +35327,7 @@
         <v>34.3</v>
       </c>
       <c r="AA358" t="n">
-        <v>43.8</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="359">
@@ -35416,7 +35416,7 @@
         <v>34.3</v>
       </c>
       <c r="AA359" t="n">
-        <v>43.8</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="360">
@@ -35505,7 +35505,7 @@
         <v>34.3</v>
       </c>
       <c r="AA360" t="n">
-        <v>43.5</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="361">
@@ -35594,7 +35594,7 @@
         <v>34.3</v>
       </c>
       <c r="AA361" t="n">
-        <v>43.6</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="362">
@@ -35683,7 +35683,7 @@
         <v>34.3</v>
       </c>
       <c r="AA362" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="363">
@@ -35772,7 +35772,7 @@
         <v>34.3</v>
       </c>
       <c r="AA363" t="n">
-        <v>43.8</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="364">
@@ -35861,7 +35861,7 @@
         <v>34.2</v>
       </c>
       <c r="AA364" t="n">
-        <v>43.7</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="365">
@@ -35950,7 +35950,7 @@
         <v>34.1</v>
       </c>
       <c r="AA365" t="n">
-        <v>43.8</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="366">
@@ -36039,7 +36039,7 @@
         <v>34.3</v>
       </c>
       <c r="AA366" t="n">
-        <v>43.6</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="367">
@@ -36128,7 +36128,7 @@
         <v>33.7</v>
       </c>
       <c r="AA367" t="n">
-        <v>43.7</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="368">
@@ -36217,7 +36217,7 @@
         <v>33.7</v>
       </c>
       <c r="AA368" t="n">
-        <v>43.8</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="369">
@@ -36306,7 +36306,7 @@
         <v>34.3</v>
       </c>
       <c r="AA369" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="370">
@@ -36395,7 +36395,7 @@
         <v>33.8</v>
       </c>
       <c r="AA370" t="n">
-        <v>43.7</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="371">
@@ -36484,7 +36484,7 @@
         <v>34.3</v>
       </c>
       <c r="AA371" t="n">
-        <v>43.7</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="372">
@@ -36573,7 +36573,7 @@
         <v>33.8</v>
       </c>
       <c r="AA372" t="n">
-        <v>43.7</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="373">
@@ -36662,7 +36662,7 @@
         <v>33.8</v>
       </c>
       <c r="AA373" t="n">
-        <v>43.9</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="374">
@@ -36751,7 +36751,7 @@
         <v>33.8</v>
       </c>
       <c r="AA374" t="n">
-        <v>43.7</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="375">
@@ -36840,7 +36840,7 @@
         <v>33.7</v>
       </c>
       <c r="AA375" t="n">
-        <v>43.7</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="376">
@@ -36929,7 +36929,7 @@
         <v>34.2</v>
       </c>
       <c r="AA376" t="n">
-        <v>43.9</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="377">
@@ -37018,7 +37018,7 @@
         <v>34.2</v>
       </c>
       <c r="AA377" t="n">
-        <v>43.8</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="378">
@@ -37107,7 +37107,7 @@
         <v>34.3</v>
       </c>
       <c r="AA378" t="n">
-        <v>43.8</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="379">
@@ -37196,7 +37196,7 @@
         <v>33.6</v>
       </c>
       <c r="AA379" t="n">
-        <v>43.8</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="380">
@@ -37285,7 +37285,7 @@
         <v>34.1</v>
       </c>
       <c r="AA380" t="n">
-        <v>43.5</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="381">
@@ -37374,7 +37374,7 @@
         <v>34.4</v>
       </c>
       <c r="AA381" t="n">
-        <v>43.7</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="382">
@@ -37463,7 +37463,7 @@
         <v>34.3</v>
       </c>
       <c r="AA382" t="n">
-        <v>43.7</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="383">
@@ -37552,7 +37552,7 @@
         <v>34.2</v>
       </c>
       <c r="AA383" t="n">
-        <v>43.4</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="384">
@@ -37641,7 +37641,7 @@
         <v>34.3</v>
       </c>
       <c r="AA384" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="385">
@@ -37730,7 +37730,7 @@
         <v>34.1</v>
       </c>
       <c r="AA385" t="n">
-        <v>43.6</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="386">
@@ -37819,7 +37819,7 @@
         <v>34.3</v>
       </c>
       <c r="AA386" t="n">
-        <v>43.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="387">
@@ -37908,7 +37908,7 @@
         <v>34.3</v>
       </c>
       <c r="AA387" t="n">
-        <v>43.8</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="388">
@@ -37997,7 +37997,7 @@
         <v>33.8</v>
       </c>
       <c r="AA388" t="n">
-        <v>43.9</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="389">
@@ -38086,7 +38086,7 @@
         <v>33.7</v>
       </c>
       <c r="AA389" t="n">
-        <v>43.8</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="390">
@@ -38175,7 +38175,7 @@
         <v>33.8</v>
       </c>
       <c r="AA390" t="n">
-        <v>43.8</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="391">
@@ -38264,7 +38264,7 @@
         <v>34.3</v>
       </c>
       <c r="AA391" t="n">
-        <v>43.5</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="392">
@@ -38353,7 +38353,7 @@
         <v>34</v>
       </c>
       <c r="AA392" t="n">
-        <v>43.7</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="393">
@@ -38442,7 +38442,7 @@
         <v>34.3</v>
       </c>
       <c r="AA393" t="n">
-        <v>43.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="394">
@@ -38531,7 +38531,7 @@
         <v>34.1</v>
       </c>
       <c r="AA394" t="n">
-        <v>43.8</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="395">
@@ -38620,7 +38620,7 @@
         <v>34.3</v>
       </c>
       <c r="AA395" t="n">
-        <v>43.8</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="396">
@@ -38709,7 +38709,7 @@
         <v>34.3</v>
       </c>
       <c r="AA396" t="n">
-        <v>43.8</v>
+        <v>3235</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,42 +556,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>IK Start</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Valerenga</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>무승부</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>England League Two+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O2" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -629,97 +629,101 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
-        <v>47.4</v>
+        <v>56.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="X2" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>England League Two+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -728,97 +732,101 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>57.7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="U3" t="n">
-        <v>35.3</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>26/05/2026 0:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GimPo Citizen</t>
+          <t>Moss FK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>4.1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>3:2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -827,70 +835,68 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T4" t="n">
-        <v>47.4</v>
+        <v>63.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="V4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="W4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="X4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>3.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>5.2</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>USA Major League Soccer+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -903,81 +909,93 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>23</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>35.3</v>
+      </c>
       <c r="V5" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="W5" t="n">
-        <v>27.3</v>
+        <v>40</v>
       </c>
       <c r="X5" t="n">
-        <v>27.3</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>27.3</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26/05/2026 3:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>GimPo Citizen</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -991,17 +1009,17 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1015,68 +1033,68 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="U6" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="W6" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Y6" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26/05/2026 4:00</t>
+          <t>26/05/2026 0:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>St Mirren</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Lillestrom SK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Scotland Premiership+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1086,26 +1104,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1114,68 +1132,68 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="T7" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>33.3</v>
       </c>
-      <c r="X7" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Y7" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26/05/2026 7:00</t>
+          <t>26/05/2026 0:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Athletic Club MG</t>
+          <t>Rosenborg BK</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1189,22 +1207,22 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="N8" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1213,22 +1231,22 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>57.7</v>
       </c>
       <c r="T8" t="n">
-        <v>47.4</v>
+        <v>46.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W8" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1237,33 +1255,33 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26/05/2026 8:00</t>
+          <t>26/05/2026 0:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Aalesund FK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
@@ -1274,7 +1292,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Brazil Serie A+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1284,26 +1302,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N9" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
         <v>21</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1315,28 +1333,1493 @@
         <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>56.8</v>
+        <v>56.1</v>
       </c>
       <c r="U9" t="n">
         <v>56.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z9" t="n">
         <v>50</v>
-      </c>
-      <c r="X9" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien+</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>31</v>
+      </c>
+      <c r="O10" t="n">
+        <v>41</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>50</v>
+      </c>
+      <c r="W10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Asane Fotball</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Raufoss IL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N11" t="n">
+        <v>26</v>
+      </c>
+      <c r="O11" t="n">
+        <v>34</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Odd BK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ranheim Fotball</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" t="n">
+        <v>31</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>27</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>37</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>40</v>
+      </c>
+      <c r="X13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IL Hodd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Egersunds IK</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>38</v>
+      </c>
+      <c r="N14" t="n">
+        <v>34</v>
+      </c>
+      <c r="O14" t="n">
+        <v>28</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>50</v>
+      </c>
+      <c r="X14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Stromsgodset IF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bryne FK</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>23</v>
+      </c>
+      <c r="O15" t="n">
+        <v>21</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>28</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>50</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>26/05/2026 0:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lyn Oslo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Strommen IF</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>30</v>
+      </c>
+      <c r="N17" t="n">
+        <v>44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>40</v>
+      </c>
+      <c r="W17" t="n">
+        <v>40</v>
+      </c>
+      <c r="X17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>23</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>USA Major League Soccer+</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>26/05/2026 2:15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien+</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>52</v>
+      </c>
+      <c r="N19" t="n">
+        <v>26</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>26/05/2026 3:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga+</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>27</v>
+      </c>
+      <c r="N20" t="n">
+        <v>39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>34</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>47</v>
+      </c>
+      <c r="U20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>26/05/2026 4:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>St Mirren</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Partick Thistle</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Scotland Premiership+</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>37</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>50</v>
+      </c>
+      <c r="W21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>26/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Athletic Club MG</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="n">
+        <v>43</v>
+      </c>
+      <c r="O22" t="n">
+        <v>34</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="X22" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>26/05/2026 8:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Brazil Serie A+</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>26</v>
+      </c>
+      <c r="N23" t="n">
+        <v>53</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>50</v>
+      </c>
+      <c r="X23" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ODD Ballklubb</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X24" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1089,22 +1089,22 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="W7" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="X7" t="n">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -628,7 +628,7 @@
         <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="U2" t="n">
         <v>14.3</v>
@@ -727,7 +727,7 @@
         <v>32.3</v>
       </c>
       <c r="T3" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="U3" t="n">
         <v>14.3</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1178,22 +1178,22 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="W8" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,261 +556,259 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/05/2026 3:30</t>
+          <t>27/05/2026 7:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Essen</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga+</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O2" t="n">
+        <v>19</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="W2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="AA2" t="n">
         <v>52</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0:2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>100</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27/05/2026 3:45</t>
+          <t>27/05/2026 7:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saint-Etienne</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Mirassol SP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>30</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>France Ligue 1+</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>35</v>
-      </c>
-      <c r="N3" t="n">
-        <v>37</v>
-      </c>
-      <c r="O3" t="n">
-        <v>28</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>32.3</v>
-      </c>
       <c r="T3" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="U3" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>40.5</v>
       </c>
       <c r="W3" t="n">
-        <v>50</v>
+        <v>13.1</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>46.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>45.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.7</v>
-      </c>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>29</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -818,61 +816,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.9</v>
+      </c>
       <c r="V4" t="n">
-        <v>58.8</v>
+        <v>48.2</v>
       </c>
       <c r="W4" t="n">
-        <v>17.6</v>
+        <v>14.1</v>
       </c>
       <c r="X4" t="n">
-        <v>23.5</v>
+        <v>37.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>52.9</v>
+        <v>48.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>27/05/2026 9:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LDU de Quito</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>38</v>
+      </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -881,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -889,17 +895,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32</v>
+      </c>
+      <c r="O5" t="n">
+        <v>38</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -907,70 +919,78 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.9</v>
+      </c>
       <c r="V5" t="n">
-        <v>69.2</v>
+        <v>72.7</v>
       </c>
       <c r="W5" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="X5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>46.2</v>
+        <v>27.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>28/05/2026 7:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Ind del Valle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atletico Torque</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>36</v>
+      </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>World CONMEBOL Libertadores+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -978,17 +998,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>34</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -996,88 +1022,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
       <c r="V6" t="n">
-        <v>63.6</v>
+        <v>35.7</v>
       </c>
       <c r="W6" t="n">
-        <v>27.3</v>
+        <v>21.4</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1</v>
+        <v>42.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>27.3</v>
+        <v>21.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.2</v>
-      </c>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>36</v>
+      </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>34</v>
+      </c>
+      <c r="N7" t="n">
+        <v>36</v>
+      </c>
+      <c r="O7" t="n">
+        <v>30</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1085,88 +1119,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V7" t="n">
-        <v>58.3</v>
+        <v>47.7</v>
       </c>
       <c r="W7" t="n">
-        <v>25</v>
+        <v>15.9</v>
       </c>
       <c r="X7" t="n">
-        <v>16.7</v>
+        <v>36.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3.1</v>
-      </c>
+          <t>Ind Santa Fe</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>38</v>
+      </c>
       <c r="I8" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>27</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="n">
+        <v>35</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1174,113 +1216,1550 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V8" t="n">
-        <v>51.6</v>
+        <v>40.9</v>
       </c>
       <c r="W8" t="n">
-        <v>19.4</v>
+        <v>15.1</v>
       </c>
       <c r="X8" t="n">
-        <v>29</v>
+        <v>44.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>32.3</v>
+        <v>46.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>28/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>61</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>46</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Estudiantes La Plata</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>30</v>
+      </c>
+      <c r="N10" t="n">
+        <v>44</v>
+      </c>
+      <c r="O10" t="n">
+        <v>26</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>50</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>27/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>34</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>27/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nacional (URU)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N12" t="n">
+        <v>40</v>
+      </c>
+      <c r="O12" t="n">
+        <v>25</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>27/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>27/05/2026 9:30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>100</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>28/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UCV FC</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>28</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>100</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>28/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>33</v>
+      </c>
+      <c r="N16" t="n">
+        <v>35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>32</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>50</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>28/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cienciano</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Juventud LP</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>29</v>
+      </c>
+      <c r="N17" t="n">
+        <v>49</v>
+      </c>
+      <c r="O17" t="n">
+        <v>22</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>50</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>28/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
+      <c r="N18" t="n">
+        <v>38</v>
+      </c>
+      <c r="O18" t="n">
+        <v>32</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>50</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>28/05/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Olimpia Asunción</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>61</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>50</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Estudiantes L.P.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Independiente Medellin</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Club Nacional</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>25</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Atletico-MG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>1.2</v>
       </c>
-      <c r="E9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F23" t="n">
         <v>12</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>9</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>World CONMEBOL Sudamericana+</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>55.6</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W23" t="n">
         <v>33.3</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X23" t="n">
         <v>11.1</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y23" t="n">
         <v>33.3</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z23" t="n">
         <v>11.1</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA23" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A. Italiano</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,17 +556,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/05/2026 7:00</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -626,44 +626,44 @@
         <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="U2" t="n">
         <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>65.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="W2" t="n">
-        <v>15.4</v>
+        <v>10.7</v>
       </c>
       <c r="X2" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>51.9</v>
+        <v>57.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.7</v>
+        <v>28.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27/05/2026 7:00</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Peñarol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mirassol SP</t>
+          <t>Ind Santa Fe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -671,14 +671,14 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>무승부</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -720,47 +720,47 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T3" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="W3" t="n">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="X3" t="n">
-        <v>46.4</v>
+        <v>43.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>45.2</v>
+        <v>46.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.1</v>
+        <v>10.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I4" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -820,65 +820,61 @@
         <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>48.2</v>
+        <v>37.9</v>
       </c>
       <c r="W4" t="n">
-        <v>14.1</v>
+        <v>19</v>
       </c>
       <c r="X4" t="n">
-        <v>37.6</v>
+        <v>43.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>48.2</v>
+        <v>46.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.2</v>
+        <v>13.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
+        <v>15.2</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -896,22 +892,22 @@
         </is>
       </c>
       <c r="M5" t="n">
+        <v>34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="n">
         <v>30</v>
       </c>
-      <c r="N5" t="n">
-        <v>32</v>
-      </c>
-      <c r="O5" t="n">
-        <v>38</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -920,134 +916,130 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V5" t="n">
-        <v>72.7</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/05/2026 7:00</t>
+          <t>28/05/2026 9:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ind del Valle</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>29</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.9</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>무승부</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>36</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>34</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36</v>
-      </c>
-      <c r="O6" t="n">
-        <v>30</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="X6" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.4</v>
+        <v>66.7</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1058,60 +1050,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>무승부</t>
-        </is>
-      </c>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>World CONMEBOL Libertadores+</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1120,31 +1114,31 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
       <c r="U7" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>47.7</v>
+        <v>66.7</v>
       </c>
       <c r="W7" t="n">
-        <v>15.9</v>
+        <v>11.1</v>
       </c>
       <c r="X7" t="n">
-        <v>36.4</v>
+        <v>22.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>43</v>
+        <v>77.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1155,60 +1149,62 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ind Santa Fe</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>무승부</t>
-        </is>
-      </c>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>World CONMEBOL Sudamericana+</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="N8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1217,31 +1213,31 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
       <c r="U8" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>40.9</v>
+        <v>100</v>
       </c>
       <c r="W8" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>44.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.699999999999999</v>
+        <v>100</v>
       </c>
       <c r="AA8" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1252,60 +1248,62 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>RB Bragantino</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>원정승</t>
-        </is>
-      </c>
+          <t>Carabobo</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>World CONMEBOL Sudamericana+</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>❓</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="O9" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1314,68 +1312,68 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V9" t="n">
-        <v>44.3</v>
+        <v>20</v>
       </c>
       <c r="W9" t="n">
-        <v>13.1</v>
+        <v>60</v>
       </c>
       <c r="X9" t="n">
-        <v>42.6</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>44.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>29/05/2026 4:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Estudiantes La Plata</t>
+          <t>Casa Pia AC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>União Torreense</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Portugal Primeira Liga+</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1389,17 +1387,17 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
         <v>26</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1413,64 +1411,64 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="T10" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="V10" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="W10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>29/05/2026 7:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9</v>
+        <v>3.6</v>
       </c>
       <c r="F11" t="n">
-        <v>15.2</v>
+        <v>5.6</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1488,17 +1486,17 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1512,157 +1510,169 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>46.5</v>
+        <v>45.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>50</v>
+      </c>
+      <c r="W11" t="n">
+        <v>50</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>50</v>
+      </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>29/05/2026 7:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nacional (URU)</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Junior Barranquilla</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>42</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
+      <c r="O12" t="n">
+        <v>36</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
         <v>8</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>35</v>
-      </c>
-      <c r="N12" t="n">
-        <v>40</v>
-      </c>
-      <c r="O12" t="n">
-        <v>25</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>32.3</v>
-      </c>
       <c r="T12" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
       <c r="U12" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="W12" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Independ. Rivadavia</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="F13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>World CONMEBOL Libertadores+</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1675,23 +1685,17 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>49</v>
-      </c>
-      <c r="O13" t="n">
-        <v>16</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1699,69 +1703,63 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27/05/2026 9:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="F14" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>World CONMEBOL Libertadores+</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1774,23 +1772,17 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>22</v>
-      </c>
-      <c r="N14" t="n">
-        <v>35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>43</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1798,65 +1790,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.9</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="W14" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/05/2026 7:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UCV FC</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="F15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1873,23 +1861,17 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>50</v>
-      </c>
-      <c r="N15" t="n">
-        <v>22</v>
-      </c>
-      <c r="O15" t="n">
-        <v>28</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1897,869 +1879,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>56.7</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W15" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>28/05/2026 7:00</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Caracas</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>33</v>
-      </c>
-      <c r="N16" t="n">
-        <v>35</v>
-      </c>
-      <c r="O16" t="n">
-        <v>32</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>50</v>
-      </c>
-      <c r="X16" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>28/05/2026 7:00</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Cienciano</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Juventud LP</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>49</v>
-      </c>
-      <c r="O17" t="n">
-        <v>22</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>50</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>28/05/2026 7:00</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>30</v>
-      </c>
-      <c r="N18" t="n">
-        <v>38</v>
-      </c>
-      <c r="O18" t="n">
-        <v>32</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0:0</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>50</v>
-      </c>
-      <c r="X18" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>28/05/2026 7:00</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Olimpia Asunción</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>61</v>
-      </c>
-      <c r="N19" t="n">
-        <v>23</v>
-      </c>
-      <c r="O19" t="n">
-        <v>16</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>50</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Estudiantes L.P.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Independiente Medellin</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Independiente del Valle</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>52</v>
-      </c>
-      <c r="W21" t="n">
         <v>20</v>
-      </c>
-      <c r="X21" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Club Nacional</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Coquimbo Unido</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>12</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>25</v>
-      </c>
-      <c r="X22" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Atletico-MG</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Puerto Cabello</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Olimpia</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>A. Italiano</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>13</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,17 +556,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>29/05/2026 7:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -599,17 +599,17 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -623,47 +623,47 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>46.8</v>
+        <v>44.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V2" t="n">
-        <v>64.3</v>
+        <v>66.2</v>
       </c>
       <c r="W2" t="n">
-        <v>10.7</v>
+        <v>16.9</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>16.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.1</v>
+        <v>52.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.6</v>
+        <v>32.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peñarol</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ind Santa Fe</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -671,14 +671,14 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>무승부</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I3" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -720,71 +720,77 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="U3" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>41.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>14.6</v>
+        <v>10.5</v>
       </c>
       <c r="X3" t="n">
-        <v>43.8</v>
+        <v>24.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>46.9</v>
+        <v>57.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.4</v>
+        <v>28.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>KFUM Oslo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -793,22 +799,22 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -817,97 +823,95 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T4" t="n">
-        <v>46.8</v>
+        <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V4" t="n">
-        <v>37.9</v>
+        <v>41.2</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>11.8</v>
       </c>
       <c r="X4" t="n">
-        <v>43.1</v>
+        <v>47.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>46.6</v>
+        <v>35.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 7:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Junior Barranquilla</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O5" t="n">
         <v>36</v>
       </c>
-      <c r="O5" t="n">
-        <v>30</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -916,73 +920,77 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="U5" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
-        <v>20</v>
+        <v>37.3</v>
       </c>
       <c r="W5" t="n">
-        <v>60</v>
+        <v>18.6</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>44.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>45.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Shenyang City</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -991,22 +999,22 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
         <v>29</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1015,64 +1023,64 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T6" t="n">
-        <v>46.8</v>
+        <v>44.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="W6" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="X6" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="Y6" t="n">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>12.2</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1090,22 +1098,22 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1117,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="U7" t="n">
         <v>1.9</v>
@@ -1126,52 +1134,52 @@
         <v>66.7</v>
       </c>
       <c r="W7" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="X7" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>77.8</v>
+        <v>33.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>América de Cali</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="E8" t="n">
-        <v>10.2</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1189,13 +1197,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1216,61 +1224,61 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="U8" t="n">
         <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28/05/2026 9:30</t>
+          <t>29/05/2026 9:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RB Bragantino</t>
+          <t>CA Tigre</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Alianza Atlético</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="F9" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1288,22 +1296,22 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1312,22 +1320,22 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>45.7</v>
+        <v>48</v>
       </c>
       <c r="U9" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="W9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1336,44 +1344,44 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29/05/2026 4:00</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Casa Pia AC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>União Torreense</t>
+          <t>IK Start</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Portugal Primeira Liga+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1387,22 +1395,22 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1411,68 +1419,68 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>32.3</v>
+        <v>76.2</v>
       </c>
       <c r="T10" t="n">
-        <v>45.7</v>
+        <v>51</v>
       </c>
       <c r="U10" t="n">
-        <v>14.3</v>
+        <v>56.7</v>
       </c>
       <c r="V10" t="n">
-        <v>33.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29/05/2026 7:00</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Valerenga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Kristiansund BK</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.6</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1486,17 +1494,17 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1510,68 +1518,68 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>57.7</v>
       </c>
       <c r="T11" t="n">
-        <v>45.7</v>
+        <v>48.5</v>
       </c>
       <c r="U11" t="n">
-        <v>14.3</v>
+        <v>35.3</v>
       </c>
       <c r="V11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X11" t="n">
         <v>50</v>
       </c>
-      <c r="W11" t="n">
-        <v>50</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>50</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29/05/2026 7:00</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Junior Barranquilla</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1585,17 +1593,17 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1609,70 +1617,68 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T12" t="n">
-        <v>46.8</v>
+        <v>48.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V12" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="W12" t="n">
         <v>33.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="Y12" t="n">
         <v>33.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Rosenborg BK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Independ. Rivadavia</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1682,20 +1688,26 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18</v>
+      </c>
+      <c r="O13" t="n">
+        <v>57</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1703,52 +1715,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>51</v>
+      </c>
+      <c r="U13" t="n">
+        <v>56.7</v>
+      </c>
       <c r="V13" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
       <c r="W13" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>30/05/2026 2:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Aalesund FK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
@@ -1759,7 +1777,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1772,17 +1790,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30</v>
+      </c>
+      <c r="O14" t="n">
+        <v>42</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1790,23 +1814,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>35.3</v>
+      </c>
       <c r="V14" t="n">
         <v>55.6</v>
       </c>
       <c r="W14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="X14" t="n">
         <v>33.3</v>
       </c>
-      <c r="X14" t="n">
-        <v>11.1</v>
-      </c>
       <c r="Y14" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>9</v>
@@ -1815,90 +1845,743 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>30/05/2026 3:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1.8</v>
       </c>
       <c r="E15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Italy Serie B+</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>33</v>
+      </c>
+      <c r="O15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30/05/2026 3:45</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saint-Etienne</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>France Ligue 1+</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>29</v>
+      </c>
+      <c r="N16" t="n">
+        <v>47</v>
+      </c>
+      <c r="O16" t="n">
+        <v>24</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30/05/2026 7:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CA Cerro</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>59</v>
+      </c>
+      <c r="N17" t="n">
+        <v>23</v>
+      </c>
+      <c r="O17" t="n">
+        <v>18</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>51</v>
+      </c>
+      <c r="U17" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nublense</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E18" t="n">
         <v>3.5</v>
       </c>
-      <c r="F15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Chile Primera División+</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Shenyang Urban</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SHANGHAI SIPG</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>China Super League+</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>44</v>
+      </c>
+      <c r="W19" t="n">
+        <v>24</v>
+      </c>
+      <c r="X19" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U. Catolica</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Libertadores+</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Alianza Atletico</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>50</v>
+      </c>
+      <c r="W21" t="n">
+        <v>30</v>
+      </c>
+      <c r="X21" t="n">
         <v>20</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Libertadores+</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="Y21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>America de Cali</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>World CONMEBOL Sudamericana+</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>60</v>
-      </c>
-      <c r="W15" t="n">
-        <v>20</v>
-      </c>
-      <c r="X15" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>20</v>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>50</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,60 +556,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29/05/2026 7:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.6</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -623,90 +629,96 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>44.6</v>
+        <v>48</v>
       </c>
       <c r="U2" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>66.2</v>
+        <v>52.9</v>
       </c>
       <c r="W2" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="X2" t="n">
-        <v>16.9</v>
+        <v>29.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>52.3</v>
+        <v>41.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.3</v>
+        <v>11.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>Lyn Oslo</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -720,72 +732,72 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T3" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V3" t="n">
-        <v>64.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="W3" t="n">
-        <v>10.5</v>
+        <v>21.4</v>
       </c>
       <c r="X3" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>57.9</v>
+        <v>35.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.1</v>
+        <v>14.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KFUM Oslo</t>
+          <t>Real Sociedad B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Cultural Leonesa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -795,26 +807,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -823,90 +835,96 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T4" t="n">
-        <v>48.5</v>
+        <v>44.7</v>
       </c>
       <c r="U4" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V4" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="W4" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="X4" t="n">
-        <v>47.1</v>
+        <v>36.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>35.3</v>
+        <v>18.2</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29/05/2026 7:00</t>
+          <t>31/05/2026 4:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Junior Barranquilla</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.9</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I5" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O5" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -920,72 +938,72 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T5" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V5" t="n">
-        <v>37.3</v>
+        <v>50</v>
       </c>
       <c r="W5" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>44.1</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>45.8</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shenyang City</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>무승부</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Japan J2/J3 League+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -999,22 +1017,22 @@
         </is>
       </c>
       <c r="M6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N6" t="n">
         <v>33</v>
       </c>
-      <c r="N6" t="n">
-        <v>38</v>
-      </c>
       <c r="O6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1026,70 +1044,74 @@
         <v>32.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U6" t="n">
         <v>14.3</v>
       </c>
       <c r="V6" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="W6" t="n">
-        <v>41.7</v>
+        <v>30.8</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Japan J2/J3 League+</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1098,22 +1120,22 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1122,73 +1144,77 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T7" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V7" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="W7" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>América de Cali</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>3.5</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1197,22 +1223,22 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1221,73 +1247,77 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>48</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="W8" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="X8" t="n">
-        <v>37.5</v>
+        <v>35.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>37.5</v>
+        <v>21.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29/05/2026 9:30</t>
+          <t>31/05/2026 5:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CA Tigre</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alianza Atlético</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="E9" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>World CONMEBOL Sudamericana+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1296,22 +1326,22 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1320,68 +1350,68 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
-        <v>48</v>
+        <v>44.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V9" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
       <c r="W9" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>30/05/2026 9:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IK Start</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>Brazil Serie B+</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,17 +1425,17 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1419,68 +1449,68 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>76.2</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="U10" t="n">
-        <v>56.7</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X10" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>30/05/2026 9:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valerenga</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kristiansund BK</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>Chile Primera División+</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1494,13 +1524,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="N11" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1527,59 +1557,59 @@
         <v>35.3</v>
       </c>
       <c r="V11" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="W11" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="X11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Daegu FC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1589,26 +1619,26 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1617,68 +1647,68 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>57.7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="U12" t="n">
-        <v>35.3</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="X12" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rosenborg BK</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1692,17 +1722,17 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O13" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1716,57 +1746,57 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>76.2</v>
+        <v>57.7</v>
       </c>
       <c r="T13" t="n">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="U13" t="n">
-        <v>56.7</v>
+        <v>35.3</v>
       </c>
       <c r="V13" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Y13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30/05/2026 2:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aalesund FK</t>
+          <t>Suwon FC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
@@ -1777,7 +1807,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1791,22 +1821,22 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N14" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1815,25 +1845,25 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>57.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>35.3</v>
+        <v>56.7</v>
       </c>
       <c r="V14" t="n">
-        <v>55.6</v>
+        <v>22.2</v>
       </c>
       <c r="W14" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="X14" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Y14" t="n">
         <v>33.3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>22.2</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -1845,38 +1875,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30/05/2026 3:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>GimPo Citizen</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Italy Serie B+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1886,26 +1916,26 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1914,68 +1944,68 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>32.3</v>
+        <v>57.7</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>48.5</v>
       </c>
       <c r="U15" t="n">
-        <v>14.3</v>
+        <v>35.3</v>
       </c>
       <c r="V15" t="n">
-        <v>62.5</v>
+        <v>11.1</v>
       </c>
       <c r="W15" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>77.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30/05/2026 3:45</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Chengdu Qianbao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saint-Etienne</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>France Ligue 1+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1989,22 +2019,22 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="N16" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2013,68 +2043,68 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>32.3</v>
+        <v>57.7</v>
       </c>
       <c r="T16" t="n">
-        <v>44.6</v>
+        <v>48.5</v>
       </c>
       <c r="U16" t="n">
-        <v>14.3</v>
+        <v>35.3</v>
       </c>
       <c r="V16" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="W16" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="X16" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30/05/2026 7:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Chongqing Tongliang</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA Cerro</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2084,21 +2114,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="N17" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2112,70 +2142,68 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>76.2</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="U17" t="n">
-        <v>56.7</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X17" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="Y17" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sichuan FC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="E18" t="n">
         <v>3.5</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>3.7</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chile Primera División+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2185,20 +2213,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>48</v>
+      </c>
+      <c r="N18" t="n">
+        <v>21</v>
+      </c>
+      <c r="O18" t="n">
+        <v>31</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2206,88 +2240,98 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>35.3</v>
+      </c>
       <c r="V18" t="n">
-        <v>43.3</v>
+        <v>37.5</v>
       </c>
       <c r="W18" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="X18" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Racing Club (URU)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SHANGHAI SIPG</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>51</v>
+      </c>
+      <c r="N19" t="n">
         <v>25</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>China Super League+</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>24</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2295,65 +2339,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>35.3</v>
+      </c>
       <c r="V19" t="n">
-        <v>44</v>
+        <v>83.3</v>
       </c>
       <c r="W19" t="n">
-        <v>24</v>
+        <v>16.7</v>
       </c>
       <c r="X19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U. Catolica</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="F20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>World CONMEBOL Libertadores+</t>
+          <t>Norway Eliteserien+</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2366,17 +2414,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>44</v>
+      </c>
+      <c r="N20" t="n">
+        <v>27</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2384,204 +2438,2584 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>50</v>
+      </c>
+      <c r="U20" t="n">
+        <v>56.7</v>
+      </c>
       <c r="V20" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="W20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="X20" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="Y20" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Moss FK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="E21" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="F21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>23</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>43</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>50</v>
+      </c>
+      <c r="U21" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.5</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>50</v>
       </c>
-      <c r="W21" t="n">
-        <v>30</v>
-      </c>
-      <c r="X21" t="n">
-        <v>20</v>
-      </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AD Ceuta</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Albacete Balompie</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Spain Segunda División+</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>21</v>
+      </c>
+      <c r="N22" t="n">
+        <v>47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>31</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>31/05/2026 3:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Danubio FC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CA Progreso</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>54</v>
+      </c>
+      <c r="N23" t="n">
+        <v>26</v>
+      </c>
+      <c r="O23" t="n">
+        <v>20</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>48</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>100</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>31/05/2026 4:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A+</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>41</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30</v>
+      </c>
+      <c r="O24" t="n">
+        <v>29</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>50</v>
+      </c>
+      <c r="U24" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>60</v>
+      </c>
+      <c r="W24" t="n">
+        <v>40</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>31/05/2026 4:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Chile Primera División+</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>19</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20</v>
+      </c>
+      <c r="O25" t="n">
+        <v>61</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>31/05/2026 6:30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Univ de Chile</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Deportes Concepción</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Chile Primera División+</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>45</v>
+      </c>
+      <c r="N26" t="n">
+        <v>33</v>
+      </c>
+      <c r="O26" t="n">
+        <v>21</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>31/05/2026 8:30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>24</v>
+      </c>
+      <c r="N27" t="n">
+        <v>37</v>
+      </c>
+      <c r="O27" t="n">
+        <v>38</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>50</v>
+      </c>
+      <c r="W27" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Atletico Paranaense</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>24</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Brazil Serie A+</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Brazil Serie A+</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vitoria</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>27</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Brazil Serie A+</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>63</v>
+      </c>
+      <c r="W30" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atletico Goianiense</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>65</v>
+      </c>
+      <c r="W31" t="n">
+        <v>15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>60</v>
+      </c>
+      <c r="W32" t="n">
+        <v>20</v>
+      </c>
+      <c r="X32" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>16</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>13</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Chile Primera División+</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>00:30</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>America de Cali</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Macara</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Universidad de Concepcion</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>38</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Chile Primera División+</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="W35" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Henan Jianye</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hangzhou Greentown</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>1.7</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>27</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>China Super League+</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chengdu Better City</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Shandong Luneng</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>22</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>China Super League+</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Qingdao Youth Island</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E38" t="n">
         <v>3.5</v>
       </c>
-      <c r="F22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>34</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>China Super League+</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sichuan Jiuniu</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Qingdao Jonoon</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>32</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>China Super League+</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>50</v>
+      </c>
+      <c r="W39" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kashima</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>34</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ODD Ballklubb</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>24</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Norway 1. Division+</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X41" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CF Os Belenenses</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>41</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Portugal Segunda Liga+</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="W42" t="n">
+        <v>22</v>
+      </c>
+      <c r="X42" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Suwon City FC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Seongnam FC</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>36</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>South Korea South-Korea K League 2+</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sporting Gijon</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>34</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Spain Segunda División+</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="W44" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X44" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>41</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Spain Segunda División+</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SS Reyes</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UD Logroñés</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>23</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>13</v>
+      </c>
+      <c r="X46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Meyrin</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chênois</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
         <v>14</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>World CONMEBOL Sudamericana+</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Switzerland 1. Liga Classic - Group 1+</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="W47" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Racing Montevideo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>28</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
         <v>50</v>
       </c>
-      <c r="W22" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>14</v>
+      <c r="W48" t="n">
+        <v>25</v>
+      </c>
+      <c r="X48" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA48"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,42 +556,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>China Super League+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -601,26 +601,26 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -629,68 +629,68 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T2" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V2" t="n">
-        <v>52.9</v>
+        <v>40</v>
       </c>
       <c r="W2" t="n">
-        <v>17.6</v>
+        <v>6.7</v>
       </c>
       <c r="X2" t="n">
-        <v>29.4</v>
+        <v>53.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>41.2</v>
+        <v>46.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Egersunds IK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lyn Oslo</t>
+          <t>Stromsgodset IF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -704,26 +704,26 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N3" t="n">
         <v>33</v>
       </c>
       <c r="O3" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -732,72 +732,72 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>57.7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>48.5</v>
+        <v>51.8</v>
       </c>
       <c r="U3" t="n">
-        <v>35.3</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
+        <v>30.8</v>
       </c>
       <c r="W3" t="n">
-        <v>21.4</v>
+        <v>23.1</v>
       </c>
       <c r="X3" t="n">
-        <v>28.6</v>
+        <v>46.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.7</v>
+        <v>38.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01/06/2026 8:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Real Sociedad B</t>
+          <t>Remo PA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cultural Leonesa</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="E4" t="n">
         <v>3.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Spain Segunda División+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,26 +807,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O4" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -835,57 +835,57 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>44.7</v>
+        <v>51.8</v>
       </c>
       <c r="U4" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>45.5</v>
+        <v>29.4</v>
       </c>
       <c r="W4" t="n">
-        <v>18.2</v>
+        <v>23.5</v>
       </c>
       <c r="X4" t="n">
-        <v>36.4</v>
+        <v>47.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.2</v>
+        <v>41.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>31/05/2026 4:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Hwaseong FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Spain Segunda División+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -914,17 +914,17 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
         <v>29</v>
       </c>
-      <c r="O5" t="n">
-        <v>31</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="W5" t="n">
+        <v>40</v>
+      </c>
+      <c r="X5" t="n">
         <v>20</v>
       </c>
-      <c r="X5" t="n">
-        <v>30</v>
-      </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>10</v>
@@ -968,42 +968,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>RB Bragantino</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>무승부</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Japan J2/J3 League+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1017,22 +1017,22 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1044,69 +1044,69 @@
         <v>32.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
         <v>14.3</v>
       </c>
       <c r="V6" t="n">
-        <v>38.5</v>
+        <v>43.8</v>
       </c>
       <c r="W6" t="n">
-        <v>30.8</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01/06/2026 1:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>무승부</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Japan J2/J3 League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1116,26 +1116,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1144,72 +1144,72 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>57.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>48.5</v>
+        <v>51.9</v>
       </c>
       <c r="U7" t="n">
-        <v>35.3</v>
+        <v>56.7</v>
       </c>
       <c r="V7" t="n">
+        <v>20</v>
+      </c>
+      <c r="W7" t="n">
         <v>40</v>
-      </c>
-      <c r="W7" t="n">
-        <v>20</v>
       </c>
       <c r="X7" t="n">
         <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>46.7</v>
+        <v>30</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.3</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01/06/2026 1:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qingdao West Coast</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Racing Genk</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>2.2</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.9</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>무승부</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Belgium Jupiler Pro League+</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1219,26 +1219,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>30</v>
       </c>
       <c r="N8" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0:0</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1247,72 +1247,72 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>48</v>
+        <v>51.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="W8" t="n">
-        <v>35.7</v>
+        <v>20</v>
       </c>
       <c r="X8" t="n">
-        <v>35.7</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31/05/2026 5:30</t>
+          <t>01/06/2026 1:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>무승부</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Brazil Serie A+</t>
+          <t>Chile Primera División+</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1322,101 +1322,105 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N9" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="O9" t="n">
+        <v>33</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y9" t="n">
         <v>25</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>18.2</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/05/2026 9:00</t>
+          <t>01/06/2026 3:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Juventud LP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Montevideo Wanderers</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Uruguay Primera División - Apertura+</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1425,22 +1429,22 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="N10" t="n">
+        <v>28</v>
+      </c>
+      <c r="O10" t="n">
         <v>37</v>
       </c>
-      <c r="O10" t="n">
-        <v>15</v>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1449,64 +1453,68 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>32.3</v>
       </c>
       <c r="T10" t="n">
-        <v>48</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9</v>
+        <v>14.3</v>
       </c>
       <c r="V10" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="W10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30/05/2026 9:30</t>
+          <t>01/06/2026 6:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>O Higgins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Everton de Vina</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="E11" t="n">
         <v>3.4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1515,7 +1523,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1524,22 +1532,22 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1548,92 +1556,96 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="U11" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V11" t="n">
-        <v>40</v>
+        <v>36.8</v>
       </c>
       <c r="W11" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>40</v>
+        <v>26.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>01/06/2026 8:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F12" t="n">
         <v>3.6</v>
       </c>
-      <c r="F12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1647,31 +1659,31 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T12" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V12" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="W12" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="X12" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.3</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1682,29 +1694,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1722,13 +1734,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1749,28 +1761,28 @@
         <v>57.7</v>
       </c>
       <c r="T13" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="U13" t="n">
         <v>35.3</v>
       </c>
       <c r="V13" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1781,29 +1793,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suwon FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
         <v>3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1817,59 +1829,59 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O14" t="n">
+        <v>32</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Y14" t="n">
         <v>25</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2:2</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>50</v>
-      </c>
-      <c r="U14" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="V14" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>33.3</v>
-      </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1880,33 +1892,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Poblense</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GimPo Citizen</t>
+          <t>CD Águilas</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1916,21 +1928,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O15" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:1</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1944,68 +1956,68 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>57.7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>48.5</v>
+        <v>51.8</v>
       </c>
       <c r="U15" t="n">
-        <v>35.3</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>11.1</v>
+        <v>66.7</v>
       </c>
       <c r="X15" t="n">
-        <v>77.8</v>
+        <v>33.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chengdu Qianbao</t>
+          <t>Real Oviedo B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2019,22 +2031,22 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O16" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2043,57 +2055,47 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T16" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="U16" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>50</v>
-      </c>
-      <c r="W16" t="n">
-        <v>50</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
+        <v>14.3</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
         <v>3.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
@@ -2118,22 +2120,22 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2142,25 +2144,25 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T17" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V17" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>40</v>
-      </c>
-      <c r="X17" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2172,38 +2174,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sichuan FC</t>
+          <t>Albion FC (URU)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>CA Torque</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Uruguay Primera División - Apertura+</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2213,17 +2215,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2244,65 +2246,65 @@
         <v>57.7</v>
       </c>
       <c r="T18" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="U18" t="n">
         <v>35.3</v>
       </c>
       <c r="V18" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="W18" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="X18" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Racing Club (URU)</t>
+          <t>São Bernardo SP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Novorizontino SP</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>Brazil Serie B+</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2312,26 +2314,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N19" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="O19" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3:0</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2340,31 +2342,31 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="U19" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V19" t="n">
-        <v>83.3</v>
+        <v>20</v>
       </c>
       <c r="W19" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y19" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2375,33 +2377,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vila Nova FC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E20" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien+</t>
+          <t>Brazil Serie B+</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2415,22 +2417,22 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="N20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2439,57 +2441,57 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>76.2</v>
+        <v>32.3</v>
       </c>
       <c r="T20" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="U20" t="n">
-        <v>56.7</v>
+        <v>14.3</v>
       </c>
       <c r="V20" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="W20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moss FK</t>
+          <t>Strommen IF</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
@@ -2514,13 +2516,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N21" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2541,7 +2543,7 @@
         <v>76.2</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="U21" t="n">
         <v>56.7</v>
@@ -2550,16 +2552,16 @@
         <v>37.5</v>
       </c>
       <c r="W21" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z21" t="n">
         <v>12.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>8</v>
@@ -2568,38 +2570,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AD Ceuta</t>
+          <t>Bryne FK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albacete Balompie</t>
+          <t>IL Hodd</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Spain Segunda División+</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2613,22 +2615,22 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="O22" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2637,68 +2639,68 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>32.3</v>
+        <v>57.7</v>
       </c>
       <c r="T22" t="n">
-        <v>44.7</v>
+        <v>49.5</v>
       </c>
       <c r="U22" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>14.3</v>
       </c>
-      <c r="V22" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>25</v>
-      </c>
       <c r="Y22" t="n">
-        <v>37.5</v>
+        <v>57.1</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>31/05/2026 3:00</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danubio FC</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CA Progreso</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2712,17 +2714,17 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N23" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>3:0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2736,13 +2738,13 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T23" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V23" t="n">
         <v>100</v>
@@ -2754,50 +2756,50 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>31/05/2026 4:00</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Raufoss IL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Brazil Serie A+</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2807,26 +2809,26 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="O24" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3:1</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2835,68 +2837,68 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>76.2</v>
+        <v>87.5</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="U24" t="n">
-        <v>56.7</v>
+        <v>73.5</v>
       </c>
       <c r="V24" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="W24" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>31/05/2026 4:00</t>
+          <t>01/06/2026 0:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ranheim Fotball</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="F25" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Chile Primera División+</t>
+          <t>Norway 1. Division+</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2906,26 +2908,26 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O25" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2934,58 +2936,68 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>57.7</v>
+        <v>76.2</v>
       </c>
       <c r="T25" t="n">
-        <v>48.5</v>
+        <v>51.9</v>
       </c>
       <c r="U25" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+        <v>56.7</v>
+      </c>
+      <c r="V25" t="n">
+        <v>25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>31/05/2026 6:30</t>
+          <t>01/06/2026 1:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Univ de Chile</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deportes Concepción</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F26" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chile Primera División+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2999,17 +3011,17 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3023,19 +3035,19 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>32.3</v>
+        <v>57.7</v>
       </c>
       <c r="T26" t="n">
-        <v>44.7</v>
+        <v>49.5</v>
       </c>
       <c r="U26" t="n">
-        <v>14.3</v>
+        <v>35.3</v>
       </c>
       <c r="V26" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="W26" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3047,44 +3059,44 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>31/05/2026 8:30</t>
+          <t>01/06/2026 2:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético Baleares</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Real Jaén</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="E27" t="n">
         <v>2.9</v>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3098,17 +3110,17 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3122,22 +3134,22 @@
         </is>
       </c>
       <c r="S27" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T27" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="U27" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="W27" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -3146,46 +3158,44 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01/06/2026 2:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Atletico Paranaense</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CD Ourense</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Brazil Serie A+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3198,17 +3208,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>10</v>
+      </c>
+      <c r="N28" t="n">
+        <v>50</v>
+      </c>
+      <c r="O28" t="n">
+        <v>40</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3216,61 +3232,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>01/06/2026 4:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chapecoense SC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3287,17 +3297,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>72</v>
+      </c>
+      <c r="N29" t="n">
+        <v>19</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3305,65 +3321,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="S29" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="U29" t="n">
         <v>14.3</v>
       </c>
-      <c r="X29" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>01/06/2026 8:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vitoria</t>
+          <t>CRB AL</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="F30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Brazil Serie A+</t>
+          <t>Brazil Serie B+</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3376,17 +3386,23 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>23</v>
+      </c>
+      <c r="N30" t="n">
+        <v>36</v>
+      </c>
+      <c r="O30" t="n">
+        <v>41</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3394,52 +3410,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V30" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="W30" t="n">
-        <v>14.8</v>
+        <v>33.3</v>
       </c>
       <c r="X30" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="E31" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3448,11 +3470,11 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3462,7 +3484,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3487,22 +3509,22 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="W31" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="X31" t="n">
-        <v>20</v>
+        <v>34.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -3513,22 +3535,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Vasco DA Gama</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Atletico-MG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3537,11 +3559,11 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Brazil Serie A+</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3576,48 +3598,48 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="W32" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="X32" t="n">
-        <v>20</v>
+        <v>30.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>26.7</v>
+        <v>30.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Operario-PR</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1.9</v>
       </c>
       <c r="E33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F33" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3626,7 +3648,7 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3665,48 +3687,48 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>56.2</v>
+        <v>46.2</v>
       </c>
       <c r="W33" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="X33" t="n">
-        <v>18.8</v>
+        <v>30.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>12.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>U. Catolica</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="F34" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3715,7 +3737,7 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3729,7 +3751,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3754,48 +3776,48 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>61.5</v>
+        <v>51.7</v>
       </c>
       <c r="W34" t="n">
-        <v>23.1</v>
+        <v>13.8</v>
       </c>
       <c r="X34" t="n">
-        <v>15.4</v>
+        <v>34.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="Z34" t="n">
-        <v>15.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Universidad de Concepcion</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="E35" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F35" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3804,11 +3826,11 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Chile Primera División+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3818,7 +3840,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3843,48 +3865,48 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>44.7</v>
+        <v>46.2</v>
       </c>
       <c r="W35" t="n">
-        <v>18.4</v>
+        <v>23.1</v>
       </c>
       <c r="X35" t="n">
-        <v>36.8</v>
+        <v>30.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>44.7</v>
+        <v>30.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hangzhou Greentown</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F36" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3893,11 +3915,11 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3932,48 +3954,48 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>59.3</v>
+        <v>54.5</v>
       </c>
       <c r="W36" t="n">
-        <v>14.8</v>
+        <v>27.3</v>
       </c>
       <c r="X36" t="n">
-        <v>25.9</v>
+        <v>18.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>37</v>
+        <v>27.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chengdu Better City</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E37" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3982,11 +4004,11 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4021,48 +4043,48 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>45.5</v>
+        <v>53.8</v>
       </c>
       <c r="W37" t="n">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="X37" t="n">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Castellón</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="E38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4071,11 +4093,11 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4110,61 +4132,61 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>38.2</v>
+        <v>44.4</v>
       </c>
       <c r="W38" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="X38" t="n">
-        <v>35.3</v>
+        <v>27.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>35.3</v>
+        <v>38.9</v>
       </c>
       <c r="Z38" t="n">
-        <v>8.800000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Deportivo La Coruna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="E39" t="n">
         <v>3.5</v>
       </c>
       <c r="F39" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>China Super League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4174,7 +4196,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4199,48 +4221,48 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="W39" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="X39" t="n">
-        <v>31.2</v>
+        <v>44.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>25</v>
+        <v>48.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>18.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kashima</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="F40" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4249,11 +4271,11 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Japan J1 League+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4288,48 +4310,48 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>58.8</v>
+        <v>46.7</v>
       </c>
       <c r="W40" t="n">
-        <v>14.7</v>
+        <v>23.3</v>
       </c>
       <c r="X40" t="n">
-        <v>26.5</v>
+        <v>30</v>
       </c>
       <c r="Y40" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ODD Ballklubb</t>
+          <t>Conquense</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="E41" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4338,11 +4360,11 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Norway 1. Division+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4377,48 +4399,48 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>58.3</v>
+        <v>58.8</v>
       </c>
       <c r="W41" t="n">
-        <v>16.7</v>
+        <v>23.5</v>
       </c>
       <c r="X41" t="n">
-        <v>25</v>
+        <v>17.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.5</v>
+        <v>17.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="E42" t="n">
         <v>3.2</v>
       </c>
       <c r="F42" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4427,11 +4449,11 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Portugal Segunda Liga+</t>
+          <t>Spain Segunda División RFEF - Play-offs+</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4441,7 +4463,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4466,48 +4488,48 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
-        <v>43.9</v>
+        <v>53.8</v>
       </c>
       <c r="W42" t="n">
-        <v>22</v>
+        <v>23.1</v>
       </c>
       <c r="X42" t="n">
-        <v>34.1</v>
+        <v>23.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>39</v>
+        <v>23.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>14.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Suwon City FC</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Atletico Torque</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="E43" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4516,11 +4538,11 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Uruguay Primera División - Apertura+</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4530,7 +4552,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -4555,467 +4577,22 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>47.2</v>
+        <v>55.6</v>
       </c>
       <c r="W43" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="X43" t="n">
-        <v>30.6</v>
+        <v>33.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>38.9</v>
+        <v>40.7</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.300000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Granada CF</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Sporting Gijon</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>34</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Spain Segunda División+</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X44" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Real Sociedad II</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
-        <v>41</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Spain Segunda División+</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="W45" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SS Reyes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>UD Logroñés</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>23</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Spain Segunda División RFEF - Play-offs+</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="W46" t="n">
-        <v>13</v>
-      </c>
-      <c r="X46" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Meyrin</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Chênois</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>14</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Switzerland 1. Liga Classic - Group 1+</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="W47" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="X47" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Racing Montevideo</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Defensor Sporting</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>28</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División - Apertura+</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="n">
-        <v>50</v>
-      </c>
-      <c r="W48" t="n">
-        <v>25</v>
-      </c>
-      <c r="X48" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,42 +556,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/06/2026 3:00</t>
+          <t>03/06/2026 9:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Junior Barranquilla</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liverpool (URU)</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>홈승</t>
+          <t>원정승</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I2" t="n">
         <v>11</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>Colombia Primera A+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2:1</t>
+          <t>0:2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -629,25 +629,25 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>57.7</v>
+        <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>49.1</v>
+        <v>44.4</v>
       </c>
       <c r="U2" t="n">
-        <v>35.3</v>
+        <v>14.3</v>
       </c>
       <c r="V2" t="n">
-        <v>36.4</v>
+        <v>45.5</v>
       </c>
       <c r="W2" t="n">
         <v>27.3</v>
       </c>
       <c r="X2" t="n">
-        <v>36.4</v>
+        <v>27.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="Z2" t="n">
         <v>9.1</v>
@@ -659,38 +659,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01/06/2026 9:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Atletico Nacional</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Chile Primera División+</t>
+          <t>Colombia Primera A+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,425 +702,47 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>57</v>
-      </c>
-      <c r="N3" t="n">
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>55</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" t="n">
         <v>25</v>
       </c>
-      <c r="O3" t="n">
-        <v>19</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2:1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>02/06/2026 7:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Brazil Serie B+</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>37</v>
-      </c>
-      <c r="N4" t="n">
-        <v>42</v>
-      </c>
-      <c r="O4" t="n">
-        <v>21</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A. Italiano</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>31</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Chile Primera División+</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Liverpool Montevideo</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División - Apertura+</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Penarol</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Central Espanol</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Uruguay Primera División - Apertura+</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,71 +556,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03/06/2026 9:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Junior Barranquilla</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Colombia Primera A+</t>
+          <t>South Korea South-Korea K League 2+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>원정정배</t>
+          <t>홈정배</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -632,117 +632,606 @@
         <v>32.3</v>
       </c>
       <c r="T2" t="n">
-        <v>44.4</v>
+        <v>45.1</v>
       </c>
       <c r="U2" t="n">
         <v>14.3</v>
       </c>
       <c r="V2" t="n">
-        <v>45.5</v>
+        <v>56.2</v>
       </c>
       <c r="W2" t="n">
-        <v>27.3</v>
+        <v>18.8</v>
       </c>
       <c r="X2" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.3</v>
+        <v>31.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.1</v>
+        <v>12.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Junior</t>
+          <t>Kamatamare Sanuki</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atletico Nacional</t>
+          <t>Nagano Parceiro</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>36</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>34</v>
+      </c>
+      <c r="N3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O3" t="n">
+        <v>36</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Daegu FC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paju Citizen</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>South Korea South-Korea K League 2+</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Busan I'Park</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Asan Mugunghwa</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>South Korea South-Korea K League 2+</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06/06/2026 7:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Danubio FC</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operario-PR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E7" t="n">
         <v>2.7</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>50</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kamatamare Sanuki</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Parceiro Nagano</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="W8" t="n">
         <v>20</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Colombia Primera A+</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>원정정배</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>55</v>
-      </c>
-      <c r="W3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="X8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
         <v>40</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,27 +556,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Seongnam FC</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Kochi United SC</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -587,16 +587,16 @@
         <v>41</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Japan J2/J3 League+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -608,14 +608,14 @@
         <v>41</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -629,68 +629,68 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>45.1</v>
+        <v>49.2</v>
       </c>
       <c r="U2" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
       <c r="W2" t="n">
-        <v>18.8</v>
+        <v>23.1</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>31.2</v>
+        <v>53.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>23.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kamatamare Sanuki</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nagano Parceiro</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>원정승</t>
+          <t>홈승</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="n">
         <v>30</v>
       </c>
-      <c r="O3" t="n">
-        <v>36</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0:2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -732,73 +732,77 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>45.1</v>
+        <v>49.2</v>
       </c>
       <c r="U3" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="W3" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="X3" t="n">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>33.3</v>
+        <v>9.1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Tochigi Uva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>MIO Biwako Kusatsu</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>4.3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Japan J2/J3 League+</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,17 +811,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>3:1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -831,92 +835,96 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>76.2</v>
       </c>
       <c r="T4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>56.7</v>
       </c>
       <c r="V4" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="W4" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="X4" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ehime FC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>South Korea South-Korea K League 2+</t>
+          <t>Japan J2/J3 League+</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -930,73 +938,77 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32.3</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>45.1</v>
+        <v>49.2</v>
       </c>
       <c r="U5" t="n">
-        <v>14.3</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
-        <v>55.6</v>
+        <v>45.5</v>
       </c>
       <c r="W5" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="X5" t="n">
-        <v>22.2</v>
+        <v>45.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/06/2026 7:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Montevideo Wanderers</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Danubio FC</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>3.7</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>Japan J1 League+</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>★</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1005,17 +1017,17 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>2:1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1029,93 +1041,101 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>57.7</v>
       </c>
       <c r="T6" t="n">
-        <v>50.8</v>
+        <v>49.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>35.3</v>
       </c>
       <c r="V6" t="n">
-        <v>37.5</v>
+        <v>46.7</v>
       </c>
       <c r="W6" t="n">
-        <v>12.5</v>
+        <v>26.7</v>
       </c>
       <c r="X6" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operario-PR</t>
+          <t>JEF United Chiba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>43</v>
+      </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Brazil Serie B+</t>
+          <t>Japan J1 League+</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>❓</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>30</v>
+      </c>
+      <c r="N7" t="n">
+        <v>43</v>
+      </c>
+      <c r="O7" t="n">
+        <v>27</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1123,115 +1143,2602 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="W7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.300000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kamatamare Sanuki</t>
+          <t>FC Tokyo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parceiro Nagano</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O8" t="n">
+        <v>37</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>42</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>42</v>
+      </c>
+      <c r="N9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>30</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yokohama FC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Renofa Yamaguchi</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>40</v>
+      </c>
+      <c r="N10" t="n">
+        <v>35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>25</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>40</v>
+      </c>
+      <c r="W10" t="n">
+        <v>20</v>
+      </c>
+      <c r="X10" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vegalta Sendai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kataller Toyama</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>41</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>37</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Consadole Sapporo</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>40</v>
+      </c>
+      <c r="N12" t="n">
+        <v>28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mito HollyHock</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>39</v>
+      </c>
+      <c r="I13" t="n">
+        <v>13</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>36</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>39</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FC Gifu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gainare Tottori</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>34</v>
+      </c>
+      <c r="N14" t="n">
+        <v>21</v>
+      </c>
+      <c r="O14" t="n">
+        <v>45</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Urawa Red Diamonds</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>42</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>32</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>40</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>31</v>
+      </c>
+      <c r="N16" t="n">
+        <v>35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>33</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Yokohama Marinos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>38</v>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>35</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38</v>
+      </c>
+      <c r="O17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>51</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>51</v>
+      </c>
+      <c r="N18" t="n">
+        <v>23</v>
+      </c>
+      <c r="O18" t="n">
+        <v>26</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>원정승</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>36</v>
+      </c>
+      <c r="I19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>35</v>
+      </c>
+      <c r="N19" t="n">
+        <v>29</v>
+      </c>
+      <c r="O19" t="n">
+        <v>36</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gyeongnam</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>39</v>
+      </c>
+      <c r="I20" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>South Korea South-Korea K League 2+</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>31</v>
+      </c>
+      <c r="N20" t="n">
+        <v>39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hwaseong FC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Suwon Bluewings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>무승부</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>36</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>South Korea South-Korea K League 2+</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>31</v>
+      </c>
+      <c r="N21" t="n">
+        <v>36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>33</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sagamihara</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Roasso Kumamoto</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>2.4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>43</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>35</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Matsumoto Yamaga</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nara Club</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>50</v>
+      </c>
+      <c r="W23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jubilo Iwata</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FC Osaka</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Japan J2/J3 League+</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>42</v>
+      </c>
+      <c r="N24" t="n">
+        <v>34</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sanfrecce</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>31</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23</v>
+      </c>
+      <c r="O25" t="n">
+        <v>46</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>50</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Central Español</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Racing Club (URU)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
         <v>3.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>45</v>
+      </c>
+      <c r="O26" t="n">
+        <v>30</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>07/06/2026 3:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CA Torque</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CD Maldonado</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>27</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>48</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Brazil Serie B+</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Shimizu S-pulse</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>홈승</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>40</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>55</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Japan J1 League+</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X29" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tochigi City</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Biwako Shiga</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>32</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Japan J2/J3 League+</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>50</v>
-      </c>
-      <c r="W8" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
         <v>30</v>
       </c>
-      <c r="Y8" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>40</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Spain Segunda División+</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>60</v>
+      </c>
+      <c r="W31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Racing Montevideo</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>16</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>원정정배</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atletico Torque</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>39</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Uruguay Primera División - Apertura+</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>홈정배</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/today_ai_all_picks.xlsx
+++ b/today_ai_all_picks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,38 +556,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/06/2026 7:00</t>
+          <t>10/06/2026 7:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liverpool (URU)</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Uruguay Primera División - Apertura+</t>
+          <t>Brazil Serie B+</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -597,26 +597,26 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>홈정배</t>
+          <t>원정정배</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O2" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0:1</t>
+          <t>2:2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -625,68 +625,60 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
-        <v>50.7</v>
+        <v>57.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>100</v>
-      </c>
-      <c r="W2" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
         <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/06/2026 7:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Junior Barranquilla</t>
+          <t>Castellón</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>홈승</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Colombia Primera A+</t>
+          <t>Spain Segunda División+</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -699,23 +691,17 @@
           <t>홈정배</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>34</v>
-      </c>
-      <c r="N3" t="n">
-        <v>40</v>
-      </c>
-      <c r="O3" t="n">
-        <v>27</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2:2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -723,398 +709,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>56.7</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="W3" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="X3" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>09/06/2026 8:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Vila Nova FC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Brazil Serie B+</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N4" t="n">
-        <v>29</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1:0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V4" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="W4" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>America Mineiro</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Atletico Goianiense</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>51</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Brazil Serie B+</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>51</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Atletico Nacional</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Junior</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>홈승</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Colombia Primera A+</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>❓</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>홈정배</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="in